--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128116295</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128116294</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128116283</v>
       </c>
       <c r="B6" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116268</v>
+        <v>128116307</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708226</v>
+        <v>708223</v>
       </c>
       <c r="R9" t="n">
-        <v>7294304</v>
+        <v>7294146</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116307</v>
+        <v>128116290</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>91364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708223</v>
+        <v>708225</v>
       </c>
       <c r="R10" t="n">
-        <v>7294146</v>
+        <v>7294123</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116290</v>
+        <v>128116268</v>
       </c>
       <c r="B11" t="n">
-        <v>91363</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708225</v>
+        <v>708226</v>
       </c>
       <c r="R11" t="n">
-        <v>7294123</v>
+        <v>7294304</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116249</v>
+        <v>128116304</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708207</v>
+        <v>708225</v>
       </c>
       <c r="R13" t="n">
-        <v>7294133</v>
+        <v>7294108</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116304</v>
+        <v>128116286</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>91364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708225</v>
+        <v>708482</v>
       </c>
       <c r="R14" t="n">
-        <v>7294108</v>
+        <v>7294632</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116258</v>
+        <v>128116249</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708471</v>
+        <v>708207</v>
       </c>
       <c r="R15" t="n">
-        <v>7294139</v>
+        <v>7294133</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116286</v>
+        <v>128116258</v>
       </c>
       <c r="B16" t="n">
-        <v>91363</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708482</v>
+        <v>708471</v>
       </c>
       <c r="R16" t="n">
-        <v>7294632</v>
+        <v>7294139</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116281</v>
+        <v>128116259</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708480</v>
+        <v>708415</v>
       </c>
       <c r="R17" t="n">
-        <v>7294127</v>
+        <v>7294078</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2327,7 +2327,7 @@
         <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>56855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R20" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116315</v>
+        <v>128116279</v>
       </c>
       <c r="B24" t="n">
-        <v>91923</v>
+        <v>79108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708330</v>
+        <v>708215</v>
       </c>
       <c r="R24" t="n">
-        <v>7294664</v>
+        <v>7294156</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116285</v>
+        <v>128116315</v>
       </c>
       <c r="B25" t="n">
-        <v>91345</v>
+        <v>91924</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708246</v>
+        <v>708330</v>
       </c>
       <c r="R25" t="n">
-        <v>7294412</v>
+        <v>7294664</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116279</v>
+        <v>128116285</v>
       </c>
       <c r="B26" t="n">
-        <v>79108</v>
+        <v>91346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708215</v>
+        <v>708246</v>
       </c>
       <c r="R26" t="n">
-        <v>7294156</v>
+        <v>7294412</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3103,7 +3103,7 @@
         <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116248</v>
+        <v>128116255</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708292</v>
+        <v>708407</v>
       </c>
       <c r="R28" t="n">
-        <v>7294045</v>
+        <v>7294680</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116274</v>
+        <v>128116289</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>91364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708243</v>
+        <v>708501</v>
       </c>
       <c r="R29" t="n">
-        <v>7294417</v>
+        <v>7294429</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B30" t="n">
-        <v>91363</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R30" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R31" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>91924</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R33" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,6 +3753,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3779,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B34" t="n">
-        <v>91923</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3790,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R34" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3850,11 +3855,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116262</v>
+        <v>128116308</v>
       </c>
       <c r="B36" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708295</v>
+        <v>708216</v>
       </c>
       <c r="R36" t="n">
-        <v>7294459</v>
+        <v>7294159</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116308</v>
+        <v>128116293</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4086,21 +4086,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708216</v>
+        <v>708521</v>
       </c>
       <c r="R37" t="n">
-        <v>7294159</v>
+        <v>7294413</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,32 +4172,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116270</v>
+        <v>128116309</v>
       </c>
       <c r="B38" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708197</v>
+        <v>708284</v>
       </c>
       <c r="R38" t="n">
-        <v>7294331</v>
+        <v>7294509</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116293</v>
+        <v>128116299</v>
       </c>
       <c r="B39" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708521</v>
+        <v>708462</v>
       </c>
       <c r="R39" t="n">
-        <v>7294413</v>
+        <v>7294126</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116309</v>
+        <v>128116262</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708284</v>
+        <v>708295</v>
       </c>
       <c r="R40" t="n">
-        <v>7294509</v>
+        <v>7294459</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116299</v>
+        <v>128116270</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708462</v>
+        <v>708197</v>
       </c>
       <c r="R41" t="n">
-        <v>7294126</v>
+        <v>7294331</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116265</v>
+        <v>128116252</v>
       </c>
       <c r="B42" t="n">
-        <v>98467</v>
+        <v>97345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708523</v>
+        <v>708525</v>
       </c>
       <c r="R42" t="n">
-        <v>7294599</v>
+        <v>7294394</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4757,7 +4757,7 @@
         <v>128116239</v>
       </c>
       <c r="B44" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116252</v>
+        <v>128116265</v>
       </c>
       <c r="B45" t="n">
-        <v>97344</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708525</v>
+        <v>708523</v>
       </c>
       <c r="R45" t="n">
-        <v>7294394</v>
+        <v>7294599</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128116288</v>
+        <v>128116296</v>
       </c>
       <c r="B46" t="n">
-        <v>91363</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708485</v>
+        <v>708450</v>
       </c>
       <c r="R46" t="n">
-        <v>7294476</v>
+        <v>7294389</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128116296</v>
+        <v>128116288</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>91364</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708450</v>
+        <v>708485</v>
       </c>
       <c r="R47" t="n">
-        <v>7294389</v>
+        <v>7294476</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B48" t="n">
-        <v>91923</v>
+        <v>82870</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R48" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B49" t="n">
-        <v>82870</v>
+        <v>91924</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R49" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5339,7 +5339,7 @@
         <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116261</v>
+        <v>128116277</v>
       </c>
       <c r="B53" t="n">
-        <v>97344</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708394</v>
+        <v>708269</v>
       </c>
       <c r="R53" t="n">
-        <v>7294544</v>
+        <v>7294506</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5698,6 +5698,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5724,10 +5729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116240</v>
+        <v>128116254</v>
       </c>
       <c r="B54" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5740,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5764,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708376</v>
+        <v>708400</v>
       </c>
       <c r="R54" t="n">
-        <v>7294699</v>
+        <v>7294674</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,10 +5826,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116310</v>
+        <v>128116260</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5832,21 +5837,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708426</v>
+        <v>708208</v>
       </c>
       <c r="R55" t="n">
-        <v>7294468</v>
+        <v>7294348</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,7 +5923,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116254</v>
+        <v>128116256</v>
       </c>
       <c r="B56" t="n">
         <v>80132</v>
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708400</v>
+        <v>708495</v>
       </c>
       <c r="R56" t="n">
-        <v>7294674</v>
+        <v>7294673</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6020,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116260</v>
+        <v>128116240</v>
       </c>
       <c r="B57" t="n">
-        <v>80132</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6031,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6055,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708208</v>
+        <v>708376</v>
       </c>
       <c r="R57" t="n">
-        <v>7294348</v>
+        <v>7294699</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,7 +6117,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116305</v>
+        <v>128116310</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708209</v>
+        <v>708426</v>
       </c>
       <c r="R58" t="n">
-        <v>7294140</v>
+        <v>7294468</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,32 +6214,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116277</v>
+        <v>128116305</v>
       </c>
       <c r="B59" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6249,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708269</v>
+        <v>708209</v>
       </c>
       <c r="R59" t="n">
-        <v>7294506</v>
+        <v>7294140</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6280,11 +6285,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6311,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116243</v>
+        <v>128116292</v>
       </c>
       <c r="B60" t="n">
-        <v>57832</v>
+        <v>91368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708329</v>
+        <v>708500</v>
       </c>
       <c r="R60" t="n">
         <v>7294658</v>
@@ -6408,10 +6408,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116292</v>
+        <v>128116243</v>
       </c>
       <c r="B61" t="n">
-        <v>91367</v>
+        <v>57832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6419,21 +6419,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708500</v>
+        <v>708329</v>
       </c>
       <c r="R61" t="n">
         <v>7294658</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116256</v>
+        <v>128116261</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>97345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708495</v>
+        <v>708394</v>
       </c>
       <c r="R62" t="n">
-        <v>7294673</v>
+        <v>7294544</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6699,32 +6699,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128116287</v>
+        <v>128116276</v>
       </c>
       <c r="B64" t="n">
-        <v>91363</v>
+        <v>98468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708515</v>
+        <v>708267</v>
       </c>
       <c r="R64" t="n">
-        <v>7294574</v>
+        <v>7294433</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -6796,32 +6796,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128116276</v>
+        <v>128116287</v>
       </c>
       <c r="B65" t="n">
-        <v>98467</v>
+        <v>91364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708267</v>
+        <v>708515</v>
       </c>
       <c r="R65" t="n">
-        <v>7294433</v>
+        <v>7294574</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B66" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R66" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116266</v>
+        <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708534</v>
+        <v>708195</v>
       </c>
       <c r="R68" t="n">
-        <v>7294561</v>
+        <v>7294329</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R69" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128116295</v>
+        <v>128116294</v>
       </c>
       <c r="B2" t="n">
         <v>91368</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708340</v>
+        <v>708521</v>
       </c>
       <c r="R2" t="n">
-        <v>7294066</v>
+        <v>7294393</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128116294</v>
+        <v>128116295</v>
       </c>
       <c r="B3" t="n">
         <v>91368</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708521</v>
+        <v>708340</v>
       </c>
       <c r="R3" t="n">
-        <v>7294393</v>
+        <v>7294066</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116306</v>
+        <v>128116290</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>91364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708199</v>
+        <v>708225</v>
       </c>
       <c r="R8" t="n">
-        <v>7294151</v>
+        <v>7294123</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116307</v>
+        <v>128116306</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708223</v>
+        <v>708199</v>
       </c>
       <c r="R9" t="n">
-        <v>7294146</v>
+        <v>7294151</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116290</v>
+        <v>128116307</v>
       </c>
       <c r="B10" t="n">
-        <v>91364</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708225</v>
+        <v>708223</v>
       </c>
       <c r="R10" t="n">
-        <v>7294123</v>
+        <v>7294146</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116268</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708226</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294304</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128116246</v>
+        <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708396</v>
+        <v>708226</v>
       </c>
       <c r="R12" t="n">
-        <v>7294100</v>
+        <v>7294304</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116286</v>
+        <v>128116258</v>
       </c>
       <c r="B14" t="n">
-        <v>91364</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708482</v>
+        <v>708471</v>
       </c>
       <c r="R14" t="n">
-        <v>7294632</v>
+        <v>7294139</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116249</v>
+        <v>128116286</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>91364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708207</v>
+        <v>708482</v>
       </c>
       <c r="R15" t="n">
-        <v>7294133</v>
+        <v>7294632</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116258</v>
+        <v>128116249</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708471</v>
+        <v>708207</v>
       </c>
       <c r="R16" t="n">
-        <v>7294139</v>
+        <v>7294133</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R17" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116312</v>
+        <v>128116259</v>
       </c>
       <c r="B18" t="n">
-        <v>82870</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708202</v>
+        <v>708415</v>
       </c>
       <c r="R18" t="n">
-        <v>7294136</v>
+        <v>7294078</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116253</v>
+        <v>128116312</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>82870</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708194</v>
+        <v>708202</v>
       </c>
       <c r="R19" t="n">
-        <v>7294336</v>
+        <v>7294136</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116281</v>
+        <v>128116253</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>92833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708480</v>
+        <v>708194</v>
       </c>
       <c r="R20" t="n">
-        <v>7294127</v>
+        <v>7294336</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116245</v>
+        <v>128116315</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>91924</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708491</v>
+        <v>708330</v>
       </c>
       <c r="R23" t="n">
-        <v>7294463</v>
+        <v>7294664</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116279</v>
+        <v>128116285</v>
       </c>
       <c r="B24" t="n">
-        <v>79108</v>
+        <v>91346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708215</v>
+        <v>708246</v>
       </c>
       <c r="R24" t="n">
-        <v>7294156</v>
+        <v>7294412</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116315</v>
+        <v>128116279</v>
       </c>
       <c r="B25" t="n">
-        <v>91924</v>
+        <v>79108</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708330</v>
+        <v>708215</v>
       </c>
       <c r="R25" t="n">
-        <v>7294664</v>
+        <v>7294156</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116285</v>
+        <v>128116245</v>
       </c>
       <c r="B26" t="n">
-        <v>91346</v>
+        <v>57669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708246</v>
+        <v>708491</v>
       </c>
       <c r="R26" t="n">
-        <v>7294412</v>
+        <v>7294463</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116313</v>
+        <v>128116301</v>
       </c>
       <c r="B33" t="n">
-        <v>91924</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708432</v>
+        <v>708375</v>
       </c>
       <c r="R33" t="n">
-        <v>7294694</v>
+        <v>7294094</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,11 +3753,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3881,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116301</v>
+        <v>128116313</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>91924</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708375</v>
+        <v>708432</v>
       </c>
       <c r="R35" t="n">
-        <v>7294094</v>
+        <v>7294694</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116308</v>
+        <v>128116262</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708216</v>
+        <v>708295</v>
       </c>
       <c r="R36" t="n">
-        <v>7294159</v>
+        <v>7294459</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116262</v>
+        <v>128116308</v>
       </c>
       <c r="B40" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708295</v>
+        <v>708216</v>
       </c>
       <c r="R40" t="n">
-        <v>7294459</v>
+        <v>7294159</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B48" t="n">
-        <v>82870</v>
+        <v>91924</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B49" t="n">
-        <v>91924</v>
+        <v>82870</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R49" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5433,7 +5433,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128116275</v>
+        <v>128116273</v>
       </c>
       <c r="B51" t="n">
         <v>98468</v>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>708260</v>
+        <v>708246</v>
       </c>
       <c r="R51" t="n">
-        <v>7294418</v>
+        <v>7294403</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128116273</v>
+        <v>128116275</v>
       </c>
       <c r="B52" t="n">
         <v>98468</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>708246</v>
+        <v>708260</v>
       </c>
       <c r="R52" t="n">
-        <v>7294403</v>
+        <v>7294418</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116277</v>
+        <v>128116240</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>79647</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708269</v>
+        <v>708376</v>
       </c>
       <c r="R53" t="n">
-        <v>7294506</v>
+        <v>7294699</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5698,11 +5698,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6020,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116240</v>
+        <v>128116292</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>91368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6031,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6055,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708376</v>
+        <v>708500</v>
       </c>
       <c r="R57" t="n">
-        <v>7294699</v>
+        <v>7294658</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6311,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116292</v>
+        <v>128116243</v>
       </c>
       <c r="B60" t="n">
-        <v>91368</v>
+        <v>57832</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708500</v>
+        <v>708329</v>
       </c>
       <c r="R60" t="n">
         <v>7294658</v>
@@ -6408,32 +6403,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116243</v>
+        <v>128116261</v>
       </c>
       <c r="B61" t="n">
-        <v>57832</v>
+        <v>97345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708329</v>
+        <v>708394</v>
       </c>
       <c r="R61" t="n">
-        <v>7294658</v>
+        <v>7294544</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6505,32 +6500,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116261</v>
+        <v>128116277</v>
       </c>
       <c r="B62" t="n">
-        <v>97345</v>
+        <v>98468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6535,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708394</v>
+        <v>708269</v>
       </c>
       <c r="R62" t="n">
-        <v>7294544</v>
+        <v>7294506</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6576,6 +6571,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6699,32 +6699,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128116276</v>
+        <v>128116287</v>
       </c>
       <c r="B64" t="n">
-        <v>98468</v>
+        <v>91364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708267</v>
+        <v>708515</v>
       </c>
       <c r="R64" t="n">
-        <v>7294433</v>
+        <v>7294574</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -6796,32 +6796,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128116287</v>
+        <v>128116276</v>
       </c>
       <c r="B65" t="n">
-        <v>91364</v>
+        <v>98468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708515</v>
+        <v>708267</v>
       </c>
       <c r="R65" t="n">
-        <v>7294574</v>
+        <v>7294433</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116242</v>
+        <v>128116241</v>
       </c>
       <c r="B66" t="n">
-        <v>57832</v>
+        <v>56864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708298</v>
+        <v>708398</v>
       </c>
       <c r="R66" t="n">
-        <v>7294185</v>
+        <v>7294092</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116241</v>
+        <v>128116242</v>
       </c>
       <c r="B67" t="n">
-        <v>56864</v>
+        <v>57832</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708398</v>
+        <v>708298</v>
       </c>
       <c r="R67" t="n">
-        <v>7294092</v>
+        <v>7294185</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128116294</v>
+        <v>128116295</v>
       </c>
       <c r="B2" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708521</v>
+        <v>708340</v>
       </c>
       <c r="R2" t="n">
-        <v>7294393</v>
+        <v>7294066</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128116295</v>
+        <v>128116294</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708340</v>
+        <v>708521</v>
       </c>
       <c r="R3" t="n">
-        <v>7294066</v>
+        <v>7294393</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1066,7 +1066,7 @@
         <v>128116283</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116290</v>
+        <v>128116306</v>
       </c>
       <c r="B8" t="n">
-        <v>91364</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708225</v>
+        <v>708199</v>
       </c>
       <c r="R8" t="n">
-        <v>7294123</v>
+        <v>7294151</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116306</v>
+        <v>128116307</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708199</v>
+        <v>708223</v>
       </c>
       <c r="R9" t="n">
-        <v>7294151</v>
+        <v>7294146</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116307</v>
+        <v>128116246</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708223</v>
+        <v>708396</v>
       </c>
       <c r="R10" t="n">
-        <v>7294146</v>
+        <v>7294100</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116290</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>91365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708225</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294123</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1648,7 +1648,7 @@
         <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128116286</v>
       </c>
       <c r="B15" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116281</v>
+        <v>128116312</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>82870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708480</v>
+        <v>708202</v>
       </c>
       <c r="R17" t="n">
-        <v>7294127</v>
+        <v>7294136</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116259</v>
+        <v>128116253</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>92834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708415</v>
+        <v>708194</v>
       </c>
       <c r="R18" t="n">
-        <v>7294078</v>
+        <v>7294336</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116312</v>
+        <v>128116259</v>
       </c>
       <c r="B19" t="n">
-        <v>82870</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708202</v>
+        <v>708415</v>
       </c>
       <c r="R19" t="n">
-        <v>7294136</v>
+        <v>7294078</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116253</v>
+        <v>128116281</v>
       </c>
       <c r="B20" t="n">
-        <v>92833</v>
+        <v>56855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708194</v>
+        <v>708480</v>
       </c>
       <c r="R20" t="n">
-        <v>7294336</v>
+        <v>7294127</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2715,7 +2715,7 @@
         <v>128116315</v>
       </c>
       <c r="B23" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128116285</v>
       </c>
       <c r="B24" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>128116289</v>
       </c>
       <c r="B29" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>91925</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R34" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3850,6 +3850,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>91924</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R35" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116262</v>
+        <v>128116270</v>
       </c>
       <c r="B36" t="n">
-        <v>57776</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708295</v>
+        <v>708197</v>
       </c>
       <c r="R36" t="n">
-        <v>7294459</v>
+        <v>7294331</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116293</v>
+        <v>128116262</v>
       </c>
       <c r="B37" t="n">
-        <v>91368</v>
+        <v>57776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708521</v>
+        <v>708295</v>
       </c>
       <c r="R37" t="n">
-        <v>7294413</v>
+        <v>7294459</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116309</v>
+        <v>128116308</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708284</v>
+        <v>708216</v>
       </c>
       <c r="R38" t="n">
-        <v>7294509</v>
+        <v>7294159</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116299</v>
+        <v>128116309</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708462</v>
+        <v>708284</v>
       </c>
       <c r="R39" t="n">
-        <v>7294126</v>
+        <v>7294509</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116308</v>
+        <v>128116299</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708216</v>
+        <v>708462</v>
       </c>
       <c r="R40" t="n">
-        <v>7294159</v>
+        <v>7294126</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116270</v>
+        <v>128116293</v>
       </c>
       <c r="B41" t="n">
-        <v>98468</v>
+        <v>91369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708197</v>
+        <v>708521</v>
       </c>
       <c r="R41" t="n">
-        <v>7294331</v>
+        <v>7294413</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116252</v>
+        <v>128116303</v>
       </c>
       <c r="B42" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708525</v>
+        <v>708288</v>
       </c>
       <c r="R42" t="n">
-        <v>7294394</v>
+        <v>7294045</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>91316</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R43" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116239</v>
+        <v>128116252</v>
       </c>
       <c r="B44" t="n">
-        <v>91315</v>
+        <v>97346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,21 +4765,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708194</v>
+        <v>708525</v>
       </c>
       <c r="R44" t="n">
-        <v>7294336</v>
+        <v>7294394</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4854,7 +4854,7 @@
         <v>128116265</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>128116288</v>
       </c>
       <c r="B47" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116314</v>
+        <v>128116272</v>
       </c>
       <c r="B48" t="n">
-        <v>91924</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
         <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294415</v>
+        <v>7294403</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116272</v>
+        <v>128116314</v>
       </c>
       <c r="B50" t="n">
-        <v>98468</v>
+        <v>91925</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294403</v>
+        <v>7294415</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128116273</v>
+        <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>708246</v>
+        <v>708260</v>
       </c>
       <c r="R51" t="n">
-        <v>7294403</v>
+        <v>7294418</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128116275</v>
+        <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>708260</v>
+        <v>708246</v>
       </c>
       <c r="R52" t="n">
-        <v>7294418</v>
+        <v>7294403</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116240</v>
+        <v>128116243</v>
       </c>
       <c r="B53" t="n">
-        <v>79647</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708376</v>
+        <v>708329</v>
       </c>
       <c r="R53" t="n">
-        <v>7294699</v>
+        <v>7294658</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116254</v>
+        <v>128116277</v>
       </c>
       <c r="B54" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708400</v>
+        <v>708269</v>
       </c>
       <c r="R54" t="n">
-        <v>7294674</v>
+        <v>7294506</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5795,6 +5795,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5821,10 +5826,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116260</v>
+        <v>128116240</v>
       </c>
       <c r="B55" t="n">
-        <v>80132</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5832,21 +5837,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708208</v>
+        <v>708376</v>
       </c>
       <c r="R55" t="n">
-        <v>7294348</v>
+        <v>7294699</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,10 +5923,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116256</v>
+        <v>128116310</v>
       </c>
       <c r="B56" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5934,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708495</v>
+        <v>708426</v>
       </c>
       <c r="R56" t="n">
-        <v>7294673</v>
+        <v>7294468</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6020,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116292</v>
+        <v>128116254</v>
       </c>
       <c r="B57" t="n">
-        <v>91368</v>
+        <v>80132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6031,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6055,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708500</v>
+        <v>708400</v>
       </c>
       <c r="R57" t="n">
-        <v>7294658</v>
+        <v>7294674</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,10 +6117,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116310</v>
+        <v>128116260</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6123,21 +6128,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708426</v>
+        <v>708208</v>
       </c>
       <c r="R58" t="n">
-        <v>7294468</v>
+        <v>7294348</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6306,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116243</v>
+        <v>128116256</v>
       </c>
       <c r="B60" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6317,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,10 +6346,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708329</v>
+        <v>708495</v>
       </c>
       <c r="R60" t="n">
-        <v>7294658</v>
+        <v>7294673</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6403,32 +6408,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116261</v>
+        <v>128116292</v>
       </c>
       <c r="B61" t="n">
-        <v>97345</v>
+        <v>91369</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708394</v>
+        <v>708500</v>
       </c>
       <c r="R61" t="n">
-        <v>7294544</v>
+        <v>7294658</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6500,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116277</v>
+        <v>128116261</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>97346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6535,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708269</v>
+        <v>708394</v>
       </c>
       <c r="R62" t="n">
-        <v>7294506</v>
+        <v>7294544</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6571,11 +6576,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>128116287</v>
       </c>
       <c r="B64" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>128116276</v>
       </c>
       <c r="B65" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116241</v>
+        <v>128116269</v>
       </c>
       <c r="B66" t="n">
-        <v>56864</v>
+        <v>98469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708398</v>
+        <v>708195</v>
       </c>
       <c r="R66" t="n">
-        <v>7294092</v>
+        <v>7294329</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B67" t="n">
-        <v>57832</v>
+        <v>98469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R67" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116269</v>
+        <v>128116241</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>56864</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708195</v>
+        <v>708398</v>
       </c>
       <c r="R68" t="n">
-        <v>7294329</v>
+        <v>7294092</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116266</v>
+        <v>128116242</v>
       </c>
       <c r="B69" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708534</v>
+        <v>708298</v>
       </c>
       <c r="R69" t="n">
-        <v>7294561</v>
+        <v>7294185</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128116295</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128116294</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128116283</v>
       </c>
       <c r="B6" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116246</v>
+        <v>128116290</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708396</v>
+        <v>708225</v>
       </c>
       <c r="R10" t="n">
-        <v>7294100</v>
+        <v>7294123</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116290</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>91365</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708225</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294123</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1648,7 +1648,7 @@
         <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116304</v>
+        <v>128116286</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>91366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708225</v>
+        <v>708482</v>
       </c>
       <c r="R13" t="n">
-        <v>7294108</v>
+        <v>7294632</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116258</v>
+        <v>128116304</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708471</v>
+        <v>708225</v>
       </c>
       <c r="R14" t="n">
-        <v>7294139</v>
+        <v>7294108</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116286</v>
+        <v>128116258</v>
       </c>
       <c r="B15" t="n">
-        <v>91365</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708482</v>
+        <v>708471</v>
       </c>
       <c r="R15" t="n">
-        <v>7294632</v>
+        <v>7294139</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116312</v>
+        <v>128116259</v>
       </c>
       <c r="B17" t="n">
-        <v>82870</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708202</v>
+        <v>708415</v>
       </c>
       <c r="R17" t="n">
-        <v>7294136</v>
+        <v>7294078</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116253</v>
+        <v>128116281</v>
       </c>
       <c r="B18" t="n">
-        <v>92834</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708194</v>
+        <v>708480</v>
       </c>
       <c r="R18" t="n">
-        <v>7294336</v>
+        <v>7294127</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116259</v>
+        <v>128116312</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>82870</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708415</v>
+        <v>708202</v>
       </c>
       <c r="R19" t="n">
-        <v>7294078</v>
+        <v>7294136</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116281</v>
+        <v>128116253</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708480</v>
+        <v>708194</v>
       </c>
       <c r="R20" t="n">
-        <v>7294127</v>
+        <v>7294336</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2715,7 +2715,7 @@
         <v>128116315</v>
       </c>
       <c r="B23" t="n">
-        <v>91925</v>
+        <v>91926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116285</v>
+        <v>128116279</v>
       </c>
       <c r="B24" t="n">
-        <v>91347</v>
+        <v>79108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708246</v>
+        <v>708215</v>
       </c>
       <c r="R24" t="n">
-        <v>7294412</v>
+        <v>7294156</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116279</v>
+        <v>128116285</v>
       </c>
       <c r="B25" t="n">
-        <v>79108</v>
+        <v>91348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708215</v>
+        <v>708246</v>
       </c>
       <c r="R25" t="n">
-        <v>7294156</v>
+        <v>7294412</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3103,7 +3103,7 @@
         <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116255</v>
+        <v>128116289</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>91366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708407</v>
+        <v>708501</v>
       </c>
       <c r="R28" t="n">
-        <v>7294680</v>
+        <v>7294429</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116289</v>
+        <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>91365</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708501</v>
+        <v>708407</v>
       </c>
       <c r="R29" t="n">
-        <v>7294429</v>
+        <v>7294680</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3491,7 +3491,7 @@
         <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116301</v>
+        <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>91926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708375</v>
+        <v>708432</v>
       </c>
       <c r="R33" t="n">
-        <v>7294094</v>
+        <v>7294694</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,6 +3753,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3779,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116313</v>
+        <v>128116301</v>
       </c>
       <c r="B34" t="n">
-        <v>91925</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708432</v>
+        <v>708375</v>
       </c>
       <c r="R34" t="n">
-        <v>7294694</v>
+        <v>7294094</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3850,11 +3855,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3884,7 +3884,7 @@
         <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116270</v>
+        <v>128116293</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>91370</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708197</v>
+        <v>708521</v>
       </c>
       <c r="R36" t="n">
-        <v>7294331</v>
+        <v>7294413</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116262</v>
+        <v>128116299</v>
       </c>
       <c r="B37" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708295</v>
+        <v>708462</v>
       </c>
       <c r="R37" t="n">
-        <v>7294459</v>
+        <v>7294126</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116308</v>
+        <v>128116309</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708216</v>
+        <v>708284</v>
       </c>
       <c r="R38" t="n">
-        <v>7294159</v>
+        <v>7294509</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116309</v>
+        <v>128116308</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708284</v>
+        <v>708216</v>
       </c>
       <c r="R39" t="n">
-        <v>7294509</v>
+        <v>7294159</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116299</v>
+        <v>128116262</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708462</v>
+        <v>708295</v>
       </c>
       <c r="R40" t="n">
-        <v>7294126</v>
+        <v>7294459</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116293</v>
+        <v>128116270</v>
       </c>
       <c r="B41" t="n">
-        <v>91369</v>
+        <v>98470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708521</v>
+        <v>708197</v>
       </c>
       <c r="R41" t="n">
-        <v>7294413</v>
+        <v>7294331</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>91317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R42" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B43" t="n">
-        <v>91316</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R43" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116252</v>
+        <v>128116303</v>
       </c>
       <c r="B44" t="n">
-        <v>97346</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708525</v>
+        <v>708288</v>
       </c>
       <c r="R44" t="n">
-        <v>7294394</v>
+        <v>7294045</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116265</v>
+        <v>128116252</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>97347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708523</v>
+        <v>708525</v>
       </c>
       <c r="R45" t="n">
-        <v>7294599</v>
+        <v>7294394</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5048,7 +5048,7 @@
         <v>128116288</v>
       </c>
       <c r="B47" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116272</v>
+        <v>128116311</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>82870</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R48" t="n">
-        <v>7294403</v>
+        <v>7294070</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B49" t="n">
-        <v>82870</v>
+        <v>91926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R49" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116314</v>
+        <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>91925</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294415</v>
+        <v>7294403</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5436,7 +5436,7 @@
         <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>128116277</v>
       </c>
       <c r="B54" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,32 +5826,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116240</v>
+        <v>128116261</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>97347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708376</v>
+        <v>708394</v>
       </c>
       <c r="R55" t="n">
-        <v>7294699</v>
+        <v>7294544</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5923,10 +5923,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116310</v>
+        <v>128116240</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5934,21 +5934,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708426</v>
+        <v>708376</v>
       </c>
       <c r="R56" t="n">
-        <v>7294468</v>
+        <v>7294699</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6214,10 +6214,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116305</v>
+        <v>128116256</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708209</v>
+        <v>708495</v>
       </c>
       <c r="R59" t="n">
-        <v>7294140</v>
+        <v>7294673</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116256</v>
+        <v>128116292</v>
       </c>
       <c r="B60" t="n">
-        <v>80132</v>
+        <v>91370</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708495</v>
+        <v>708500</v>
       </c>
       <c r="R60" t="n">
-        <v>7294673</v>
+        <v>7294658</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6408,10 +6408,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116292</v>
+        <v>128116305</v>
       </c>
       <c r="B61" t="n">
-        <v>91369</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6419,21 +6419,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708500</v>
+        <v>708209</v>
       </c>
       <c r="R61" t="n">
-        <v>7294658</v>
+        <v>7294140</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116261</v>
+        <v>128116310</v>
       </c>
       <c r="B62" t="n">
-        <v>97346</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708394</v>
+        <v>708426</v>
       </c>
       <c r="R62" t="n">
-        <v>7294544</v>
+        <v>7294468</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>128116287</v>
       </c>
       <c r="B64" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>128116276</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116269</v>
+        <v>128116241</v>
       </c>
       <c r="B66" t="n">
-        <v>98469</v>
+        <v>56864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708195</v>
+        <v>708398</v>
       </c>
       <c r="R66" t="n">
-        <v>7294329</v>
+        <v>7294092</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116266</v>
+        <v>128116242</v>
       </c>
       <c r="B67" t="n">
-        <v>98469</v>
+        <v>57832</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708534</v>
+        <v>708298</v>
       </c>
       <c r="R67" t="n">
-        <v>7294561</v>
+        <v>7294185</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116241</v>
+        <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708398</v>
+        <v>708195</v>
       </c>
       <c r="R68" t="n">
-        <v>7294092</v>
+        <v>7294329</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R69" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116306</v>
+        <v>128116290</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>91366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708199</v>
+        <v>708225</v>
       </c>
       <c r="R8" t="n">
-        <v>7294151</v>
+        <v>7294123</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116307</v>
+        <v>128116246</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708223</v>
+        <v>708396</v>
       </c>
       <c r="R9" t="n">
-        <v>7294146</v>
+        <v>7294100</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116290</v>
+        <v>128116306</v>
       </c>
       <c r="B10" t="n">
-        <v>91366</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708225</v>
+        <v>708199</v>
       </c>
       <c r="R10" t="n">
-        <v>7294123</v>
+        <v>7294151</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116307</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708223</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294146</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116304</v>
+        <v>128116258</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708225</v>
+        <v>708471</v>
       </c>
       <c r="R14" t="n">
-        <v>7294108</v>
+        <v>7294139</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116258</v>
+        <v>128116304</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708471</v>
+        <v>708225</v>
       </c>
       <c r="R15" t="n">
-        <v>7294139</v>
+        <v>7294108</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116259</v>
+        <v>128116312</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>82870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708415</v>
+        <v>708202</v>
       </c>
       <c r="R17" t="n">
-        <v>7294078</v>
+        <v>7294136</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116281</v>
+        <v>128116253</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708480</v>
+        <v>708194</v>
       </c>
       <c r="R18" t="n">
-        <v>7294127</v>
+        <v>7294336</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116312</v>
+        <v>128116259</v>
       </c>
       <c r="B19" t="n">
-        <v>82870</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708202</v>
+        <v>708415</v>
       </c>
       <c r="R19" t="n">
-        <v>7294136</v>
+        <v>7294078</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116253</v>
+        <v>128116281</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>56855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708194</v>
+        <v>708480</v>
       </c>
       <c r="R20" t="n">
-        <v>7294336</v>
+        <v>7294127</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116315</v>
+        <v>128116251</v>
       </c>
       <c r="B23" t="n">
-        <v>91926</v>
+        <v>97347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708330</v>
+        <v>708490</v>
       </c>
       <c r="R23" t="n">
-        <v>7294664</v>
+        <v>7294651</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116279</v>
+        <v>128116315</v>
       </c>
       <c r="B24" t="n">
-        <v>79108</v>
+        <v>91926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708215</v>
+        <v>708330</v>
       </c>
       <c r="R24" t="n">
-        <v>7294156</v>
+        <v>7294664</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116245</v>
+        <v>128116279</v>
       </c>
       <c r="B26" t="n">
-        <v>57669</v>
+        <v>79108</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708491</v>
+        <v>708215</v>
       </c>
       <c r="R26" t="n">
-        <v>7294463</v>
+        <v>7294156</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116251</v>
+        <v>128116245</v>
       </c>
       <c r="B27" t="n">
-        <v>97347</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708490</v>
+        <v>708491</v>
       </c>
       <c r="R27" t="n">
-        <v>7294651</v>
+        <v>7294463</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B28" t="n">
-        <v>91366</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R28" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R29" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R30" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R31" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B33" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R33" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,11 +3753,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3881,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R35" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116293</v>
+        <v>128116262</v>
       </c>
       <c r="B36" t="n">
-        <v>91370</v>
+        <v>57776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708521</v>
+        <v>708295</v>
       </c>
       <c r="R36" t="n">
-        <v>7294413</v>
+        <v>7294459</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116299</v>
+        <v>128116270</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708462</v>
+        <v>708197</v>
       </c>
       <c r="R37" t="n">
-        <v>7294126</v>
+        <v>7294331</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116309</v>
+        <v>128116293</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708284</v>
+        <v>708521</v>
       </c>
       <c r="R38" t="n">
-        <v>7294509</v>
+        <v>7294413</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116262</v>
+        <v>128116309</v>
       </c>
       <c r="B40" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708295</v>
+        <v>708284</v>
       </c>
       <c r="R40" t="n">
-        <v>7294459</v>
+        <v>7294509</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116270</v>
+        <v>128116299</v>
       </c>
       <c r="B41" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708197</v>
+        <v>708462</v>
       </c>
       <c r="R41" t="n">
-        <v>7294331</v>
+        <v>7294126</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B42" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R42" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116265</v>
+        <v>128116252</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708523</v>
+        <v>708525</v>
       </c>
       <c r="R43" t="n">
-        <v>7294599</v>
+        <v>7294394</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>91317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R44" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116252</v>
+        <v>128116303</v>
       </c>
       <c r="B45" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708525</v>
+        <v>708288</v>
       </c>
       <c r="R45" t="n">
-        <v>7294394</v>
+        <v>7294045</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116311</v>
+        <v>128116272</v>
       </c>
       <c r="B48" t="n">
-        <v>82870</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294070</v>
+        <v>7294403</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B49" t="n">
-        <v>91926</v>
+        <v>82870</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R49" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116272</v>
+        <v>128116314</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294403</v>
+        <v>7294415</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116243</v>
+        <v>128116292</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>91370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708329</v>
+        <v>708500</v>
       </c>
       <c r="R53" t="n">
         <v>7294658</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116277</v>
+        <v>128116240</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>79647</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708269</v>
+        <v>708376</v>
       </c>
       <c r="R54" t="n">
-        <v>7294506</v>
+        <v>7294699</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5795,11 +5795,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5826,32 +5821,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116261</v>
+        <v>128116254</v>
       </c>
       <c r="B55" t="n">
-        <v>97347</v>
+        <v>80132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5861,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708394</v>
+        <v>708400</v>
       </c>
       <c r="R55" t="n">
-        <v>7294544</v>
+        <v>7294674</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5923,10 +5918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116240</v>
+        <v>128116260</v>
       </c>
       <c r="B56" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5934,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708376</v>
+        <v>708208</v>
       </c>
       <c r="R56" t="n">
-        <v>7294699</v>
+        <v>7294348</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6020,7 +6015,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116254</v>
+        <v>128116256</v>
       </c>
       <c r="B57" t="n">
         <v>80132</v>
@@ -6055,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708400</v>
+        <v>708495</v>
       </c>
       <c r="R57" t="n">
-        <v>7294674</v>
+        <v>7294673</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6117,10 +6112,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116260</v>
+        <v>128116310</v>
       </c>
       <c r="B58" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6128,21 +6123,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708208</v>
+        <v>708426</v>
       </c>
       <c r="R58" t="n">
-        <v>7294348</v>
+        <v>7294468</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6214,10 +6209,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116256</v>
+        <v>128116305</v>
       </c>
       <c r="B59" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6225,21 +6220,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6249,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708495</v>
+        <v>708209</v>
       </c>
       <c r="R59" t="n">
-        <v>7294673</v>
+        <v>7294140</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6311,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116292</v>
+        <v>128116243</v>
       </c>
       <c r="B60" t="n">
-        <v>91370</v>
+        <v>57832</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708500</v>
+        <v>708329</v>
       </c>
       <c r="R60" t="n">
         <v>7294658</v>
@@ -6408,32 +6403,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116305</v>
+        <v>128116277</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708209</v>
+        <v>708269</v>
       </c>
       <c r="R61" t="n">
-        <v>7294140</v>
+        <v>7294506</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6479,6 +6474,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116310</v>
+        <v>128116261</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708426</v>
+        <v>708394</v>
       </c>
       <c r="R62" t="n">
-        <v>7294468</v>
+        <v>7294544</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6699,32 +6699,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128116287</v>
+        <v>128116276</v>
       </c>
       <c r="B64" t="n">
-        <v>91366</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708515</v>
+        <v>708267</v>
       </c>
       <c r="R64" t="n">
-        <v>7294574</v>
+        <v>7294433</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -6796,32 +6796,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128116276</v>
+        <v>128116287</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>91366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708267</v>
+        <v>708515</v>
       </c>
       <c r="R65" t="n">
-        <v>7294433</v>
+        <v>7294574</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116246</v>
+        <v>128116306</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708396</v>
+        <v>708199</v>
       </c>
       <c r="R9" t="n">
-        <v>7294100</v>
+        <v>7294151</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116306</v>
+        <v>128116307</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708199</v>
+        <v>708223</v>
       </c>
       <c r="R10" t="n">
-        <v>7294151</v>
+        <v>7294146</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116307</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708223</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294146</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R28" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R29" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B30" t="n">
-        <v>91366</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R30" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R31" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R33" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,6 +3753,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R35" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116292</v>
+        <v>128116240</v>
       </c>
       <c r="B53" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708500</v>
+        <v>708376</v>
       </c>
       <c r="R53" t="n">
-        <v>7294658</v>
+        <v>7294699</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116240</v>
+        <v>128116254</v>
       </c>
       <c r="B54" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708376</v>
+        <v>708400</v>
       </c>
       <c r="R54" t="n">
-        <v>7294699</v>
+        <v>7294674</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116254</v>
+        <v>128116260</v>
       </c>
       <c r="B55" t="n">
         <v>80132</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708400</v>
+        <v>708208</v>
       </c>
       <c r="R55" t="n">
-        <v>7294674</v>
+        <v>7294348</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116260</v>
+        <v>128116256</v>
       </c>
       <c r="B56" t="n">
         <v>80132</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708208</v>
+        <v>708495</v>
       </c>
       <c r="R56" t="n">
-        <v>7294348</v>
+        <v>7294673</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116256</v>
+        <v>128116310</v>
       </c>
       <c r="B57" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708495</v>
+        <v>708426</v>
       </c>
       <c r="R57" t="n">
-        <v>7294673</v>
+        <v>7294468</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116310</v>
+        <v>128116305</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708426</v>
+        <v>708209</v>
       </c>
       <c r="R58" t="n">
-        <v>7294468</v>
+        <v>7294140</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,32 +6209,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116305</v>
+        <v>128116277</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708209</v>
+        <v>708269</v>
       </c>
       <c r="R59" t="n">
-        <v>7294140</v>
+        <v>7294506</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6280,6 +6280,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6306,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116243</v>
+        <v>128116292</v>
       </c>
       <c r="B60" t="n">
-        <v>57832</v>
+        <v>91370</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6317,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708329</v>
+        <v>708500</v>
       </c>
       <c r="R60" t="n">
         <v>7294658</v>
@@ -6403,32 +6408,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116277</v>
+        <v>128116261</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708269</v>
+        <v>708394</v>
       </c>
       <c r="R61" t="n">
-        <v>7294506</v>
+        <v>7294544</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6474,11 +6479,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116261</v>
+        <v>128116243</v>
       </c>
       <c r="B62" t="n">
-        <v>97347</v>
+        <v>57832</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708394</v>
+        <v>708329</v>
       </c>
       <c r="R62" t="n">
-        <v>7294544</v>
+        <v>7294658</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116251</v>
+        <v>128116245</v>
       </c>
       <c r="B23" t="n">
-        <v>97347</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708490</v>
+        <v>708491</v>
       </c>
       <c r="R23" t="n">
-        <v>7294651</v>
+        <v>7294463</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116245</v>
+        <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>97347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708491</v>
+        <v>708490</v>
       </c>
       <c r="R27" t="n">
-        <v>7294463</v>
+        <v>7294651</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B28" t="n">
-        <v>91366</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R28" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R29" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R30" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R31" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116272</v>
+        <v>128116311</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>82870</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R48" t="n">
-        <v>7294403</v>
+        <v>7294070</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B49" t="n">
-        <v>82870</v>
+        <v>91926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R49" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116314</v>
+        <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294415</v>
+        <v>7294403</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116240</v>
+        <v>128116292</v>
       </c>
       <c r="B53" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708376</v>
+        <v>708500</v>
       </c>
       <c r="R53" t="n">
-        <v>7294699</v>
+        <v>7294658</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116254</v>
+        <v>128116240</v>
       </c>
       <c r="B54" t="n">
-        <v>80132</v>
+        <v>79647</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708400</v>
+        <v>708376</v>
       </c>
       <c r="R54" t="n">
-        <v>7294674</v>
+        <v>7294699</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116260</v>
+        <v>128116254</v>
       </c>
       <c r="B55" t="n">
         <v>80132</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708208</v>
+        <v>708400</v>
       </c>
       <c r="R55" t="n">
-        <v>7294348</v>
+        <v>7294674</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116256</v>
+        <v>128116260</v>
       </c>
       <c r="B56" t="n">
         <v>80132</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708495</v>
+        <v>708208</v>
       </c>
       <c r="R56" t="n">
-        <v>7294673</v>
+        <v>7294348</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116310</v>
+        <v>128116256</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708426</v>
+        <v>708495</v>
       </c>
       <c r="R57" t="n">
-        <v>7294468</v>
+        <v>7294673</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116305</v>
+        <v>128116310</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708209</v>
+        <v>708426</v>
       </c>
       <c r="R58" t="n">
-        <v>7294140</v>
+        <v>7294468</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,32 +6209,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116277</v>
+        <v>128116305</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708269</v>
+        <v>708209</v>
       </c>
       <c r="R59" t="n">
-        <v>7294506</v>
+        <v>7294140</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6280,11 +6280,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6311,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116292</v>
+        <v>128116243</v>
       </c>
       <c r="B60" t="n">
-        <v>91370</v>
+        <v>57832</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708500</v>
+        <v>708329</v>
       </c>
       <c r="R60" t="n">
         <v>7294658</v>
@@ -6408,32 +6403,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116261</v>
+        <v>128116277</v>
       </c>
       <c r="B61" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708394</v>
+        <v>708269</v>
       </c>
       <c r="R61" t="n">
-        <v>7294544</v>
+        <v>7294506</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6479,6 +6474,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116243</v>
+        <v>128116261</v>
       </c>
       <c r="B62" t="n">
-        <v>57832</v>
+        <v>97347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708329</v>
+        <v>708394</v>
       </c>
       <c r="R62" t="n">
-        <v>7294658</v>
+        <v>7294544</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116306</v>
+        <v>128116246</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708199</v>
+        <v>708396</v>
       </c>
       <c r="R9" t="n">
-        <v>7294151</v>
+        <v>7294100</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116307</v>
+        <v>128116306</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708223</v>
+        <v>708199</v>
       </c>
       <c r="R10" t="n">
-        <v>7294146</v>
+        <v>7294151</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116307</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708223</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294146</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116253</v>
+        <v>128116259</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708194</v>
+        <v>708415</v>
       </c>
       <c r="R18" t="n">
-        <v>7294336</v>
+        <v>7294078</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116259</v>
+        <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708415</v>
+        <v>708194</v>
       </c>
       <c r="R19" t="n">
-        <v>7294078</v>
+        <v>7294336</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R28" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R29" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B30" t="n">
-        <v>91366</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R30" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R31" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116262</v>
+        <v>128116270</v>
       </c>
       <c r="B36" t="n">
-        <v>57776</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708295</v>
+        <v>708197</v>
       </c>
       <c r="R36" t="n">
-        <v>7294459</v>
+        <v>7294331</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116270</v>
+        <v>128116293</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>91370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708197</v>
+        <v>708521</v>
       </c>
       <c r="R37" t="n">
-        <v>7294331</v>
+        <v>7294413</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116293</v>
+        <v>128116308</v>
       </c>
       <c r="B38" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708521</v>
+        <v>708216</v>
       </c>
       <c r="R38" t="n">
-        <v>7294413</v>
+        <v>7294159</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116308</v>
+        <v>128116309</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708216</v>
+        <v>708284</v>
       </c>
       <c r="R39" t="n">
-        <v>7294159</v>
+        <v>7294509</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116309</v>
+        <v>128116299</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708284</v>
+        <v>708462</v>
       </c>
       <c r="R40" t="n">
-        <v>7294509</v>
+        <v>7294126</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116299</v>
+        <v>128116262</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708462</v>
+        <v>708295</v>
       </c>
       <c r="R41" t="n">
-        <v>7294126</v>
+        <v>7294459</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116311</v>
+        <v>128116272</v>
       </c>
       <c r="B48" t="n">
-        <v>82870</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294070</v>
+        <v>7294403</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B49" t="n">
-        <v>91926</v>
+        <v>82870</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R49" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116272</v>
+        <v>128116314</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294403</v>
+        <v>7294415</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116241</v>
+        <v>128116269</v>
       </c>
       <c r="B66" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708398</v>
+        <v>708195</v>
       </c>
       <c r="R66" t="n">
-        <v>7294092</v>
+        <v>7294329</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B67" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R67" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R68" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116266</v>
+        <v>128116241</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>56864</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708534</v>
+        <v>708398</v>
       </c>
       <c r="R69" t="n">
-        <v>7294561</v>
+        <v>7294092</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116246</v>
+        <v>128116306</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708396</v>
+        <v>708199</v>
       </c>
       <c r="R9" t="n">
-        <v>7294100</v>
+        <v>7294151</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116306</v>
+        <v>128116307</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708199</v>
+        <v>708223</v>
       </c>
       <c r="R10" t="n">
-        <v>7294151</v>
+        <v>7294146</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116307</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708223</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294146</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116259</v>
+        <v>128116253</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708415</v>
+        <v>708194</v>
       </c>
       <c r="R18" t="n">
-        <v>7294078</v>
+        <v>7294336</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116253</v>
+        <v>128116259</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708194</v>
+        <v>708415</v>
       </c>
       <c r="R19" t="n">
-        <v>7294336</v>
+        <v>7294078</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116245</v>
+        <v>128116251</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>97347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708491</v>
+        <v>708490</v>
       </c>
       <c r="R23" t="n">
-        <v>7294463</v>
+        <v>7294651</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116251</v>
+        <v>128116245</v>
       </c>
       <c r="B27" t="n">
-        <v>97347</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708490</v>
+        <v>708491</v>
       </c>
       <c r="R27" t="n">
-        <v>7294651</v>
+        <v>7294463</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B28" t="n">
-        <v>91366</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R28" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R29" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R30" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R31" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B33" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R33" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,11 +3753,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3881,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R35" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116270</v>
+        <v>128116262</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>57776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708197</v>
+        <v>708295</v>
       </c>
       <c r="R36" t="n">
-        <v>7294331</v>
+        <v>7294459</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116293</v>
+        <v>128116270</v>
       </c>
       <c r="B37" t="n">
-        <v>91370</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708521</v>
+        <v>708197</v>
       </c>
       <c r="R37" t="n">
-        <v>7294413</v>
+        <v>7294331</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116308</v>
+        <v>128116293</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708216</v>
+        <v>708521</v>
       </c>
       <c r="R38" t="n">
-        <v>7294159</v>
+        <v>7294413</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116309</v>
+        <v>128116308</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708284</v>
+        <v>708216</v>
       </c>
       <c r="R39" t="n">
-        <v>7294509</v>
+        <v>7294159</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116299</v>
+        <v>128116309</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708462</v>
+        <v>708284</v>
       </c>
       <c r="R40" t="n">
-        <v>7294126</v>
+        <v>7294509</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116262</v>
+        <v>128116299</v>
       </c>
       <c r="B41" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708295</v>
+        <v>708462</v>
       </c>
       <c r="R41" t="n">
-        <v>7294459</v>
+        <v>7294126</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116269</v>
+        <v>128116241</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>56864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708195</v>
+        <v>708398</v>
       </c>
       <c r="R66" t="n">
-        <v>7294329</v>
+        <v>7294092</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116266</v>
+        <v>128116242</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708534</v>
+        <v>708298</v>
       </c>
       <c r="R67" t="n">
-        <v>7294561</v>
+        <v>7294185</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116242</v>
+        <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708298</v>
+        <v>708195</v>
       </c>
       <c r="R68" t="n">
-        <v>7294185</v>
+        <v>7294329</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116241</v>
+        <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708398</v>
+        <v>708534</v>
       </c>
       <c r="R69" t="n">
-        <v>7294092</v>
+        <v>7294561</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128116278</v>
+        <v>128116247</v>
       </c>
       <c r="B5" t="n">
-        <v>79108</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708407</v>
+        <v>708354</v>
       </c>
       <c r="R5" t="n">
-        <v>7294657</v>
+        <v>7294074</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128116283</v>
+        <v>128116278</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>79108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708522</v>
+        <v>708407</v>
       </c>
       <c r="R6" t="n">
-        <v>7294412</v>
+        <v>7294657</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128116247</v>
+        <v>128116283</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708354</v>
+        <v>708522</v>
       </c>
       <c r="R7" t="n">
-        <v>7294074</v>
+        <v>7294412</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116306</v>
+        <v>128116246</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708199</v>
+        <v>708396</v>
       </c>
       <c r="R9" t="n">
-        <v>7294151</v>
+        <v>7294100</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116307</v>
+        <v>128116306</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708223</v>
+        <v>708199</v>
       </c>
       <c r="R10" t="n">
-        <v>7294146</v>
+        <v>7294151</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116307</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708223</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294146</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>91366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R28" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R29" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B30" t="n">
-        <v>91366</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R30" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R31" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116292</v>
+        <v>128116240</v>
       </c>
       <c r="B53" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708500</v>
+        <v>708376</v>
       </c>
       <c r="R53" t="n">
-        <v>7294658</v>
+        <v>7294699</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116240</v>
+        <v>128116254</v>
       </c>
       <c r="B54" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708376</v>
+        <v>708400</v>
       </c>
       <c r="R54" t="n">
-        <v>7294699</v>
+        <v>7294674</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116254</v>
+        <v>128116260</v>
       </c>
       <c r="B55" t="n">
         <v>80132</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708400</v>
+        <v>708208</v>
       </c>
       <c r="R55" t="n">
-        <v>7294674</v>
+        <v>7294348</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116260</v>
+        <v>128116256</v>
       </c>
       <c r="B56" t="n">
         <v>80132</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708208</v>
+        <v>708495</v>
       </c>
       <c r="R56" t="n">
-        <v>7294348</v>
+        <v>7294673</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116256</v>
+        <v>128116310</v>
       </c>
       <c r="B57" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708495</v>
+        <v>708426</v>
       </c>
       <c r="R57" t="n">
-        <v>7294673</v>
+        <v>7294468</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116310</v>
+        <v>128116305</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708426</v>
+        <v>708209</v>
       </c>
       <c r="R58" t="n">
-        <v>7294468</v>
+        <v>7294140</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,32 +6209,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116305</v>
+        <v>128116277</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708209</v>
+        <v>708269</v>
       </c>
       <c r="R59" t="n">
-        <v>7294140</v>
+        <v>7294506</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6280,6 +6280,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6306,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116243</v>
+        <v>128116292</v>
       </c>
       <c r="B60" t="n">
-        <v>57832</v>
+        <v>91370</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6317,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708329</v>
+        <v>708500</v>
       </c>
       <c r="R60" t="n">
         <v>7294658</v>
@@ -6403,32 +6408,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116277</v>
+        <v>128116261</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708269</v>
+        <v>708394</v>
       </c>
       <c r="R61" t="n">
-        <v>7294506</v>
+        <v>7294544</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6474,11 +6479,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116261</v>
+        <v>128116243</v>
       </c>
       <c r="B62" t="n">
-        <v>97347</v>
+        <v>57832</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708394</v>
+        <v>708329</v>
       </c>
       <c r="R62" t="n">
-        <v>7294544</v>
+        <v>7294658</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116251</v>
+        <v>128116245</v>
       </c>
       <c r="B23" t="n">
-        <v>97347</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708490</v>
+        <v>708491</v>
       </c>
       <c r="R23" t="n">
-        <v>7294651</v>
+        <v>7294463</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116245</v>
+        <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>97347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708491</v>
+        <v>708490</v>
       </c>
       <c r="R27" t="n">
-        <v>7294463</v>
+        <v>7294651</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R33" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,6 +3753,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R35" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116272</v>
+        <v>128116311</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>82870</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R48" t="n">
-        <v>7294403</v>
+        <v>7294070</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B49" t="n">
-        <v>82870</v>
+        <v>91926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R49" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116314</v>
+        <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294415</v>
+        <v>7294403</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128116295</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128116294</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128116297</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128116247</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128116278</v>
       </c>
       <c r="B6" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128116283</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128116290</v>
       </c>
       <c r="B8" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116246</v>
+        <v>128116306</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708396</v>
+        <v>708199</v>
       </c>
       <c r="R9" t="n">
-        <v>7294100</v>
+        <v>7294151</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116306</v>
+        <v>128116307</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708199</v>
+        <v>708223</v>
       </c>
       <c r="R10" t="n">
-        <v>7294151</v>
+        <v>7294146</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116307</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708223</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294146</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1648,7 +1648,7 @@
         <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116286</v>
+        <v>128116304</v>
       </c>
       <c r="B13" t="n">
-        <v>91366</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708482</v>
+        <v>708225</v>
       </c>
       <c r="R13" t="n">
-        <v>7294632</v>
+        <v>7294108</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1842,7 +1842,7 @@
         <v>128116258</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116304</v>
+        <v>128116286</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>91374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708225</v>
+        <v>708482</v>
       </c>
       <c r="R15" t="n">
-        <v>7294108</v>
+        <v>7294632</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2036,7 +2036,7 @@
         <v>128116249</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116312</v>
+        <v>128116281</v>
       </c>
       <c r="B17" t="n">
-        <v>82870</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708202</v>
+        <v>708480</v>
       </c>
       <c r="R17" t="n">
-        <v>7294136</v>
+        <v>7294127</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116253</v>
+        <v>128116312</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>82873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708194</v>
+        <v>708202</v>
       </c>
       <c r="R18" t="n">
-        <v>7294336</v>
+        <v>7294136</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116259</v>
+        <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>92843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708415</v>
+        <v>708194</v>
       </c>
       <c r="R19" t="n">
-        <v>7294078</v>
+        <v>7294336</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116281</v>
+        <v>128116259</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708480</v>
+        <v>708415</v>
       </c>
       <c r="R20" t="n">
-        <v>7294127</v>
+        <v>7294078</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2521,7 +2521,7 @@
         <v>128116302</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128116298</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116245</v>
+        <v>128116315</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>91934</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708491</v>
+        <v>708330</v>
       </c>
       <c r="R23" t="n">
-        <v>7294463</v>
+        <v>7294664</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116315</v>
+        <v>128116285</v>
       </c>
       <c r="B24" t="n">
-        <v>91926</v>
+        <v>91356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708330</v>
+        <v>708246</v>
       </c>
       <c r="R24" t="n">
-        <v>7294664</v>
+        <v>7294412</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116285</v>
+        <v>128116279</v>
       </c>
       <c r="B25" t="n">
-        <v>91348</v>
+        <v>79111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708246</v>
+        <v>708215</v>
       </c>
       <c r="R25" t="n">
-        <v>7294412</v>
+        <v>7294156</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116279</v>
+        <v>128116245</v>
       </c>
       <c r="B26" t="n">
-        <v>79108</v>
+        <v>57670</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708215</v>
+        <v>708491</v>
       </c>
       <c r="R26" t="n">
-        <v>7294156</v>
+        <v>7294463</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3103,7 +3103,7 @@
         <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116289</v>
+        <v>128116255</v>
       </c>
       <c r="B28" t="n">
-        <v>91366</v>
+        <v>80135</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708501</v>
+        <v>708407</v>
       </c>
       <c r="R28" t="n">
-        <v>7294429</v>
+        <v>7294680</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116255</v>
+        <v>128116248</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>57670</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708407</v>
+        <v>708292</v>
       </c>
       <c r="R29" t="n">
-        <v>7294680</v>
+        <v>7294045</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>91374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R30" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3491,7 +3491,7 @@
         <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>128116300</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B33" t="n">
-        <v>91926</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R33" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,11 +3753,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3787,7 +3782,7 @@
         <v>128116301</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>91934</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R35" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116262</v>
+        <v>128116293</v>
       </c>
       <c r="B36" t="n">
-        <v>57776</v>
+        <v>91378</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708295</v>
+        <v>708521</v>
       </c>
       <c r="R36" t="n">
-        <v>7294459</v>
+        <v>7294413</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116270</v>
+        <v>128116308</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708197</v>
+        <v>708216</v>
       </c>
       <c r="R37" t="n">
-        <v>7294331</v>
+        <v>7294159</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116293</v>
+        <v>128116309</v>
       </c>
       <c r="B38" t="n">
-        <v>91370</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708521</v>
+        <v>708284</v>
       </c>
       <c r="R38" t="n">
-        <v>7294413</v>
+        <v>7294509</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116308</v>
+        <v>128116299</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708216</v>
+        <v>708462</v>
       </c>
       <c r="R39" t="n">
-        <v>7294159</v>
+        <v>7294126</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116309</v>
+        <v>128116262</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708284</v>
+        <v>708295</v>
       </c>
       <c r="R40" t="n">
-        <v>7294509</v>
+        <v>7294459</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116299</v>
+        <v>128116270</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708462</v>
+        <v>708197</v>
       </c>
       <c r="R41" t="n">
-        <v>7294126</v>
+        <v>7294331</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116265</v>
+        <v>128116239</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>91325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708523</v>
+        <v>708194</v>
       </c>
       <c r="R42" t="n">
-        <v>7294599</v>
+        <v>7294336</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116252</v>
+        <v>128116303</v>
       </c>
       <c r="B43" t="n">
-        <v>97347</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708525</v>
+        <v>708288</v>
       </c>
       <c r="R43" t="n">
-        <v>7294394</v>
+        <v>7294045</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B44" t="n">
-        <v>91317</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R44" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116303</v>
+        <v>128116252</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>97355</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708288</v>
+        <v>708525</v>
       </c>
       <c r="R45" t="n">
-        <v>7294045</v>
+        <v>7294394</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128116296</v>
+        <v>128116288</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>91374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708450</v>
+        <v>708485</v>
       </c>
       <c r="R46" t="n">
-        <v>7294389</v>
+        <v>7294476</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128116288</v>
+        <v>128116296</v>
       </c>
       <c r="B47" t="n">
-        <v>91366</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708485</v>
+        <v>708450</v>
       </c>
       <c r="R47" t="n">
-        <v>7294476</v>
+        <v>7294389</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5145,7 +5145,7 @@
         <v>128116311</v>
       </c>
       <c r="B48" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128116314</v>
       </c>
       <c r="B49" t="n">
-        <v>91926</v>
+        <v>91934</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116240</v>
+        <v>128116292</v>
       </c>
       <c r="B53" t="n">
-        <v>79647</v>
+        <v>91378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708376</v>
+        <v>708500</v>
       </c>
       <c r="R53" t="n">
-        <v>7294699</v>
+        <v>7294658</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116254</v>
+        <v>128116261</v>
       </c>
       <c r="B54" t="n">
-        <v>80132</v>
+        <v>97355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708400</v>
+        <v>708394</v>
       </c>
       <c r="R54" t="n">
-        <v>7294674</v>
+        <v>7294544</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116260</v>
+        <v>128116277</v>
       </c>
       <c r="B55" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708208</v>
+        <v>708269</v>
       </c>
       <c r="R55" t="n">
-        <v>7294348</v>
+        <v>7294506</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5892,6 +5892,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5918,10 +5923,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116256</v>
+        <v>128116240</v>
       </c>
       <c r="B56" t="n">
-        <v>80132</v>
+        <v>79650</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5934,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708495</v>
+        <v>708376</v>
       </c>
       <c r="R56" t="n">
-        <v>7294673</v>
+        <v>7294699</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6018,7 +6023,7 @@
         <v>128116310</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6112,10 +6117,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116305</v>
+        <v>128116254</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6123,21 +6128,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708209</v>
+        <v>708400</v>
       </c>
       <c r="R58" t="n">
-        <v>7294140</v>
+        <v>7294674</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,32 +6214,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116277</v>
+        <v>128116260</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6249,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708269</v>
+        <v>708208</v>
       </c>
       <c r="R59" t="n">
-        <v>7294506</v>
+        <v>7294348</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6280,11 +6285,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6311,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116292</v>
+        <v>128116305</v>
       </c>
       <c r="B60" t="n">
-        <v>91370</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708500</v>
+        <v>708209</v>
       </c>
       <c r="R60" t="n">
-        <v>7294658</v>
+        <v>7294140</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6408,32 +6408,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116261</v>
+        <v>128116256</v>
       </c>
       <c r="B61" t="n">
-        <v>97347</v>
+        <v>80135</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708394</v>
+        <v>708495</v>
       </c>
       <c r="R61" t="n">
-        <v>7294544</v>
+        <v>7294673</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6508,7 +6508,7 @@
         <v>128116243</v>
       </c>
       <c r="B62" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6699,32 +6699,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128116276</v>
+        <v>128116287</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>91374</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708267</v>
+        <v>708515</v>
       </c>
       <c r="R64" t="n">
-        <v>7294433</v>
+        <v>7294574</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -6796,32 +6796,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128116287</v>
+        <v>128116276</v>
       </c>
       <c r="B65" t="n">
-        <v>91366</v>
+        <v>98478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708515</v>
+        <v>708267</v>
       </c>
       <c r="R65" t="n">
-        <v>7294574</v>
+        <v>7294433</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -6993,7 +6993,7 @@
         <v>128116242</v>
       </c>
       <c r="B67" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128116247</v>
+        <v>128116278</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708354</v>
+        <v>708407</v>
       </c>
       <c r="R5" t="n">
-        <v>7294074</v>
+        <v>7294657</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128116278</v>
+        <v>128116283</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708407</v>
+        <v>708522</v>
       </c>
       <c r="R6" t="n">
-        <v>7294657</v>
+        <v>7294412</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128116283</v>
+        <v>128116247</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708522</v>
+        <v>708354</v>
       </c>
       <c r="R7" t="n">
-        <v>7294412</v>
+        <v>7294074</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116264</v>
+        <v>128116301</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708489</v>
+        <v>708375</v>
       </c>
       <c r="R33" t="n">
-        <v>7294661</v>
+        <v>7294094</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116301</v>
+        <v>128116313</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>91934</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708375</v>
+        <v>708432</v>
       </c>
       <c r="R34" t="n">
-        <v>7294094</v>
+        <v>7294694</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3850,6 +3850,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>91934</v>
+        <v>98478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R35" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B42" t="n">
-        <v>91325</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R42" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R43" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116265</v>
+        <v>128116303</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708523</v>
+        <v>708288</v>
       </c>
       <c r="R44" t="n">
-        <v>7294599</v>
+        <v>7294045</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116292</v>
+        <v>128116277</v>
       </c>
       <c r="B53" t="n">
-        <v>91378</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708500</v>
+        <v>708269</v>
       </c>
       <c r="R53" t="n">
-        <v>7294658</v>
+        <v>7294506</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5698,6 +5698,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5821,32 +5826,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116277</v>
+        <v>128116260</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708269</v>
+        <v>708208</v>
       </c>
       <c r="R55" t="n">
-        <v>7294506</v>
+        <v>7294348</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5892,11 +5897,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5923,10 +5923,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116240</v>
+        <v>128116305</v>
       </c>
       <c r="B56" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5934,21 +5934,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708376</v>
+        <v>708209</v>
       </c>
       <c r="R56" t="n">
-        <v>7294699</v>
+        <v>7294140</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116310</v>
+        <v>128116292</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>91378</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6031,21 +6031,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708426</v>
+        <v>708500</v>
       </c>
       <c r="R57" t="n">
-        <v>7294468</v>
+        <v>7294658</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116254</v>
+        <v>128116240</v>
       </c>
       <c r="B58" t="n">
-        <v>80135</v>
+        <v>79650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6128,21 +6128,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708400</v>
+        <v>708376</v>
       </c>
       <c r="R58" t="n">
-        <v>7294674</v>
+        <v>7294699</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6214,10 +6214,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116260</v>
+        <v>128116310</v>
       </c>
       <c r="B59" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708208</v>
+        <v>708426</v>
       </c>
       <c r="R59" t="n">
-        <v>7294348</v>
+        <v>7294468</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116305</v>
+        <v>128116254</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708209</v>
+        <v>708400</v>
       </c>
       <c r="R60" t="n">
-        <v>7294140</v>
+        <v>7294674</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128116295</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128116294</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128116297</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128116278</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128116283</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128116247</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116290</v>
+        <v>128116246</v>
       </c>
       <c r="B8" t="n">
-        <v>91374</v>
+        <v>57682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708225</v>
+        <v>708396</v>
       </c>
       <c r="R8" t="n">
-        <v>7294123</v>
+        <v>7294100</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1357,7 +1357,7 @@
         <v>128116306</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128116307</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116290</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>91466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708225</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294123</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1648,7 +1648,7 @@
         <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116304</v>
+        <v>128116258</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708225</v>
+        <v>708471</v>
       </c>
       <c r="R13" t="n">
-        <v>7294108</v>
+        <v>7294139</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116258</v>
+        <v>128116249</v>
       </c>
       <c r="B14" t="n">
-        <v>80135</v>
+        <v>57682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708471</v>
+        <v>708207</v>
       </c>
       <c r="R14" t="n">
-        <v>7294139</v>
+        <v>7294133</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116286</v>
+        <v>128116304</v>
       </c>
       <c r="B15" t="n">
-        <v>91374</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708482</v>
+        <v>708225</v>
       </c>
       <c r="R15" t="n">
-        <v>7294632</v>
+        <v>7294108</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116249</v>
+        <v>128116286</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>91466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708207</v>
+        <v>708482</v>
       </c>
       <c r="R16" t="n">
-        <v>7294133</v>
+        <v>7294632</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116281</v>
+        <v>128116312</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>82942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708480</v>
+        <v>708202</v>
       </c>
       <c r="R17" t="n">
-        <v>7294127</v>
+        <v>7294136</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116312</v>
+        <v>128116281</v>
       </c>
       <c r="B18" t="n">
-        <v>82873</v>
+        <v>56867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708202</v>
+        <v>708480</v>
       </c>
       <c r="R18" t="n">
-        <v>7294136</v>
+        <v>7294127</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2327,7 +2327,7 @@
         <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128116259</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128116302</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128116298</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116315</v>
+        <v>128116251</v>
       </c>
       <c r="B23" t="n">
-        <v>91934</v>
+        <v>97448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708330</v>
+        <v>708490</v>
       </c>
       <c r="R23" t="n">
-        <v>7294664</v>
+        <v>7294651</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
         <v>128116285</v>
       </c>
       <c r="B24" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128116279</v>
       </c>
       <c r="B25" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116245</v>
+        <v>128116315</v>
       </c>
       <c r="B26" t="n">
-        <v>57670</v>
+        <v>92026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708491</v>
+        <v>708330</v>
       </c>
       <c r="R26" t="n">
-        <v>7294463</v>
+        <v>7294664</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116251</v>
+        <v>128116245</v>
       </c>
       <c r="B27" t="n">
-        <v>97355</v>
+        <v>57682</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708490</v>
+        <v>708491</v>
       </c>
       <c r="R27" t="n">
-        <v>7294651</v>
+        <v>7294463</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116255</v>
+        <v>128116248</v>
       </c>
       <c r="B28" t="n">
-        <v>80135</v>
+        <v>57682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708407</v>
+        <v>708292</v>
       </c>
       <c r="R28" t="n">
-        <v>7294680</v>
+        <v>7294045</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116248</v>
+        <v>128116289</v>
       </c>
       <c r="B29" t="n">
-        <v>57670</v>
+        <v>91466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708292</v>
+        <v>708501</v>
       </c>
       <c r="R29" t="n">
-        <v>7294045</v>
+        <v>7294429</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116289</v>
+        <v>128116255</v>
       </c>
       <c r="B30" t="n">
-        <v>91374</v>
+        <v>80188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708501</v>
+        <v>708407</v>
       </c>
       <c r="R30" t="n">
-        <v>7294429</v>
+        <v>7294680</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3491,7 +3491,7 @@
         <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>128116300</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116301</v>
+        <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>92026</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708375</v>
+        <v>708432</v>
       </c>
       <c r="R33" t="n">
-        <v>7294094</v>
+        <v>7294694</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,6 +3753,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3779,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116313</v>
+        <v>128116301</v>
       </c>
       <c r="B34" t="n">
-        <v>91934</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708432</v>
+        <v>708375</v>
       </c>
       <c r="R34" t="n">
-        <v>7294694</v>
+        <v>7294094</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3850,11 +3855,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3884,7 +3884,7 @@
         <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116293</v>
+        <v>128116262</v>
       </c>
       <c r="B36" t="n">
-        <v>91378</v>
+        <v>57789</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708521</v>
+        <v>708295</v>
       </c>
       <c r="R36" t="n">
-        <v>7294413</v>
+        <v>7294459</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116308</v>
+        <v>128116270</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708216</v>
+        <v>708197</v>
       </c>
       <c r="R37" t="n">
-        <v>7294159</v>
+        <v>7294331</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116309</v>
+        <v>128116308</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708284</v>
+        <v>708216</v>
       </c>
       <c r="R38" t="n">
-        <v>7294509</v>
+        <v>7294159</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116299</v>
+        <v>128116293</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708462</v>
+        <v>708521</v>
       </c>
       <c r="R39" t="n">
-        <v>7294126</v>
+        <v>7294413</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116262</v>
+        <v>128116309</v>
       </c>
       <c r="B40" t="n">
-        <v>57777</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708295</v>
+        <v>708284</v>
       </c>
       <c r="R40" t="n">
-        <v>7294459</v>
+        <v>7294509</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116270</v>
+        <v>128116299</v>
       </c>
       <c r="B41" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708197</v>
+        <v>708462</v>
       </c>
       <c r="R41" t="n">
-        <v>7294331</v>
+        <v>7294126</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116265</v>
+        <v>128116303</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708523</v>
+        <v>708288</v>
       </c>
       <c r="R42" t="n">
-        <v>7294599</v>
+        <v>7294045</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4660,7 +4660,7 @@
         <v>128116239</v>
       </c>
       <c r="B43" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116303</v>
+        <v>128116265</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708288</v>
+        <v>708523</v>
       </c>
       <c r="R44" t="n">
-        <v>7294045</v>
+        <v>7294599</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4854,7 +4854,7 @@
         <v>128116252</v>
       </c>
       <c r="B45" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>128116288</v>
       </c>
       <c r="B46" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>128116296</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B48" t="n">
-        <v>82873</v>
+        <v>92026</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B49" t="n">
-        <v>91934</v>
+        <v>82942</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R49" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5339,7 +5339,7 @@
         <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116277</v>
+        <v>128116254</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708269</v>
+        <v>708400</v>
       </c>
       <c r="R53" t="n">
-        <v>7294506</v>
+        <v>7294674</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5698,11 +5698,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5729,32 +5724,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116261</v>
+        <v>128116260</v>
       </c>
       <c r="B54" t="n">
-        <v>97355</v>
+        <v>80188</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5764,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708394</v>
+        <v>708208</v>
       </c>
       <c r="R54" t="n">
-        <v>7294544</v>
+        <v>7294348</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5826,10 +5821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116260</v>
+        <v>128116256</v>
       </c>
       <c r="B55" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5861,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708208</v>
+        <v>708495</v>
       </c>
       <c r="R55" t="n">
-        <v>7294348</v>
+        <v>7294673</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5923,10 +5918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116305</v>
+        <v>128116240</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5934,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708209</v>
+        <v>708376</v>
       </c>
       <c r="R56" t="n">
-        <v>7294140</v>
+        <v>7294699</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6020,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116292</v>
+        <v>128116310</v>
       </c>
       <c r="B57" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6031,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6055,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708500</v>
+        <v>708426</v>
       </c>
       <c r="R57" t="n">
-        <v>7294658</v>
+        <v>7294468</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6117,10 +6112,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116240</v>
+        <v>128116305</v>
       </c>
       <c r="B58" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6128,21 +6123,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708376</v>
+        <v>708209</v>
       </c>
       <c r="R58" t="n">
-        <v>7294699</v>
+        <v>7294140</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6214,10 +6209,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116310</v>
+        <v>128116292</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6225,21 +6220,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6249,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708426</v>
+        <v>708500</v>
       </c>
       <c r="R59" t="n">
-        <v>7294468</v>
+        <v>7294658</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6311,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116254</v>
+        <v>128116243</v>
       </c>
       <c r="B60" t="n">
-        <v>80135</v>
+        <v>57845</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708400</v>
+        <v>708329</v>
       </c>
       <c r="R60" t="n">
-        <v>7294674</v>
+        <v>7294658</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6408,32 +6403,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116256</v>
+        <v>128116261</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>97448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708495</v>
+        <v>708394</v>
       </c>
       <c r="R61" t="n">
-        <v>7294673</v>
+        <v>7294544</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6505,32 +6500,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116243</v>
+        <v>128116277</v>
       </c>
       <c r="B62" t="n">
-        <v>57833</v>
+        <v>98571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6535,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708329</v>
+        <v>708269</v>
       </c>
       <c r="R62" t="n">
-        <v>7294658</v>
+        <v>7294506</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6576,6 +6571,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>128116287</v>
       </c>
       <c r="B64" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>128116276</v>
       </c>
       <c r="B65" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>128116241</v>
       </c>
       <c r="B66" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>128116242</v>
       </c>
       <c r="B67" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116246</v>
+        <v>128116290</v>
       </c>
       <c r="B8" t="n">
-        <v>57682</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708396</v>
+        <v>708225</v>
       </c>
       <c r="R8" t="n">
-        <v>7294100</v>
+        <v>7294123</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116290</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>91466</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708225</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294123</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116258</v>
+        <v>128116286</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>91466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708471</v>
+        <v>708482</v>
       </c>
       <c r="R13" t="n">
-        <v>7294139</v>
+        <v>7294632</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116249</v>
+        <v>128116258</v>
       </c>
       <c r="B14" t="n">
-        <v>57682</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708207</v>
+        <v>708471</v>
       </c>
       <c r="R14" t="n">
-        <v>7294133</v>
+        <v>7294139</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116286</v>
+        <v>128116249</v>
       </c>
       <c r="B16" t="n">
-        <v>91466</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708482</v>
+        <v>708207</v>
       </c>
       <c r="R16" t="n">
-        <v>7294632</v>
+        <v>7294133</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116281</v>
+        <v>128116253</v>
       </c>
       <c r="B18" t="n">
-        <v>56867</v>
+        <v>92935</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708480</v>
+        <v>708194</v>
       </c>
       <c r="R18" t="n">
-        <v>7294127</v>
+        <v>7294336</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116253</v>
+        <v>128116259</v>
       </c>
       <c r="B19" t="n">
-        <v>92935</v>
+        <v>80188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708194</v>
+        <v>708415</v>
       </c>
       <c r="R19" t="n">
-        <v>7294336</v>
+        <v>7294078</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B20" t="n">
-        <v>80188</v>
+        <v>56867</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R20" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116285</v>
+        <v>128116315</v>
       </c>
       <c r="B24" t="n">
-        <v>91448</v>
+        <v>92026</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708246</v>
+        <v>708330</v>
       </c>
       <c r="R24" t="n">
-        <v>7294412</v>
+        <v>7294664</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116279</v>
+        <v>128116285</v>
       </c>
       <c r="B25" t="n">
-        <v>79162</v>
+        <v>91448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708215</v>
+        <v>708246</v>
       </c>
       <c r="R25" t="n">
-        <v>7294156</v>
+        <v>7294412</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116315</v>
+        <v>128116279</v>
       </c>
       <c r="B26" t="n">
-        <v>92026</v>
+        <v>79162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708330</v>
+        <v>708215</v>
       </c>
       <c r="R26" t="n">
-        <v>7294664</v>
+        <v>7294156</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116289</v>
+        <v>128116274</v>
       </c>
       <c r="B29" t="n">
-        <v>91466</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708501</v>
+        <v>708243</v>
       </c>
       <c r="R29" t="n">
-        <v>7294429</v>
+        <v>7294417</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116274</v>
+        <v>128116289</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>91466</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708243</v>
+        <v>708501</v>
       </c>
       <c r="R31" t="n">
-        <v>7294417</v>
+        <v>7294429</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116262</v>
+        <v>128116293</v>
       </c>
       <c r="B36" t="n">
-        <v>57789</v>
+        <v>91470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708295</v>
+        <v>708521</v>
       </c>
       <c r="R36" t="n">
-        <v>7294459</v>
+        <v>7294413</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116270</v>
+        <v>128116299</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708197</v>
+        <v>708462</v>
       </c>
       <c r="R37" t="n">
-        <v>7294331</v>
+        <v>7294126</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116308</v>
+        <v>128116309</v>
       </c>
       <c r="B38" t="n">
         <v>79083</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708216</v>
+        <v>708284</v>
       </c>
       <c r="R38" t="n">
-        <v>7294159</v>
+        <v>7294509</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116293</v>
+        <v>128116308</v>
       </c>
       <c r="B39" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708521</v>
+        <v>708216</v>
       </c>
       <c r="R39" t="n">
-        <v>7294413</v>
+        <v>7294159</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116309</v>
+        <v>128116262</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>57789</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708284</v>
+        <v>708295</v>
       </c>
       <c r="R40" t="n">
-        <v>7294509</v>
+        <v>7294459</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116299</v>
+        <v>128116270</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708462</v>
+        <v>708197</v>
       </c>
       <c r="R41" t="n">
-        <v>7294126</v>
+        <v>7294331</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116303</v>
+        <v>128116252</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708288</v>
+        <v>708525</v>
       </c>
       <c r="R42" t="n">
-        <v>7294045</v>
+        <v>7294394</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B43" t="n">
-        <v>91417</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R43" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116265</v>
+        <v>128116239</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>91417</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708523</v>
+        <v>708194</v>
       </c>
       <c r="R44" t="n">
-        <v>7294599</v>
+        <v>7294336</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116252</v>
+        <v>128116303</v>
       </c>
       <c r="B45" t="n">
-        <v>97448</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708525</v>
+        <v>708288</v>
       </c>
       <c r="R45" t="n">
-        <v>7294394</v>
+        <v>7294045</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116311</v>
+        <v>128116272</v>
       </c>
       <c r="B49" t="n">
-        <v>82942</v>
+        <v>98571</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R49" t="n">
-        <v>7294070</v>
+        <v>7294403</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,32 +5336,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116272</v>
+        <v>128116311</v>
       </c>
       <c r="B50" t="n">
-        <v>98571</v>
+        <v>82942</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R50" t="n">
-        <v>7294403</v>
+        <v>7294070</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116254</v>
+        <v>128116243</v>
       </c>
       <c r="B53" t="n">
-        <v>80188</v>
+        <v>57845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708400</v>
+        <v>708329</v>
       </c>
       <c r="R53" t="n">
-        <v>7294674</v>
+        <v>7294658</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116260</v>
+        <v>128116292</v>
       </c>
       <c r="B54" t="n">
-        <v>80188</v>
+        <v>91470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708208</v>
+        <v>708500</v>
       </c>
       <c r="R54" t="n">
-        <v>7294348</v>
+        <v>7294658</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116256</v>
+        <v>128116240</v>
       </c>
       <c r="B55" t="n">
-        <v>80188</v>
+        <v>79702</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708495</v>
+        <v>708376</v>
       </c>
       <c r="R55" t="n">
-        <v>7294673</v>
+        <v>7294699</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116240</v>
+        <v>128116254</v>
       </c>
       <c r="B56" t="n">
-        <v>79702</v>
+        <v>80188</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708376</v>
+        <v>708400</v>
       </c>
       <c r="R56" t="n">
-        <v>7294699</v>
+        <v>7294674</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116310</v>
+        <v>128116305</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708426</v>
+        <v>708209</v>
       </c>
       <c r="R57" t="n">
-        <v>7294468</v>
+        <v>7294140</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,10 +6112,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116305</v>
+        <v>128116256</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6123,21 +6123,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708209</v>
+        <v>708495</v>
       </c>
       <c r="R58" t="n">
-        <v>7294140</v>
+        <v>7294673</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,10 +6209,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116292</v>
+        <v>128116310</v>
       </c>
       <c r="B59" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708500</v>
+        <v>708426</v>
       </c>
       <c r="R59" t="n">
-        <v>7294658</v>
+        <v>7294468</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6306,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116243</v>
+        <v>128116260</v>
       </c>
       <c r="B60" t="n">
-        <v>57845</v>
+        <v>80188</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708329</v>
+        <v>708208</v>
       </c>
       <c r="R60" t="n">
-        <v>7294658</v>
+        <v>7294348</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116241</v>
+        <v>128116269</v>
       </c>
       <c r="B66" t="n">
-        <v>56876</v>
+        <v>98571</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708398</v>
+        <v>708195</v>
       </c>
       <c r="R66" t="n">
-        <v>7294092</v>
+        <v>7294329</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B67" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R67" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B68" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R68" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116266</v>
+        <v>128116241</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>56876</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708534</v>
+        <v>708398</v>
       </c>
       <c r="R69" t="n">
-        <v>7294561</v>
+        <v>7294092</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7278,6 +7278,6729 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128118838</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>708431</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7294677</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128118833</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>185</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>708245</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7294232</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128118834</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>708433</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7294555</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128118840</v>
+      </c>
+      <c r="B73" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>708415</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7294056</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128118856</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>708459</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7294618</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128118893</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>708463</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7294191</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128118837</v>
+      </c>
+      <c r="B76" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>708415</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7294151</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>3st honor</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128118881</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>708273</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7294469</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128118863</v>
+      </c>
+      <c r="B78" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>708340</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7294657</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128118867</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>708482</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7294514</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128118866</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>708412</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7294653</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128118848</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>708237</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7294377</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128118900</v>
+      </c>
+      <c r="B82" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>708422</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7294064</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128118901</v>
+      </c>
+      <c r="B83" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>708358</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7294071</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128118844</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>708472</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7294621</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128118851</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>708470</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7294185</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128118873</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>708238</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7294359</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128118877</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>708246</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7294419</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128118876</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>708233</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7294407</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128118870</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>708407</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7294148</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128118855</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>708232</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7294278</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128118885</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91448</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>708414</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7294147</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128118829</v>
+      </c>
+      <c r="B92" t="n">
+        <v>105594</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>708299</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7294038</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128118854</v>
+      </c>
+      <c r="B93" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>708246</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7294430</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128118868</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>708494</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7294519</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128118884</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>864</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>708477</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7294616</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128118896</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>708411</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7294054</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128118878</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>708258</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7294447</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128118892</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>708476</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7294478</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128118860</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>708188</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7294093</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128118909</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>708416</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7294052</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128118861</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>708259</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7294452</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128118847</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>708461</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7294368</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128118895</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>708412</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7294150</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128118912</v>
+      </c>
+      <c r="B104" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>708262</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7294457</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128118906</v>
+      </c>
+      <c r="B105" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>708432</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7294676</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128118841</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>708337</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7294039</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128118886</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>708480</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7294478</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128118832</v>
+      </c>
+      <c r="B108" t="n">
+        <v>105594</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>708229</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7294386</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128118853</v>
+      </c>
+      <c r="B109" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>708228</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7294377</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128118835</v>
+      </c>
+      <c r="B110" t="n">
+        <v>58544</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>708445</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7294644</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128118872</v>
+      </c>
+      <c r="B111" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>708200</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7294326</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128118874</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>708235</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7294371</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128118888</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>708218</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7294252</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128118843</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>708496</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7294626</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128118879</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>708260</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7294439</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128118875</v>
+      </c>
+      <c r="B116" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>708230</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7294377</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128118836</v>
+      </c>
+      <c r="B117" t="n">
+        <v>58544</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>708203</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7294324</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128118862</v>
+      </c>
+      <c r="B118" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>708424</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7294076</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128118890</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>708232</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7294415</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128118898</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>708249</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7294216</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128118894</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>708443</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7294180</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128118845</v>
+      </c>
+      <c r="B122" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>708477</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7294616</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128118849</v>
+      </c>
+      <c r="B123" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>708250</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7294430</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128118889</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>708192</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7294318</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128118883</v>
+      </c>
+      <c r="B125" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>708436</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7294589</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128118902</v>
+      </c>
+      <c r="B126" t="n">
+        <v>91713</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>65</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>708202</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7294326</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128118882</v>
+      </c>
+      <c r="B127" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>708290</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7294501</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128118839</v>
+      </c>
+      <c r="B128" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>708424</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7294672</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128118899</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>708214</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7294309</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128118887</v>
+      </c>
+      <c r="B130" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>708488</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7294468</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128118846</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>708469</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7294524</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128118880</v>
+      </c>
+      <c r="B132" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>708290</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7294490</v>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128118869</v>
+      </c>
+      <c r="B133" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>708487</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7294472</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128118857</v>
+      </c>
+      <c r="B134" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>708335</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7294032</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128118903</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98488</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>708233</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7294206</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128118908</v>
+      </c>
+      <c r="B136" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>708424</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7294668</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128118831</v>
+      </c>
+      <c r="B137" t="n">
+        <v>105594</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>708226</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128118850</v>
+      </c>
+      <c r="B138" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Guorpaliden nord, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>708256</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7294451</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128116278</v>
+        <v>128116247</v>
       </c>
       <c r="B5" t="n">
-        <v>79162</v>
+        <v>57682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708407</v>
+        <v>708354</v>
       </c>
       <c r="R5" t="n">
-        <v>7294657</v>
+        <v>7294074</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128116283</v>
+        <v>128116278</v>
       </c>
       <c r="B6" t="n">
-        <v>91448</v>
+        <v>79162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708522</v>
+        <v>708407</v>
       </c>
       <c r="R6" t="n">
-        <v>7294412</v>
+        <v>7294657</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128116247</v>
+        <v>128116283</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>91448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708354</v>
+        <v>708522</v>
       </c>
       <c r="R7" t="n">
-        <v>7294074</v>
+        <v>7294412</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116290</v>
+        <v>128116306</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708225</v>
+        <v>708199</v>
       </c>
       <c r="R8" t="n">
-        <v>7294123</v>
+        <v>7294151</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116306</v>
+        <v>128116307</v>
       </c>
       <c r="B9" t="n">
         <v>79083</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708199</v>
+        <v>708223</v>
       </c>
       <c r="R9" t="n">
-        <v>7294151</v>
+        <v>7294146</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116307</v>
+        <v>128116246</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708223</v>
+        <v>708396</v>
       </c>
       <c r="R10" t="n">
-        <v>7294146</v>
+        <v>7294100</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116268</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708226</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294304</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128116268</v>
+        <v>128116290</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>91466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708226</v>
+        <v>708225</v>
       </c>
       <c r="R12" t="n">
-        <v>7294304</v>
+        <v>7294123</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116258</v>
+        <v>128116249</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>57682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708471</v>
+        <v>708207</v>
       </c>
       <c r="R14" t="n">
-        <v>7294139</v>
+        <v>7294133</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116249</v>
+        <v>128116258</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708207</v>
+        <v>708471</v>
       </c>
       <c r="R16" t="n">
-        <v>7294133</v>
+        <v>7294139</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116312</v>
+        <v>128116259</v>
       </c>
       <c r="B17" t="n">
-        <v>82942</v>
+        <v>80188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708202</v>
+        <v>708415</v>
       </c>
       <c r="R17" t="n">
-        <v>7294136</v>
+        <v>7294078</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116253</v>
+        <v>128116312</v>
       </c>
       <c r="B18" t="n">
-        <v>92935</v>
+        <v>82942</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708194</v>
+        <v>708202</v>
       </c>
       <c r="R18" t="n">
-        <v>7294336</v>
+        <v>7294136</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116259</v>
+        <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>80188</v>
+        <v>92935</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708415</v>
+        <v>708194</v>
       </c>
       <c r="R19" t="n">
-        <v>7294078</v>
+        <v>7294336</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116251</v>
+        <v>128116245</v>
       </c>
       <c r="B23" t="n">
-        <v>97448</v>
+        <v>57682</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708490</v>
+        <v>708491</v>
       </c>
       <c r="R23" t="n">
-        <v>7294651</v>
+        <v>7294463</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116315</v>
+        <v>128116279</v>
       </c>
       <c r="B24" t="n">
-        <v>92026</v>
+        <v>79162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708330</v>
+        <v>708215</v>
       </c>
       <c r="R24" t="n">
-        <v>7294664</v>
+        <v>7294156</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116285</v>
+        <v>128116315</v>
       </c>
       <c r="B25" t="n">
-        <v>91448</v>
+        <v>92026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708246</v>
+        <v>708330</v>
       </c>
       <c r="R25" t="n">
-        <v>7294412</v>
+        <v>7294664</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116279</v>
+        <v>128116285</v>
       </c>
       <c r="B26" t="n">
-        <v>79162</v>
+        <v>91448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708215</v>
+        <v>708246</v>
       </c>
       <c r="R26" t="n">
-        <v>7294156</v>
+        <v>7294412</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116245</v>
+        <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>57682</v>
+        <v>97448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708491</v>
+        <v>708490</v>
       </c>
       <c r="R27" t="n">
-        <v>7294463</v>
+        <v>7294651</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116248</v>
+        <v>128116274</v>
       </c>
       <c r="B28" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708292</v>
+        <v>708243</v>
       </c>
       <c r="R28" t="n">
-        <v>7294045</v>
+        <v>7294417</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R29" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116255</v>
+        <v>128116248</v>
       </c>
       <c r="B30" t="n">
-        <v>80188</v>
+        <v>57682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708407</v>
+        <v>708292</v>
       </c>
       <c r="R30" t="n">
-        <v>7294680</v>
+        <v>7294045</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116313</v>
+        <v>128116301</v>
       </c>
       <c r="B33" t="n">
-        <v>92026</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708432</v>
+        <v>708375</v>
       </c>
       <c r="R33" t="n">
-        <v>7294694</v>
+        <v>7294094</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,11 +3753,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3784,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116301</v>
+        <v>128116313</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>92026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708375</v>
+        <v>708432</v>
       </c>
       <c r="R34" t="n">
-        <v>7294094</v>
+        <v>7294694</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3855,6 +3850,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116293</v>
+        <v>128116262</v>
       </c>
       <c r="B36" t="n">
-        <v>91470</v>
+        <v>57789</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708521</v>
+        <v>708295</v>
       </c>
       <c r="R36" t="n">
-        <v>7294413</v>
+        <v>7294459</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116299</v>
+        <v>128116270</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708462</v>
+        <v>708197</v>
       </c>
       <c r="R37" t="n">
-        <v>7294126</v>
+        <v>7294331</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116309</v>
+        <v>128116308</v>
       </c>
       <c r="B38" t="n">
         <v>79083</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708284</v>
+        <v>708216</v>
       </c>
       <c r="R38" t="n">
-        <v>7294509</v>
+        <v>7294159</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116308</v>
+        <v>128116309</v>
       </c>
       <c r="B39" t="n">
         <v>79083</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708216</v>
+        <v>708284</v>
       </c>
       <c r="R39" t="n">
-        <v>7294159</v>
+        <v>7294509</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116262</v>
+        <v>128116299</v>
       </c>
       <c r="B40" t="n">
-        <v>57789</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708295</v>
+        <v>708462</v>
       </c>
       <c r="R40" t="n">
-        <v>7294459</v>
+        <v>7294126</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116270</v>
+        <v>128116293</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>91470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708197</v>
+        <v>708521</v>
       </c>
       <c r="R41" t="n">
-        <v>7294331</v>
+        <v>7294413</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116252</v>
+        <v>128116239</v>
       </c>
       <c r="B42" t="n">
-        <v>97448</v>
+        <v>91417</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4571,21 +4571,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708525</v>
+        <v>708194</v>
       </c>
       <c r="R42" t="n">
-        <v>7294394</v>
+        <v>7294336</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116239</v>
+        <v>128116303</v>
       </c>
       <c r="B44" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708194</v>
+        <v>708288</v>
       </c>
       <c r="R44" t="n">
-        <v>7294336</v>
+        <v>7294045</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116303</v>
+        <v>128116252</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708288</v>
+        <v>708525</v>
       </c>
       <c r="R45" t="n">
-        <v>7294045</v>
+        <v>7294394</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128116288</v>
+        <v>128116296</v>
       </c>
       <c r="B46" t="n">
-        <v>91466</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708485</v>
+        <v>708450</v>
       </c>
       <c r="R46" t="n">
-        <v>7294476</v>
+        <v>7294389</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128116296</v>
+        <v>128116288</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>91466</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708450</v>
+        <v>708485</v>
       </c>
       <c r="R47" t="n">
-        <v>7294389</v>
+        <v>7294476</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B48" t="n">
-        <v>92026</v>
+        <v>82942</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R48" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5336,32 +5336,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B50" t="n">
-        <v>82942</v>
+        <v>92026</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116243</v>
+        <v>128116277</v>
       </c>
       <c r="B53" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708329</v>
+        <v>708269</v>
       </c>
       <c r="R53" t="n">
-        <v>7294658</v>
+        <v>7294506</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5698,6 +5698,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5821,32 +5826,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116240</v>
+        <v>128116261</v>
       </c>
       <c r="B55" t="n">
-        <v>79702</v>
+        <v>97448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708376</v>
+        <v>708394</v>
       </c>
       <c r="R55" t="n">
-        <v>7294699</v>
+        <v>7294544</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,10 +5923,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116254</v>
+        <v>128116240</v>
       </c>
       <c r="B56" t="n">
-        <v>80188</v>
+        <v>79702</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5934,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708400</v>
+        <v>708376</v>
       </c>
       <c r="R56" t="n">
-        <v>7294674</v>
+        <v>7294699</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,7 +6020,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116305</v>
+        <v>128116310</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6050,10 +6055,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708209</v>
+        <v>708426</v>
       </c>
       <c r="R57" t="n">
-        <v>7294140</v>
+        <v>7294468</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,7 +6117,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116256</v>
+        <v>128116254</v>
       </c>
       <c r="B58" t="n">
         <v>80188</v>
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708495</v>
+        <v>708400</v>
       </c>
       <c r="R58" t="n">
-        <v>7294673</v>
+        <v>7294674</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,10 +6214,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116310</v>
+        <v>128116260</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6220,21 +6225,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6249,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708426</v>
+        <v>708208</v>
       </c>
       <c r="R59" t="n">
-        <v>7294468</v>
+        <v>7294348</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6306,10 +6311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116260</v>
+        <v>128116305</v>
       </c>
       <c r="B60" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6317,21 +6322,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,10 +6346,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708208</v>
+        <v>708209</v>
       </c>
       <c r="R60" t="n">
-        <v>7294348</v>
+        <v>7294140</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6403,32 +6408,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116261</v>
+        <v>128116256</v>
       </c>
       <c r="B61" t="n">
-        <v>97448</v>
+        <v>80188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708394</v>
+        <v>708495</v>
       </c>
       <c r="R61" t="n">
-        <v>7294544</v>
+        <v>7294673</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6500,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116277</v>
+        <v>128116243</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6535,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708269</v>
+        <v>708329</v>
       </c>
       <c r="R62" t="n">
-        <v>7294506</v>
+        <v>7294658</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6571,11 +6576,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B66" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R66" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116266</v>
+        <v>128116241</v>
       </c>
       <c r="B67" t="n">
-        <v>98571</v>
+        <v>56876</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708534</v>
+        <v>708398</v>
       </c>
       <c r="R67" t="n">
-        <v>7294561</v>
+        <v>7294092</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116242</v>
+        <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708298</v>
+        <v>708195</v>
       </c>
       <c r="R68" t="n">
-        <v>7294185</v>
+        <v>7294329</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116241</v>
+        <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>56876</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708398</v>
+        <v>708534</v>
       </c>
       <c r="R69" t="n">
-        <v>7294092</v>
+        <v>7294561</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7378,10 +7378,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118833</v>
+        <v>128118893</v>
       </c>
       <c r="B71" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7389,21 +7389,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708245</v>
+        <v>708463</v>
       </c>
       <c r="R71" t="n">
-        <v>7294232</v>
+        <v>7294191</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7468,39 +7468,39 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128118834</v>
+        <v>128118856</v>
       </c>
       <c r="B72" t="n">
-        <v>91417</v>
+        <v>80188</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708433</v>
+        <v>708459</v>
       </c>
       <c r="R72" t="n">
-        <v>7294555</v>
+        <v>7294618</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7669,32 +7669,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118856</v>
+        <v>128118834</v>
       </c>
       <c r="B74" t="n">
-        <v>80188</v>
+        <v>91417</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708459</v>
+        <v>708433</v>
       </c>
       <c r="R74" t="n">
-        <v>7294618</v>
+        <v>7294555</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7766,10 +7766,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128118893</v>
+        <v>128118833</v>
       </c>
       <c r="B75" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7777,21 +7777,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708463</v>
+        <v>708245</v>
       </c>
       <c r="R75" t="n">
-        <v>7294191</v>
+        <v>7294232</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118881</v>
+        <v>128118867</v>
       </c>
       <c r="B77" t="n">
         <v>98571</v>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708273</v>
+        <v>708482</v>
       </c>
       <c r="R77" t="n">
-        <v>7294469</v>
+        <v>7294514</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8036,11 +8036,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8067,32 +8062,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128118863</v>
+        <v>128118866</v>
       </c>
       <c r="B78" t="n">
-        <v>58055</v>
+        <v>98571</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8102,10 +8097,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708340</v>
+        <v>708412</v>
       </c>
       <c r="R78" t="n">
-        <v>7294657</v>
+        <v>7294653</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8138,6 +8133,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8164,7 +8164,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128118867</v>
+        <v>128118881</v>
       </c>
       <c r="B79" t="n">
         <v>98571</v>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708482</v>
+        <v>708273</v>
       </c>
       <c r="R79" t="n">
-        <v>7294514</v>
+        <v>7294469</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8235,6 +8235,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8261,32 +8266,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128118866</v>
+        <v>128118863</v>
       </c>
       <c r="B80" t="n">
-        <v>98571</v>
+        <v>58055</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8296,10 +8301,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708412</v>
+        <v>708340</v>
       </c>
       <c r="R80" t="n">
-        <v>7294653</v>
+        <v>7294657</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8332,11 +8337,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8363,32 +8363,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128118848</v>
+        <v>128118900</v>
       </c>
       <c r="B81" t="n">
-        <v>98592</v>
+        <v>82942</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>708237</v>
+        <v>708422</v>
       </c>
       <c r="R81" t="n">
-        <v>7294377</v>
+        <v>7294064</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8453,39 +8453,39 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128118900</v>
+        <v>128118848</v>
       </c>
       <c r="B82" t="n">
-        <v>82942</v>
+        <v>98592</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>708422</v>
+        <v>708237</v>
       </c>
       <c r="R82" t="n">
-        <v>7294064</v>
+        <v>7294377</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8550,39 +8550,39 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128118901</v>
+        <v>128118844</v>
       </c>
       <c r="B83" t="n">
-        <v>82942</v>
+        <v>98592</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708358</v>
+        <v>708472</v>
       </c>
       <c r="R83" t="n">
-        <v>7294071</v>
+        <v>7294621</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8647,39 +8647,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128118844</v>
+        <v>128118873</v>
       </c>
       <c r="B84" t="n">
-        <v>98592</v>
+        <v>98571</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708472</v>
+        <v>708238</v>
       </c>
       <c r="R84" t="n">
-        <v>7294621</v>
+        <v>7294359</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8751,32 +8751,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128118851</v>
+        <v>128118877</v>
       </c>
       <c r="B85" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708470</v>
+        <v>708246</v>
       </c>
       <c r="R85" t="n">
-        <v>7294185</v>
+        <v>7294419</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8848,32 +8848,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128118873</v>
+        <v>128118901</v>
       </c>
       <c r="B86" t="n">
-        <v>98571</v>
+        <v>82942</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708238</v>
+        <v>708358</v>
       </c>
       <c r="R86" t="n">
-        <v>7294359</v>
+        <v>7294071</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8938,39 +8938,39 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128118877</v>
+        <v>128118851</v>
       </c>
       <c r="B87" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708246</v>
+        <v>708470</v>
       </c>
       <c r="R87" t="n">
-        <v>7294419</v>
+        <v>7294185</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9042,32 +9042,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128118876</v>
+        <v>128118855</v>
       </c>
       <c r="B88" t="n">
-        <v>98571</v>
+        <v>79107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>708233</v>
+        <v>708232</v>
       </c>
       <c r="R88" t="n">
-        <v>7294407</v>
+        <v>7294278</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9139,7 +9139,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128118870</v>
+        <v>128118876</v>
       </c>
       <c r="B89" t="n">
         <v>98571</v>
@@ -9174,10 +9174,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>708407</v>
+        <v>708233</v>
       </c>
       <c r="R89" t="n">
-        <v>7294148</v>
+        <v>7294407</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9236,32 +9236,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128118855</v>
+        <v>128118870</v>
       </c>
       <c r="B90" t="n">
-        <v>79107</v>
+        <v>98571</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>708232</v>
+        <v>708407</v>
       </c>
       <c r="R90" t="n">
-        <v>7294278</v>
+        <v>7294148</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9430,32 +9430,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118829</v>
+        <v>128118868</v>
       </c>
       <c r="B92" t="n">
-        <v>105594</v>
+        <v>98571</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708299</v>
+        <v>708494</v>
       </c>
       <c r="R92" t="n">
-        <v>7294038</v>
+        <v>7294519</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9527,32 +9527,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128118854</v>
+        <v>128118896</v>
       </c>
       <c r="B93" t="n">
-        <v>97448</v>
+        <v>79083</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708246</v>
+        <v>708411</v>
       </c>
       <c r="R93" t="n">
-        <v>7294430</v>
+        <v>7294054</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9617,39 +9617,39 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128118868</v>
+        <v>128118884</v>
       </c>
       <c r="B94" t="n">
-        <v>98571</v>
+        <v>79162</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708494</v>
+        <v>708477</v>
       </c>
       <c r="R94" t="n">
-        <v>7294519</v>
+        <v>7294616</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9721,32 +9721,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128118884</v>
+        <v>128118854</v>
       </c>
       <c r="B95" t="n">
-        <v>79162</v>
+        <v>97448</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708477</v>
+        <v>708246</v>
       </c>
       <c r="R95" t="n">
-        <v>7294616</v>
+        <v>7294430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9818,32 +9818,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128118896</v>
+        <v>128118829</v>
       </c>
       <c r="B96" t="n">
-        <v>79083</v>
+        <v>105594</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708411</v>
+        <v>708299</v>
       </c>
       <c r="R96" t="n">
-        <v>7294054</v>
+        <v>7294038</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9908,39 +9908,39 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128118878</v>
+        <v>128118892</v>
       </c>
       <c r="B97" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9950,10 +9950,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>708258</v>
+        <v>708476</v>
       </c>
       <c r="R97" t="n">
-        <v>7294447</v>
+        <v>7294478</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10005,39 +10005,39 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128118892</v>
+        <v>128118878</v>
       </c>
       <c r="B98" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>708476</v>
+        <v>708258</v>
       </c>
       <c r="R98" t="n">
-        <v>7294478</v>
+        <v>7294447</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10102,39 +10102,39 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128118860</v>
+        <v>128118909</v>
       </c>
       <c r="B99" t="n">
-        <v>80188</v>
+        <v>80223</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>708188</v>
+        <v>708416</v>
       </c>
       <c r="R99" t="n">
-        <v>7294093</v>
+        <v>7294052</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10199,39 +10199,39 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128118909</v>
+        <v>128118861</v>
       </c>
       <c r="B100" t="n">
-        <v>80223</v>
+        <v>80188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>708416</v>
+        <v>708259</v>
       </c>
       <c r="R100" t="n">
-        <v>7294052</v>
+        <v>7294452</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10296,14 +10296,14 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128118861</v>
+        <v>128118860</v>
       </c>
       <c r="B101" t="n">
         <v>80188</v>
@@ -10338,10 +10338,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>708259</v>
+        <v>708188</v>
       </c>
       <c r="R101" t="n">
-        <v>7294452</v>
+        <v>7294093</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10497,27 +10497,27 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128118895</v>
+        <v>128118912</v>
       </c>
       <c r="B103" t="n">
-        <v>79083</v>
+        <v>80223</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>708412</v>
+        <v>708262</v>
       </c>
       <c r="R103" t="n">
-        <v>7294150</v>
+        <v>7294457</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10594,10 +10594,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128118912</v>
+        <v>128118841</v>
       </c>
       <c r="B104" t="n">
-        <v>80223</v>
+        <v>80217</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10605,21 +10605,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>708262</v>
+        <v>708337</v>
       </c>
       <c r="R104" t="n">
-        <v>7294457</v>
+        <v>7294039</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -10788,32 +10788,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128118841</v>
+        <v>128118895</v>
       </c>
       <c r="B106" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>708337</v>
+        <v>708412</v>
       </c>
       <c r="R106" t="n">
-        <v>7294039</v>
+        <v>7294150</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10878,39 +10878,39 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128118886</v>
+        <v>128118835</v>
       </c>
       <c r="B107" t="n">
-        <v>91470</v>
+        <v>58544</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>208249</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>708480</v>
+        <v>708445</v>
       </c>
       <c r="R107" t="n">
-        <v>7294478</v>
+        <v>7294644</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -10982,32 +10982,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128118832</v>
+        <v>128118872</v>
       </c>
       <c r="B108" t="n">
-        <v>105594</v>
+        <v>98571</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>708229</v>
+        <v>708200</v>
       </c>
       <c r="R108" t="n">
-        <v>7294386</v>
+        <v>7294326</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11079,32 +11079,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128118853</v>
+        <v>128118874</v>
       </c>
       <c r="B109" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>708228</v>
+        <v>708235</v>
       </c>
       <c r="R109" t="n">
-        <v>7294377</v>
+        <v>7294371</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11176,32 +11176,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128118835</v>
+        <v>128118886</v>
       </c>
       <c r="B110" t="n">
-        <v>58544</v>
+        <v>91470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>208249</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>708445</v>
+        <v>708480</v>
       </c>
       <c r="R110" t="n">
-        <v>7294644</v>
+        <v>7294478</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11273,32 +11273,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128118872</v>
+        <v>128118853</v>
       </c>
       <c r="B111" t="n">
-        <v>98571</v>
+        <v>97448</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>708200</v>
+        <v>708228</v>
       </c>
       <c r="R111" t="n">
-        <v>7294326</v>
+        <v>7294377</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11370,32 +11370,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128118874</v>
+        <v>128118832</v>
       </c>
       <c r="B112" t="n">
-        <v>98571</v>
+        <v>105594</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>708235</v>
+        <v>708229</v>
       </c>
       <c r="R112" t="n">
-        <v>7294371</v>
+        <v>7294386</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11467,32 +11467,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128118888</v>
+        <v>128118879</v>
       </c>
       <c r="B113" t="n">
-        <v>91470</v>
+        <v>98571</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>708218</v>
+        <v>708260</v>
       </c>
       <c r="R113" t="n">
-        <v>7294252</v>
+        <v>7294439</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11540,6 +11540,11 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -11557,39 +11562,39 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128118843</v>
+        <v>128118888</v>
       </c>
       <c r="B114" t="n">
-        <v>98592</v>
+        <v>91470</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11599,10 +11604,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>708496</v>
+        <v>708218</v>
       </c>
       <c r="R114" t="n">
-        <v>7294626</v>
+        <v>7294252</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11637,11 +11642,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -11659,39 +11659,39 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128118879</v>
+        <v>128118843</v>
       </c>
       <c r="B115" t="n">
-        <v>98571</v>
+        <v>98592</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>708260</v>
+        <v>708496</v>
       </c>
       <c r="R115" t="n">
-        <v>7294439</v>
+        <v>7294626</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Stort bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11768,32 +11768,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128118875</v>
+        <v>128118836</v>
       </c>
       <c r="B116" t="n">
-        <v>98571</v>
+        <v>58544</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>708230</v>
+        <v>708203</v>
       </c>
       <c r="R116" t="n">
-        <v>7294377</v>
+        <v>7294324</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128118836</v>
+        <v>128118875</v>
       </c>
       <c r="B117" t="n">
-        <v>58544</v>
+        <v>98571</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>708203</v>
+        <v>708230</v>
       </c>
       <c r="R117" t="n">
-        <v>7294324</v>
+        <v>7294377</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12156,7 +12156,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128118898</v>
+        <v>128118894</v>
       </c>
       <c r="B120" t="n">
         <v>79083</v>
@@ -12191,10 +12191,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>708249</v>
+        <v>708443</v>
       </c>
       <c r="R120" t="n">
-        <v>7294216</v>
+        <v>7294180</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12253,7 +12253,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128118894</v>
+        <v>128118898</v>
       </c>
       <c r="B121" t="n">
         <v>79083</v>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>708443</v>
+        <v>708249</v>
       </c>
       <c r="R121" t="n">
-        <v>7294180</v>
+        <v>7294216</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12350,32 +12350,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128118845</v>
+        <v>128118883</v>
       </c>
       <c r="B122" t="n">
-        <v>98592</v>
+        <v>98571</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12385,10 +12385,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>708477</v>
+        <v>708436</v>
       </c>
       <c r="R122" t="n">
-        <v>7294616</v>
+        <v>7294589</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12447,32 +12447,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128118849</v>
+        <v>128118889</v>
       </c>
       <c r="B123" t="n">
-        <v>98592</v>
+        <v>91470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>708250</v>
+        <v>708192</v>
       </c>
       <c r="R123" t="n">
-        <v>7294430</v>
+        <v>7294318</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12537,39 +12537,39 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128118889</v>
+        <v>128118849</v>
       </c>
       <c r="B124" t="n">
-        <v>91470</v>
+        <v>98592</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>708192</v>
+        <v>708250</v>
       </c>
       <c r="R124" t="n">
-        <v>7294318</v>
+        <v>7294430</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -12634,39 +12634,39 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128118883</v>
+        <v>128118845</v>
       </c>
       <c r="B125" t="n">
-        <v>98571</v>
+        <v>98592</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>708436</v>
+        <v>708477</v>
       </c>
       <c r="R125" t="n">
-        <v>7294589</v>
+        <v>7294616</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128118902</v>
+        <v>128118839</v>
       </c>
       <c r="B126" t="n">
-        <v>91713</v>
+        <v>80217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>708202</v>
+        <v>708424</v>
       </c>
       <c r="R126" t="n">
-        <v>7294326</v>
+        <v>7294672</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -12828,39 +12828,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128118882</v>
+        <v>128118899</v>
       </c>
       <c r="B127" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>708290</v>
+        <v>708214</v>
       </c>
       <c r="R127" t="n">
-        <v>7294501</v>
+        <v>7294309</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -12925,39 +12925,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128118839</v>
+        <v>128118882</v>
       </c>
       <c r="B128" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>708424</v>
+        <v>708290</v>
       </c>
       <c r="R128" t="n">
-        <v>7294672</v>
+        <v>7294501</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13029,32 +13029,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128118899</v>
+        <v>128118902</v>
       </c>
       <c r="B129" t="n">
-        <v>79083</v>
+        <v>91713</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>708214</v>
+        <v>708202</v>
       </c>
       <c r="R129" t="n">
-        <v>7294309</v>
+        <v>7294326</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13320,32 +13320,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128118880</v>
+        <v>128118857</v>
       </c>
       <c r="B132" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>708290</v>
+        <v>708335</v>
       </c>
       <c r="R132" t="n">
-        <v>7294490</v>
+        <v>7294032</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13417,32 +13417,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128118869</v>
+        <v>128118903</v>
       </c>
       <c r="B133" t="n">
-        <v>98571</v>
+        <v>98488</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>708487</v>
+        <v>708233</v>
       </c>
       <c r="R133" t="n">
-        <v>7294472</v>
+        <v>7294206</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -13490,11 +13490,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -13512,39 +13507,39 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128118857</v>
+        <v>128118869</v>
       </c>
       <c r="B134" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13554,10 +13549,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>708335</v>
+        <v>708487</v>
       </c>
       <c r="R134" t="n">
-        <v>7294032</v>
+        <v>7294472</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -13590,6 +13585,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13616,32 +13616,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128118903</v>
+        <v>128118880</v>
       </c>
       <c r="B135" t="n">
-        <v>98488</v>
+        <v>98571</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>708233</v>
+        <v>708290</v>
       </c>
       <c r="R135" t="n">
-        <v>7294206</v>
+        <v>7294490</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116306</v>
+        <v>128116268</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708199</v>
+        <v>708226</v>
       </c>
       <c r="R8" t="n">
-        <v>7294151</v>
+        <v>7294304</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116307</v>
+        <v>128116306</v>
       </c>
       <c r="B9" t="n">
         <v>79083</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708223</v>
+        <v>708199</v>
       </c>
       <c r="R9" t="n">
-        <v>7294146</v>
+        <v>7294151</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116246</v>
+        <v>128116307</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708396</v>
+        <v>708223</v>
       </c>
       <c r="R10" t="n">
-        <v>7294100</v>
+        <v>7294146</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116268</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708226</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294304</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116286</v>
+        <v>128116249</v>
       </c>
       <c r="B13" t="n">
-        <v>91466</v>
+        <v>57682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708482</v>
+        <v>708207</v>
       </c>
       <c r="R13" t="n">
-        <v>7294632</v>
+        <v>7294133</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116249</v>
+        <v>128116286</v>
       </c>
       <c r="B14" t="n">
-        <v>57682</v>
+        <v>91466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708207</v>
+        <v>708482</v>
       </c>
       <c r="R14" t="n">
-        <v>7294133</v>
+        <v>7294632</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116312</v>
+        <v>128116281</v>
       </c>
       <c r="B18" t="n">
-        <v>82942</v>
+        <v>56867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708202</v>
+        <v>708480</v>
       </c>
       <c r="R18" t="n">
-        <v>7294136</v>
+        <v>7294127</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116253</v>
+        <v>128116312</v>
       </c>
       <c r="B19" t="n">
-        <v>92935</v>
+        <v>82942</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708194</v>
+        <v>708202</v>
       </c>
       <c r="R19" t="n">
-        <v>7294336</v>
+        <v>7294136</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116281</v>
+        <v>128116253</v>
       </c>
       <c r="B20" t="n">
-        <v>56867</v>
+        <v>92935</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708480</v>
+        <v>708194</v>
       </c>
       <c r="R20" t="n">
-        <v>7294127</v>
+        <v>7294336</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116239</v>
+        <v>128116303</v>
       </c>
       <c r="B42" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708194</v>
+        <v>708288</v>
       </c>
       <c r="R42" t="n">
-        <v>7294336</v>
+        <v>7294045</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116265</v>
+        <v>128116252</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>97448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708523</v>
+        <v>708525</v>
       </c>
       <c r="R43" t="n">
-        <v>7294599</v>
+        <v>7294394</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R44" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116252</v>
+        <v>128116265</v>
       </c>
       <c r="B45" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708525</v>
+        <v>708523</v>
       </c>
       <c r="R45" t="n">
-        <v>7294394</v>
+        <v>7294599</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B66" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R66" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B68" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R68" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,7 +7184,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116266</v>
+        <v>128116269</v>
       </c>
       <c r="B69" t="n">
         <v>98571</v>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708534</v>
+        <v>708195</v>
       </c>
       <c r="R69" t="n">
-        <v>7294561</v>
+        <v>7294329</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7378,10 +7378,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118893</v>
+        <v>128118833</v>
       </c>
       <c r="B71" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7389,21 +7389,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708463</v>
+        <v>708245</v>
       </c>
       <c r="R71" t="n">
-        <v>7294191</v>
+        <v>7294232</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7468,39 +7468,39 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128118856</v>
+        <v>128118867</v>
       </c>
       <c r="B72" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708459</v>
+        <v>708482</v>
       </c>
       <c r="R72" t="n">
-        <v>7294618</v>
+        <v>7294514</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7572,32 +7572,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128118840</v>
+        <v>128118866</v>
       </c>
       <c r="B73" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708415</v>
+        <v>708412</v>
       </c>
       <c r="R73" t="n">
-        <v>7294056</v>
+        <v>7294653</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7643,6 +7643,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7669,32 +7674,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118834</v>
+        <v>128118881</v>
       </c>
       <c r="B74" t="n">
-        <v>91417</v>
+        <v>98571</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7704,10 +7709,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708433</v>
+        <v>708273</v>
       </c>
       <c r="R74" t="n">
-        <v>7294555</v>
+        <v>7294469</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7740,6 +7745,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7766,32 +7776,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128118833</v>
+        <v>128118863</v>
       </c>
       <c r="B75" t="n">
-        <v>79115</v>
+        <v>58055</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7801,10 +7811,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708245</v>
+        <v>708340</v>
       </c>
       <c r="R75" t="n">
-        <v>7294232</v>
+        <v>7294657</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7863,32 +7873,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128118837</v>
+        <v>128118893</v>
       </c>
       <c r="B76" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7898,10 +7908,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>708415</v>
+        <v>708463</v>
       </c>
       <c r="R76" t="n">
-        <v>7294151</v>
+        <v>7294191</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7936,11 +7946,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>3st honor</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -7958,39 +7963,39 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118867</v>
+        <v>128118856</v>
       </c>
       <c r="B77" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8000,10 +8005,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708482</v>
+        <v>708459</v>
       </c>
       <c r="R77" t="n">
-        <v>7294514</v>
+        <v>7294618</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8062,32 +8067,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128118866</v>
+        <v>128118840</v>
       </c>
       <c r="B78" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8097,10 +8102,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708412</v>
+        <v>708415</v>
       </c>
       <c r="R78" t="n">
-        <v>7294653</v>
+        <v>7294056</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8133,11 +8138,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8164,32 +8164,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128118881</v>
+        <v>128118834</v>
       </c>
       <c r="B79" t="n">
-        <v>98571</v>
+        <v>91417</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708273</v>
+        <v>708433</v>
       </c>
       <c r="R79" t="n">
-        <v>7294469</v>
+        <v>7294555</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8235,11 +8235,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8266,10 +8261,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128118863</v>
+        <v>128118837</v>
       </c>
       <c r="B80" t="n">
-        <v>58055</v>
+        <v>56876</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8277,21 +8272,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8296,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708340</v>
+        <v>708415</v>
       </c>
       <c r="R80" t="n">
-        <v>7294657</v>
+        <v>7294151</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8337,6 +8332,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>3st honor</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8557,32 +8557,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128118844</v>
+        <v>128118851</v>
       </c>
       <c r="B83" t="n">
-        <v>98592</v>
+        <v>57682</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708472</v>
+        <v>708470</v>
       </c>
       <c r="R83" t="n">
-        <v>7294621</v>
+        <v>7294185</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8654,32 +8654,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128118873</v>
+        <v>128118901</v>
       </c>
       <c r="B84" t="n">
-        <v>98571</v>
+        <v>82942</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708238</v>
+        <v>708358</v>
       </c>
       <c r="R84" t="n">
-        <v>7294359</v>
+        <v>7294071</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8744,39 +8744,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128118877</v>
+        <v>128118844</v>
       </c>
       <c r="B85" t="n">
-        <v>98571</v>
+        <v>98592</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708246</v>
+        <v>708472</v>
       </c>
       <c r="R85" t="n">
-        <v>7294419</v>
+        <v>7294621</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8848,32 +8848,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128118901</v>
+        <v>128118873</v>
       </c>
       <c r="B86" t="n">
-        <v>82942</v>
+        <v>98571</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708358</v>
+        <v>708238</v>
       </c>
       <c r="R86" t="n">
-        <v>7294071</v>
+        <v>7294359</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8938,39 +8938,39 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128118851</v>
+        <v>128118877</v>
       </c>
       <c r="B87" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708470</v>
+        <v>708246</v>
       </c>
       <c r="R87" t="n">
-        <v>7294185</v>
+        <v>7294419</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128116295</v>
+        <v>128116294</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708340</v>
+        <v>708521</v>
       </c>
       <c r="R2" t="n">
-        <v>7294066</v>
+        <v>7294393</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128116294</v>
+        <v>128116295</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708521</v>
+        <v>708340</v>
       </c>
       <c r="R3" t="n">
-        <v>7294393</v>
+        <v>7294066</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -872,7 +872,7 @@
         <v>128116297</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128116247</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128116278</v>
       </c>
       <c r="B6" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128116283</v>
       </c>
       <c r="B7" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116268</v>
+        <v>128116246</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708226</v>
+        <v>708396</v>
       </c>
       <c r="R8" t="n">
-        <v>7294304</v>
+        <v>7294100</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116306</v>
+        <v>128116268</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708199</v>
+        <v>708226</v>
       </c>
       <c r="R9" t="n">
-        <v>7294151</v>
+        <v>7294304</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116307</v>
+        <v>128116290</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>91478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708223</v>
+        <v>708225</v>
       </c>
       <c r="R10" t="n">
-        <v>7294146</v>
+        <v>7294123</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116246</v>
+        <v>128116306</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708396</v>
+        <v>708199</v>
       </c>
       <c r="R11" t="n">
-        <v>7294100</v>
+        <v>7294151</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128116290</v>
+        <v>128116307</v>
       </c>
       <c r="B12" t="n">
-        <v>91466</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708225</v>
+        <v>708223</v>
       </c>
       <c r="R12" t="n">
-        <v>7294123</v>
+        <v>7294146</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116249</v>
+        <v>128116286</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708207</v>
+        <v>708482</v>
       </c>
       <c r="R13" t="n">
-        <v>7294133</v>
+        <v>7294632</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116286</v>
+        <v>128116258</v>
       </c>
       <c r="B14" t="n">
-        <v>91466</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708482</v>
+        <v>708471</v>
       </c>
       <c r="R14" t="n">
-        <v>7294632</v>
+        <v>7294139</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116304</v>
+        <v>128116249</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708225</v>
+        <v>708207</v>
       </c>
       <c r="R15" t="n">
-        <v>7294108</v>
+        <v>7294133</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116258</v>
+        <v>128116304</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708471</v>
+        <v>708225</v>
       </c>
       <c r="R16" t="n">
-        <v>7294139</v>
+        <v>7294108</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>56871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R17" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128116281</v>
+        <v>128116312</v>
       </c>
       <c r="B18" t="n">
-        <v>56867</v>
+        <v>82946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708480</v>
+        <v>708202</v>
       </c>
       <c r="R18" t="n">
-        <v>7294127</v>
+        <v>7294136</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128116312</v>
+        <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>82942</v>
+        <v>92947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708202</v>
+        <v>708194</v>
       </c>
       <c r="R19" t="n">
-        <v>7294136</v>
+        <v>7294336</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116253</v>
+        <v>128116259</v>
       </c>
       <c r="B20" t="n">
-        <v>92935</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708194</v>
+        <v>708415</v>
       </c>
       <c r="R20" t="n">
-        <v>7294336</v>
+        <v>7294078</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2521,7 +2521,7 @@
         <v>128116302</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128116298</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116245</v>
+        <v>128116279</v>
       </c>
       <c r="B23" t="n">
-        <v>57682</v>
+        <v>79166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708491</v>
+        <v>708215</v>
       </c>
       <c r="R23" t="n">
-        <v>7294463</v>
+        <v>7294156</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116279</v>
+        <v>128116315</v>
       </c>
       <c r="B24" t="n">
-        <v>79162</v>
+        <v>92038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708215</v>
+        <v>708330</v>
       </c>
       <c r="R24" t="n">
-        <v>7294156</v>
+        <v>7294664</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116315</v>
+        <v>128116285</v>
       </c>
       <c r="B25" t="n">
-        <v>92026</v>
+        <v>91460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708330</v>
+        <v>708246</v>
       </c>
       <c r="R25" t="n">
-        <v>7294664</v>
+        <v>7294412</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116285</v>
+        <v>128116245</v>
       </c>
       <c r="B26" t="n">
-        <v>91448</v>
+        <v>57686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708246</v>
+        <v>708491</v>
       </c>
       <c r="R26" t="n">
-        <v>7294412</v>
+        <v>7294463</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3103,7 +3103,7 @@
         <v>128116251</v>
       </c>
       <c r="B27" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116274</v>
+        <v>128116289</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>91478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708243</v>
+        <v>708501</v>
       </c>
       <c r="R28" t="n">
-        <v>7294417</v>
+        <v>7294429</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3297,7 +3297,7 @@
         <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116248</v>
+        <v>128116274</v>
       </c>
       <c r="B30" t="n">
-        <v>57682</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708292</v>
+        <v>708243</v>
       </c>
       <c r="R30" t="n">
-        <v>7294045</v>
+        <v>7294417</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B31" t="n">
-        <v>91466</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R31" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3588,7 +3588,7 @@
         <v>128116300</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128116301</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B34" t="n">
-        <v>92026</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R34" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3850,11 +3850,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3881,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116264</v>
+        <v>128116313</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>92038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708489</v>
+        <v>708432</v>
       </c>
       <c r="R35" t="n">
-        <v>7294661</v>
+        <v>7294694</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116262</v>
+        <v>128116299</v>
       </c>
       <c r="B36" t="n">
-        <v>57789</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708295</v>
+        <v>708462</v>
       </c>
       <c r="R36" t="n">
-        <v>7294459</v>
+        <v>7294126</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116270</v>
+        <v>128116309</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708197</v>
+        <v>708284</v>
       </c>
       <c r="R37" t="n">
-        <v>7294331</v>
+        <v>7294509</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4175,7 +4175,7 @@
         <v>128116308</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116309</v>
+        <v>128116293</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708284</v>
+        <v>708521</v>
       </c>
       <c r="R39" t="n">
-        <v>7294509</v>
+        <v>7294413</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116299</v>
+        <v>128116262</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>57793</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708462</v>
+        <v>708295</v>
       </c>
       <c r="R40" t="n">
-        <v>7294126</v>
+        <v>7294459</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116293</v>
+        <v>128116270</v>
       </c>
       <c r="B41" t="n">
-        <v>91470</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708521</v>
+        <v>708197</v>
       </c>
       <c r="R41" t="n">
-        <v>7294413</v>
+        <v>7294331</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>91429</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R42" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116252</v>
+        <v>128116303</v>
       </c>
       <c r="B43" t="n">
-        <v>97448</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708525</v>
+        <v>708288</v>
       </c>
       <c r="R43" t="n">
-        <v>7294394</v>
+        <v>7294045</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B44" t="n">
-        <v>91417</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R44" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4851,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128116265</v>
+        <v>128116252</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>97460</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708523</v>
+        <v>708525</v>
       </c>
       <c r="R45" t="n">
-        <v>7294599</v>
+        <v>7294394</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128116296</v>
+        <v>128116288</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>91478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708450</v>
+        <v>708485</v>
       </c>
       <c r="R46" t="n">
-        <v>7294389</v>
+        <v>7294476</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128116288</v>
+        <v>128116296</v>
       </c>
       <c r="B47" t="n">
-        <v>91466</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708485</v>
+        <v>708450</v>
       </c>
       <c r="R47" t="n">
-        <v>7294476</v>
+        <v>7294389</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116311</v>
+        <v>128116272</v>
       </c>
       <c r="B48" t="n">
-        <v>82942</v>
+        <v>98585</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294070</v>
+        <v>7294403</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116272</v>
+        <v>128116311</v>
       </c>
       <c r="B49" t="n">
-        <v>98571</v>
+        <v>82946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R49" t="n">
-        <v>7294403</v>
+        <v>7294070</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5339,7 +5339,7 @@
         <v>128116314</v>
       </c>
       <c r="B50" t="n">
-        <v>92026</v>
+        <v>92038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116277</v>
+        <v>128116305</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708269</v>
+        <v>708209</v>
       </c>
       <c r="R53" t="n">
-        <v>7294506</v>
+        <v>7294140</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5698,11 +5698,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5732,7 +5727,7 @@
         <v>128116292</v>
       </c>
       <c r="B54" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,32 +5821,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116261</v>
+        <v>128116310</v>
       </c>
       <c r="B55" t="n">
-        <v>97448</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5861,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708394</v>
+        <v>708426</v>
       </c>
       <c r="R55" t="n">
-        <v>7294544</v>
+        <v>7294468</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5926,7 +5921,7 @@
         <v>128116240</v>
       </c>
       <c r="B56" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6020,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116310</v>
+        <v>128116254</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>80192</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6031,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6055,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708426</v>
+        <v>708400</v>
       </c>
       <c r="R57" t="n">
-        <v>7294468</v>
+        <v>7294674</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6117,10 +6112,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116254</v>
+        <v>128116260</v>
       </c>
       <c r="B58" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708400</v>
+        <v>708208</v>
       </c>
       <c r="R58" t="n">
-        <v>7294674</v>
+        <v>7294348</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6214,10 +6209,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116260</v>
+        <v>128116256</v>
       </c>
       <c r="B59" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6249,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708208</v>
+        <v>708495</v>
       </c>
       <c r="R59" t="n">
-        <v>7294348</v>
+        <v>7294673</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6311,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116305</v>
+        <v>128116243</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>57849</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6322,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6346,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708209</v>
+        <v>708329</v>
       </c>
       <c r="R60" t="n">
-        <v>7294140</v>
+        <v>7294658</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6408,32 +6403,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116256</v>
+        <v>128116277</v>
       </c>
       <c r="B61" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708495</v>
+        <v>708269</v>
       </c>
       <c r="R61" t="n">
-        <v>7294673</v>
+        <v>7294506</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6479,6 +6474,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116243</v>
+        <v>128116261</v>
       </c>
       <c r="B62" t="n">
-        <v>57845</v>
+        <v>97460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708329</v>
+        <v>708394</v>
       </c>
       <c r="R62" t="n">
-        <v>7294658</v>
+        <v>7294544</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6699,32 +6699,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128116287</v>
+        <v>128116276</v>
       </c>
       <c r="B64" t="n">
-        <v>91466</v>
+        <v>98585</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708515</v>
+        <v>708267</v>
       </c>
       <c r="R64" t="n">
-        <v>7294574</v>
+        <v>7294433</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -6796,32 +6796,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128116276</v>
+        <v>128116287</v>
       </c>
       <c r="B65" t="n">
-        <v>98571</v>
+        <v>91478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708267</v>
+        <v>708515</v>
       </c>
       <c r="R65" t="n">
-        <v>7294433</v>
+        <v>7294574</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128116266</v>
+        <v>128116241</v>
       </c>
       <c r="B66" t="n">
-        <v>98571</v>
+        <v>56880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708534</v>
+        <v>708398</v>
       </c>
       <c r="R66" t="n">
-        <v>7294561</v>
+        <v>7294092</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116241</v>
+        <v>128116269</v>
       </c>
       <c r="B67" t="n">
-        <v>56876</v>
+        <v>98585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708398</v>
+        <v>708195</v>
       </c>
       <c r="R67" t="n">
-        <v>7294092</v>
+        <v>7294329</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B68" t="n">
-        <v>57845</v>
+        <v>98585</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R68" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>57849</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R69" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7284,7 +7284,7 @@
         <v>128118838</v>
       </c>
       <c r="B70" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7378,32 +7378,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118833</v>
+        <v>128118867</v>
       </c>
       <c r="B71" t="n">
-        <v>79115</v>
+        <v>98585</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708245</v>
+        <v>708482</v>
       </c>
       <c r="R71" t="n">
-        <v>7294232</v>
+        <v>7294514</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7475,10 +7475,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128118867</v>
+        <v>128118866</v>
       </c>
       <c r="B72" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708482</v>
+        <v>708412</v>
       </c>
       <c r="R72" t="n">
-        <v>7294514</v>
+        <v>7294653</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7546,6 +7546,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7572,10 +7577,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128118866</v>
+        <v>128118881</v>
       </c>
       <c r="B73" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7607,10 +7612,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708412</v>
+        <v>708273</v>
       </c>
       <c r="R73" t="n">
-        <v>7294653</v>
+        <v>7294469</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7647,7 +7652,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Mycket rikligt bestånd</t>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7674,32 +7679,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118881</v>
+        <v>128118837</v>
       </c>
       <c r="B74" t="n">
-        <v>98571</v>
+        <v>56880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7709,10 +7714,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708273</v>
+        <v>708415</v>
       </c>
       <c r="R74" t="n">
-        <v>7294469</v>
+        <v>7294151</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7749,7 +7754,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Stort bestånd</t>
+          <t>3st honor</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7779,7 +7784,7 @@
         <v>128118863</v>
       </c>
       <c r="B75" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7873,10 +7878,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128118893</v>
+        <v>128118833</v>
       </c>
       <c r="B76" t="n">
-        <v>79083</v>
+        <v>79119</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7884,21 +7889,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7908,10 +7913,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>708463</v>
+        <v>708245</v>
       </c>
       <c r="R76" t="n">
-        <v>7294191</v>
+        <v>7294232</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7963,39 +7968,39 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118856</v>
+        <v>128118834</v>
       </c>
       <c r="B77" t="n">
-        <v>80188</v>
+        <v>91429</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708459</v>
+        <v>708433</v>
       </c>
       <c r="R77" t="n">
-        <v>7294618</v>
+        <v>7294555</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8067,32 +8072,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128118840</v>
+        <v>128118893</v>
       </c>
       <c r="B78" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8102,10 +8107,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708415</v>
+        <v>708463</v>
       </c>
       <c r="R78" t="n">
-        <v>7294056</v>
+        <v>7294191</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8157,39 +8162,39 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128118834</v>
+        <v>128118856</v>
       </c>
       <c r="B79" t="n">
-        <v>91417</v>
+        <v>80192</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8199,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708433</v>
+        <v>708459</v>
       </c>
       <c r="R79" t="n">
-        <v>7294555</v>
+        <v>7294618</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8261,10 +8266,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128118837</v>
+        <v>128118840</v>
       </c>
       <c r="B80" t="n">
-        <v>56876</v>
+        <v>80221</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8272,21 +8277,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8299,7 +8304,7 @@
         <v>708415</v>
       </c>
       <c r="R80" t="n">
-        <v>7294151</v>
+        <v>7294056</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8332,11 +8337,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>3st honor</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8366,7 +8366,7 @@
         <v>128118900</v>
       </c>
       <c r="B81" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>128118848</v>
       </c>
       <c r="B82" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128118851</v>
+        <v>128118901</v>
       </c>
       <c r="B83" t="n">
-        <v>57682</v>
+        <v>82946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8568,21 +8568,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708470</v>
+        <v>708358</v>
       </c>
       <c r="R83" t="n">
-        <v>7294185</v>
+        <v>7294071</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8647,17 +8647,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128118901</v>
+        <v>128118851</v>
       </c>
       <c r="B84" t="n">
-        <v>82942</v>
+        <v>57686</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708358</v>
+        <v>708470</v>
       </c>
       <c r="R84" t="n">
-        <v>7294071</v>
+        <v>7294185</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8744,39 +8744,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128118844</v>
+        <v>128118873</v>
       </c>
       <c r="B85" t="n">
-        <v>98592</v>
+        <v>98585</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708472</v>
+        <v>708238</v>
       </c>
       <c r="R85" t="n">
-        <v>7294621</v>
+        <v>7294359</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8848,10 +8848,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128118873</v>
+        <v>128118877</v>
       </c>
       <c r="B86" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708238</v>
+        <v>708246</v>
       </c>
       <c r="R86" t="n">
-        <v>7294359</v>
+        <v>7294419</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8945,32 +8945,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128118877</v>
+        <v>128118844</v>
       </c>
       <c r="B87" t="n">
-        <v>98571</v>
+        <v>98606</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708246</v>
+        <v>708472</v>
       </c>
       <c r="R87" t="n">
-        <v>7294419</v>
+        <v>7294621</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9045,7 +9045,7 @@
         <v>128118855</v>
       </c>
       <c r="B88" t="n">
-        <v>79107</v>
+        <v>79111</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>128118876</v>
       </c>
       <c r="B89" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>128118870</v>
       </c>
       <c r="B90" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>128118885</v>
       </c>
       <c r="B91" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9430,32 +9430,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118868</v>
+        <v>128118896</v>
       </c>
       <c r="B92" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708494</v>
+        <v>708411</v>
       </c>
       <c r="R92" t="n">
-        <v>7294519</v>
+        <v>7294054</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9520,39 +9520,39 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128118896</v>
+        <v>128118868</v>
       </c>
       <c r="B93" t="n">
-        <v>79083</v>
+        <v>98585</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708411</v>
+        <v>708494</v>
       </c>
       <c r="R93" t="n">
-        <v>7294054</v>
+        <v>7294519</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9617,39 +9617,39 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128118884</v>
+        <v>128118829</v>
       </c>
       <c r="B94" t="n">
-        <v>79162</v>
+        <v>105615</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>864</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708477</v>
+        <v>708299</v>
       </c>
       <c r="R94" t="n">
-        <v>7294616</v>
+        <v>7294038</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9721,32 +9721,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128118854</v>
+        <v>128118884</v>
       </c>
       <c r="B95" t="n">
-        <v>97448</v>
+        <v>79166</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708246</v>
+        <v>708477</v>
       </c>
       <c r="R95" t="n">
-        <v>7294430</v>
+        <v>7294616</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9818,10 +9818,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128118829</v>
+        <v>128118854</v>
       </c>
       <c r="B96" t="n">
-        <v>105594</v>
+        <v>97460</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9829,21 +9829,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708299</v>
+        <v>708246</v>
       </c>
       <c r="R96" t="n">
-        <v>7294038</v>
+        <v>7294430</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9918,7 +9918,7 @@
         <v>128118892</v>
       </c>
       <c r="B97" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>128118878</v>
       </c>
       <c r="B98" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>128118909</v>
       </c>
       <c r="B99" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>128118861</v>
       </c>
       <c r="B100" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>128118860</v>
       </c>
       <c r="B101" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>128118847</v>
       </c>
       <c r="B102" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10497,27 +10497,27 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128118912</v>
+        <v>128118895</v>
       </c>
       <c r="B103" t="n">
-        <v>80223</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>708262</v>
+        <v>708412</v>
       </c>
       <c r="R103" t="n">
-        <v>7294457</v>
+        <v>7294150</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10594,32 +10594,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128118841</v>
+        <v>128118886</v>
       </c>
       <c r="B104" t="n">
-        <v>80217</v>
+        <v>91482</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>708337</v>
+        <v>708480</v>
       </c>
       <c r="R104" t="n">
-        <v>7294039</v>
+        <v>7294478</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10691,10 +10691,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128118906</v>
+        <v>128118841</v>
       </c>
       <c r="B105" t="n">
-        <v>80223</v>
+        <v>80221</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>708432</v>
+        <v>708337</v>
       </c>
       <c r="R105" t="n">
-        <v>7294676</v>
+        <v>7294039</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10781,39 +10781,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128118895</v>
+        <v>128118835</v>
       </c>
       <c r="B106" t="n">
-        <v>79083</v>
+        <v>58548</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>708412</v>
+        <v>708445</v>
       </c>
       <c r="R106" t="n">
-        <v>7294150</v>
+        <v>7294644</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10878,39 +10878,39 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128118835</v>
+        <v>128118872</v>
       </c>
       <c r="B107" t="n">
-        <v>58544</v>
+        <v>98585</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>708445</v>
+        <v>708200</v>
       </c>
       <c r="R107" t="n">
-        <v>7294644</v>
+        <v>7294326</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -10982,10 +10982,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128118872</v>
+        <v>128118874</v>
       </c>
       <c r="B108" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>708200</v>
+        <v>708235</v>
       </c>
       <c r="R108" t="n">
-        <v>7294326</v>
+        <v>7294371</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11079,32 +11079,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128118874</v>
+        <v>128118853</v>
       </c>
       <c r="B109" t="n">
-        <v>98571</v>
+        <v>97460</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>708235</v>
+        <v>708228</v>
       </c>
       <c r="R109" t="n">
-        <v>7294371</v>
+        <v>7294377</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11176,32 +11176,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128118886</v>
+        <v>128118912</v>
       </c>
       <c r="B110" t="n">
-        <v>91470</v>
+        <v>80227</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>708480</v>
+        <v>708262</v>
       </c>
       <c r="R110" t="n">
-        <v>7294478</v>
+        <v>7294457</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128118853</v>
+        <v>128118906</v>
       </c>
       <c r="B111" t="n">
-        <v>97448</v>
+        <v>80227</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>708228</v>
+        <v>708432</v>
       </c>
       <c r="R111" t="n">
-        <v>7294377</v>
+        <v>7294676</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11373,7 +11373,7 @@
         <v>128118832</v>
       </c>
       <c r="B112" t="n">
-        <v>105594</v>
+        <v>105615</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11467,32 +11467,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128118879</v>
+        <v>128118888</v>
       </c>
       <c r="B113" t="n">
-        <v>98571</v>
+        <v>91482</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>708260</v>
+        <v>708218</v>
       </c>
       <c r="R113" t="n">
-        <v>7294439</v>
+        <v>7294252</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11540,11 +11540,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -11562,39 +11557,39 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128118888</v>
+        <v>128118879</v>
       </c>
       <c r="B114" t="n">
-        <v>91470</v>
+        <v>98585</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11604,10 +11599,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>708218</v>
+        <v>708260</v>
       </c>
       <c r="R114" t="n">
-        <v>7294252</v>
+        <v>7294439</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11642,6 +11637,11 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -11669,7 +11669,7 @@
         <v>128118843</v>
       </c>
       <c r="B115" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>128118836</v>
       </c>
       <c r="B116" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>128118875</v>
       </c>
       <c r="B117" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11962,32 +11962,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128118862</v>
+        <v>128118898</v>
       </c>
       <c r="B118" t="n">
-        <v>58055</v>
+        <v>79087</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>708424</v>
+        <v>708249</v>
       </c>
       <c r="R118" t="n">
-        <v>7294076</v>
+        <v>7294216</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12052,17 +12052,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128118890</v>
+        <v>128118894</v>
       </c>
       <c r="B119" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12070,21 +12070,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>708232</v>
+        <v>708443</v>
       </c>
       <c r="R119" t="n">
-        <v>7294415</v>
+        <v>7294180</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12156,10 +12156,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128118894</v>
+        <v>128118890</v>
       </c>
       <c r="B120" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12167,21 +12167,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12191,10 +12191,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>708443</v>
+        <v>708232</v>
       </c>
       <c r="R120" t="n">
-        <v>7294180</v>
+        <v>7294415</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12253,32 +12253,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128118898</v>
+        <v>128118862</v>
       </c>
       <c r="B121" t="n">
-        <v>79083</v>
+        <v>58059</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>708249</v>
+        <v>708424</v>
       </c>
       <c r="R121" t="n">
-        <v>7294216</v>
+        <v>7294076</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12353,7 +12353,7 @@
         <v>128118883</v>
       </c>
       <c r="B122" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>128118889</v>
       </c>
       <c r="B123" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128118849</v>
+        <v>128118845</v>
       </c>
       <c r="B124" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>708250</v>
+        <v>708477</v>
       </c>
       <c r="R124" t="n">
-        <v>7294430</v>
+        <v>7294616</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -12641,10 +12641,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128118845</v>
+        <v>128118849</v>
       </c>
       <c r="B125" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>708477</v>
+        <v>708250</v>
       </c>
       <c r="R125" t="n">
-        <v>7294616</v>
+        <v>7294430</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128118839</v>
+        <v>128118899</v>
       </c>
       <c r="B126" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>708424</v>
+        <v>708214</v>
       </c>
       <c r="R126" t="n">
-        <v>7294672</v>
+        <v>7294309</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -12828,39 +12828,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128118899</v>
+        <v>128118839</v>
       </c>
       <c r="B127" t="n">
-        <v>79083</v>
+        <v>80221</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>708214</v>
+        <v>708424</v>
       </c>
       <c r="R127" t="n">
-        <v>7294309</v>
+        <v>7294672</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -12935,7 +12935,7 @@
         <v>128118882</v>
       </c>
       <c r="B128" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>128118902</v>
       </c>
       <c r="B129" t="n">
-        <v>91713</v>
+        <v>91725</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>128118887</v>
       </c>
       <c r="B130" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>128118846</v>
       </c>
       <c r="B131" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13320,32 +13320,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128118857</v>
+        <v>128118903</v>
       </c>
       <c r="B132" t="n">
-        <v>80188</v>
+        <v>98502</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>708335</v>
+        <v>708233</v>
       </c>
       <c r="R132" t="n">
-        <v>7294032</v>
+        <v>7294206</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13410,39 +13410,39 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128118903</v>
+        <v>128118880</v>
       </c>
       <c r="B133" t="n">
-        <v>98488</v>
+        <v>98585</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>708233</v>
+        <v>708290</v>
       </c>
       <c r="R133" t="n">
-        <v>7294206</v>
+        <v>7294490</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
         <v>128118869</v>
       </c>
       <c r="B134" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13616,32 +13616,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128118880</v>
+        <v>128118857</v>
       </c>
       <c r="B135" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>708290</v>
+        <v>708335</v>
       </c>
       <c r="R135" t="n">
-        <v>7294490</v>
+        <v>7294032</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -13716,7 +13716,7 @@
         <v>128118908</v>
       </c>
       <c r="B136" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>128118831</v>
       </c>
       <c r="B137" t="n">
-        <v>105594</v>
+        <v>105615</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>128118850</v>
       </c>
       <c r="B138" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128116247</v>
+        <v>128116278</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>79166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708354</v>
+        <v>708407</v>
       </c>
       <c r="R5" t="n">
-        <v>7294074</v>
+        <v>7294657</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128116278</v>
+        <v>128116283</v>
       </c>
       <c r="B6" t="n">
-        <v>79166</v>
+        <v>91460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708407</v>
+        <v>708522</v>
       </c>
       <c r="R6" t="n">
-        <v>7294657</v>
+        <v>7294412</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128116283</v>
+        <v>128116247</v>
       </c>
       <c r="B7" t="n">
-        <v>91460</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708522</v>
+        <v>708354</v>
       </c>
       <c r="R7" t="n">
-        <v>7294412</v>
+        <v>7294074</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116246</v>
+        <v>128116290</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>91478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708396</v>
+        <v>708225</v>
       </c>
       <c r="R8" t="n">
-        <v>7294100</v>
+        <v>7294123</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116268</v>
+        <v>128116246</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708226</v>
+        <v>708396</v>
       </c>
       <c r="R9" t="n">
-        <v>7294304</v>
+        <v>7294100</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116290</v>
+        <v>128116306</v>
       </c>
       <c r="B10" t="n">
-        <v>91478</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708225</v>
+        <v>708199</v>
       </c>
       <c r="R10" t="n">
-        <v>7294123</v>
+        <v>7294151</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116306</v>
+        <v>128116307</v>
       </c>
       <c r="B11" t="n">
         <v>79087</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708199</v>
+        <v>708223</v>
       </c>
       <c r="R11" t="n">
-        <v>7294151</v>
+        <v>7294146</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128116307</v>
+        <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708223</v>
+        <v>708226</v>
       </c>
       <c r="R12" t="n">
-        <v>7294146</v>
+        <v>7294304</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116281</v>
+        <v>128116259</v>
       </c>
       <c r="B17" t="n">
-        <v>56871</v>
+        <v>80192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708480</v>
+        <v>708415</v>
       </c>
       <c r="R17" t="n">
-        <v>7294127</v>
+        <v>7294078</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>56871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R20" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116255</v>
+        <v>128116274</v>
       </c>
       <c r="B29" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708407</v>
+        <v>708243</v>
       </c>
       <c r="R29" t="n">
-        <v>7294680</v>
+        <v>7294417</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116274</v>
+        <v>128116248</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708243</v>
+        <v>708292</v>
       </c>
       <c r="R30" t="n">
-        <v>7294417</v>
+        <v>7294045</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116248</v>
+        <v>128116255</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>80192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708292</v>
+        <v>708407</v>
       </c>
       <c r="R31" t="n">
-        <v>7294045</v>
+        <v>7294680</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128116301</v>
+        <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>92038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708375</v>
+        <v>708432</v>
       </c>
       <c r="R33" t="n">
-        <v>7294094</v>
+        <v>7294694</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3753,6 +3753,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3779,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128116264</v>
+        <v>128116301</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708489</v>
+        <v>708375</v>
       </c>
       <c r="R34" t="n">
-        <v>7294661</v>
+        <v>7294094</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128116313</v>
+        <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>92038</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708432</v>
+        <v>708489</v>
       </c>
       <c r="R35" t="n">
-        <v>7294694</v>
+        <v>7294661</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -9430,10 +9430,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118896</v>
+        <v>128118884</v>
       </c>
       <c r="B92" t="n">
-        <v>79087</v>
+        <v>79166</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9441,21 +9441,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708411</v>
+        <v>708477</v>
       </c>
       <c r="R92" t="n">
-        <v>7294054</v>
+        <v>7294616</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9520,39 +9520,39 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128118868</v>
+        <v>128118896</v>
       </c>
       <c r="B93" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708494</v>
+        <v>708411</v>
       </c>
       <c r="R93" t="n">
-        <v>7294519</v>
+        <v>7294054</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9617,39 +9617,39 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128118829</v>
+        <v>128118868</v>
       </c>
       <c r="B94" t="n">
-        <v>105615</v>
+        <v>98585</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708299</v>
+        <v>708494</v>
       </c>
       <c r="R94" t="n">
-        <v>7294038</v>
+        <v>7294519</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9721,32 +9721,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128118884</v>
+        <v>128118854</v>
       </c>
       <c r="B95" t="n">
-        <v>79166</v>
+        <v>97460</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708477</v>
+        <v>708246</v>
       </c>
       <c r="R95" t="n">
-        <v>7294616</v>
+        <v>7294430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9818,10 +9818,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128118854</v>
+        <v>128118829</v>
       </c>
       <c r="B96" t="n">
-        <v>97460</v>
+        <v>105615</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9829,21 +9829,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708246</v>
+        <v>708299</v>
       </c>
       <c r="R96" t="n">
-        <v>7294430</v>
+        <v>7294038</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -13320,32 +13320,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128118903</v>
+        <v>128118857</v>
       </c>
       <c r="B132" t="n">
-        <v>98502</v>
+        <v>80192</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>708233</v>
+        <v>708335</v>
       </c>
       <c r="R132" t="n">
-        <v>7294206</v>
+        <v>7294032</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13410,39 +13410,39 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128118880</v>
+        <v>128118903</v>
       </c>
       <c r="B133" t="n">
-        <v>98585</v>
+        <v>98502</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>708290</v>
+        <v>708233</v>
       </c>
       <c r="R133" t="n">
-        <v>7294490</v>
+        <v>7294206</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -13507,14 +13507,14 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128118869</v>
+        <v>128118880</v>
       </c>
       <c r="B134" t="n">
         <v>98585</v>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>708487</v>
+        <v>708290</v>
       </c>
       <c r="R134" t="n">
-        <v>7294472</v>
+        <v>7294490</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -13585,11 +13585,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13616,32 +13611,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128118857</v>
+        <v>128118869</v>
       </c>
       <c r="B135" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13651,10 +13646,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>708335</v>
+        <v>708487</v>
       </c>
       <c r="R135" t="n">
-        <v>7294032</v>
+        <v>7294472</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -13687,6 +13682,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD135" t="b">

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116290</v>
+        <v>128116246</v>
       </c>
       <c r="B8" t="n">
-        <v>91478</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708225</v>
+        <v>708396</v>
       </c>
       <c r="R8" t="n">
-        <v>7294123</v>
+        <v>7294100</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116246</v>
+        <v>128116268</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708396</v>
+        <v>708226</v>
       </c>
       <c r="R9" t="n">
-        <v>7294100</v>
+        <v>7294304</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128116306</v>
+        <v>128116290</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>91478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708199</v>
+        <v>708225</v>
       </c>
       <c r="R10" t="n">
-        <v>7294151</v>
+        <v>7294123</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116307</v>
+        <v>128116306</v>
       </c>
       <c r="B11" t="n">
         <v>79087</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708223</v>
+        <v>708199</v>
       </c>
       <c r="R11" t="n">
-        <v>7294146</v>
+        <v>7294151</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128116268</v>
+        <v>128116307</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708226</v>
+        <v>708223</v>
       </c>
       <c r="R12" t="n">
-        <v>7294304</v>
+        <v>7294146</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116258</v>
+        <v>128116249</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708471</v>
+        <v>708207</v>
       </c>
       <c r="R14" t="n">
-        <v>7294139</v>
+        <v>7294133</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116249</v>
+        <v>128116304</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708207</v>
+        <v>708225</v>
       </c>
       <c r="R15" t="n">
-        <v>7294133</v>
+        <v>7294108</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116304</v>
+        <v>128116258</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708225</v>
+        <v>708471</v>
       </c>
       <c r="R16" t="n">
-        <v>7294108</v>
+        <v>7294139</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B17" t="n">
-        <v>80192</v>
+        <v>56871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R17" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116281</v>
+        <v>128116259</v>
       </c>
       <c r="B20" t="n">
-        <v>56871</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708480</v>
+        <v>708415</v>
       </c>
       <c r="R20" t="n">
-        <v>7294127</v>
+        <v>7294078</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R29" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116248</v>
+        <v>128116274</v>
       </c>
       <c r="B30" t="n">
-        <v>57686</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708292</v>
+        <v>708243</v>
       </c>
       <c r="R30" t="n">
-        <v>7294045</v>
+        <v>7294417</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116255</v>
+        <v>128116248</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708407</v>
+        <v>708292</v>
       </c>
       <c r="R31" t="n">
-        <v>7294680</v>
+        <v>7294045</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128116299</v>
+        <v>128116262</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>57793</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708462</v>
+        <v>708295</v>
       </c>
       <c r="R36" t="n">
-        <v>7294126</v>
+        <v>7294459</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116309</v>
+        <v>128116299</v>
       </c>
       <c r="B37" t="n">
         <v>79087</v>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708284</v>
+        <v>708462</v>
       </c>
       <c r="R37" t="n">
-        <v>7294509</v>
+        <v>7294126</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116308</v>
+        <v>128116309</v>
       </c>
       <c r="B38" t="n">
         <v>79087</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708216</v>
+        <v>708284</v>
       </c>
       <c r="R38" t="n">
-        <v>7294159</v>
+        <v>7294509</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128116293</v>
+        <v>128116308</v>
       </c>
       <c r="B39" t="n">
-        <v>91482</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708521</v>
+        <v>708216</v>
       </c>
       <c r="R39" t="n">
-        <v>7294413</v>
+        <v>7294159</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116262</v>
+        <v>128116293</v>
       </c>
       <c r="B40" t="n">
-        <v>57793</v>
+        <v>91482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708295</v>
+        <v>708521</v>
       </c>
       <c r="R40" t="n">
-        <v>7294459</v>
+        <v>7294413</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128116288</v>
+        <v>128116296</v>
       </c>
       <c r="B46" t="n">
-        <v>91478</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708485</v>
+        <v>708450</v>
       </c>
       <c r="R46" t="n">
-        <v>7294476</v>
+        <v>7294389</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128116296</v>
+        <v>128116288</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>91478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708450</v>
+        <v>708485</v>
       </c>
       <c r="R47" t="n">
-        <v>7294389</v>
+        <v>7294476</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116305</v>
+        <v>128116243</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>57849</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708209</v>
+        <v>708329</v>
       </c>
       <c r="R53" t="n">
-        <v>7294140</v>
+        <v>7294658</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116292</v>
+        <v>128116305</v>
       </c>
       <c r="B54" t="n">
-        <v>91482</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708500</v>
+        <v>708209</v>
       </c>
       <c r="R54" t="n">
-        <v>7294658</v>
+        <v>7294140</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116310</v>
+        <v>128116292</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>91482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708426</v>
+        <v>708500</v>
       </c>
       <c r="R55" t="n">
-        <v>7294468</v>
+        <v>7294658</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116240</v>
+        <v>128116310</v>
       </c>
       <c r="B56" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708376</v>
+        <v>708426</v>
       </c>
       <c r="R56" t="n">
-        <v>7294699</v>
+        <v>7294468</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116254</v>
+        <v>128116240</v>
       </c>
       <c r="B57" t="n">
-        <v>80192</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708400</v>
+        <v>708376</v>
       </c>
       <c r="R57" t="n">
-        <v>7294674</v>
+        <v>7294699</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116260</v>
+        <v>128116254</v>
       </c>
       <c r="B58" t="n">
         <v>80192</v>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708208</v>
+        <v>708400</v>
       </c>
       <c r="R58" t="n">
-        <v>7294348</v>
+        <v>7294674</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,7 +6209,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116256</v>
+        <v>128116260</v>
       </c>
       <c r="B59" t="n">
         <v>80192</v>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708495</v>
+        <v>708208</v>
       </c>
       <c r="R59" t="n">
-        <v>7294673</v>
+        <v>7294348</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6306,10 +6306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116243</v>
+        <v>128116256</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>80192</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708329</v>
+        <v>708495</v>
       </c>
       <c r="R60" t="n">
-        <v>7294658</v>
+        <v>7294673</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7284,7 +7284,7 @@
         <v>128118838</v>
       </c>
       <c r="B70" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7378,32 +7378,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118867</v>
+        <v>128118837</v>
       </c>
       <c r="B71" t="n">
-        <v>98585</v>
+        <v>56880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708482</v>
+        <v>708415</v>
       </c>
       <c r="R71" t="n">
-        <v>7294514</v>
+        <v>7294151</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7449,6 +7449,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>3st honor</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7475,32 +7480,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128118866</v>
+        <v>128118893</v>
       </c>
       <c r="B72" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7510,10 +7515,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708412</v>
+        <v>708463</v>
       </c>
       <c r="R72" t="n">
-        <v>7294653</v>
+        <v>7294191</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7548,11 +7553,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7570,39 +7570,39 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128118881</v>
+        <v>128118834</v>
       </c>
       <c r="B73" t="n">
-        <v>98585</v>
+        <v>91431</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708273</v>
+        <v>708433</v>
       </c>
       <c r="R73" t="n">
-        <v>7294469</v>
+        <v>7294555</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7648,11 +7648,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7679,32 +7674,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118837</v>
+        <v>128118856</v>
       </c>
       <c r="B74" t="n">
-        <v>56880</v>
+        <v>80194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7714,10 +7709,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708415</v>
+        <v>708459</v>
       </c>
       <c r="R74" t="n">
-        <v>7294151</v>
+        <v>7294618</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7750,11 +7745,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>3st honor</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7781,10 +7771,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128118863</v>
+        <v>128118840</v>
       </c>
       <c r="B75" t="n">
-        <v>58059</v>
+        <v>80223</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7792,21 +7782,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7816,10 +7806,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708340</v>
+        <v>708415</v>
       </c>
       <c r="R75" t="n">
-        <v>7294657</v>
+        <v>7294056</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7881,7 +7871,7 @@
         <v>128118833</v>
       </c>
       <c r="B76" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7975,10 +7965,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118834</v>
+        <v>128118863</v>
       </c>
       <c r="B77" t="n">
-        <v>91429</v>
+        <v>58059</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7986,21 +7976,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8010,10 +8000,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708433</v>
+        <v>708340</v>
       </c>
       <c r="R77" t="n">
-        <v>7294555</v>
+        <v>7294657</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8072,32 +8062,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128118893</v>
+        <v>128118867</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>98588</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8107,10 +8097,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708463</v>
+        <v>708482</v>
       </c>
       <c r="R78" t="n">
-        <v>7294191</v>
+        <v>7294514</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8162,39 +8152,39 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128118856</v>
+        <v>128118866</v>
       </c>
       <c r="B79" t="n">
-        <v>80192</v>
+        <v>98588</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8194,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708459</v>
+        <v>708412</v>
       </c>
       <c r="R79" t="n">
-        <v>7294618</v>
+        <v>7294653</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8240,6 +8230,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8266,32 +8261,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128118840</v>
+        <v>128118881</v>
       </c>
       <c r="B80" t="n">
-        <v>80221</v>
+        <v>98588</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8296,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708415</v>
+        <v>708273</v>
       </c>
       <c r="R80" t="n">
-        <v>7294056</v>
+        <v>7294469</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8337,6 +8332,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8366,7 +8366,7 @@
         <v>128118900</v>
       </c>
       <c r="B81" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
         <v>128118848</v>
       </c>
       <c r="B82" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>128118901</v>
       </c>
       <c r="B83" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8754,7 +8754,7 @@
         <v>128118873</v>
       </c>
       <c r="B85" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>128118877</v>
       </c>
       <c r="B86" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>128118844</v>
       </c>
       <c r="B87" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>128118855</v>
       </c>
       <c r="B88" t="n">
-        <v>79111</v>
+        <v>79113</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>128118876</v>
       </c>
       <c r="B89" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>128118870</v>
       </c>
       <c r="B90" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>128118885</v>
       </c>
       <c r="B91" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9430,32 +9430,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118884</v>
+        <v>128118829</v>
       </c>
       <c r="B92" t="n">
-        <v>79166</v>
+        <v>105627</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>864</v>
+        <v>221725</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708477</v>
+        <v>708299</v>
       </c>
       <c r="R92" t="n">
-        <v>7294616</v>
+        <v>7294038</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9527,32 +9527,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128118896</v>
+        <v>128118854</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>97462</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708411</v>
+        <v>708246</v>
       </c>
       <c r="R93" t="n">
-        <v>7294054</v>
+        <v>7294430</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9617,39 +9617,39 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128118868</v>
+        <v>128118884</v>
       </c>
       <c r="B94" t="n">
-        <v>98585</v>
+        <v>79168</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708494</v>
+        <v>708477</v>
       </c>
       <c r="R94" t="n">
-        <v>7294519</v>
+        <v>7294616</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9721,32 +9721,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128118854</v>
+        <v>128118896</v>
       </c>
       <c r="B95" t="n">
-        <v>97460</v>
+        <v>79089</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708246</v>
+        <v>708411</v>
       </c>
       <c r="R95" t="n">
-        <v>7294430</v>
+        <v>7294054</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9811,39 +9811,39 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128118829</v>
+        <v>128118868</v>
       </c>
       <c r="B96" t="n">
-        <v>105615</v>
+        <v>98588</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708299</v>
+        <v>708494</v>
       </c>
       <c r="R96" t="n">
-        <v>7294038</v>
+        <v>7294519</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9915,32 +9915,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128118892</v>
+        <v>128118878</v>
       </c>
       <c r="B97" t="n">
-        <v>79087</v>
+        <v>98588</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9950,10 +9950,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>708476</v>
+        <v>708258</v>
       </c>
       <c r="R97" t="n">
-        <v>7294478</v>
+        <v>7294447</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10005,39 +10005,39 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128118878</v>
+        <v>128118892</v>
       </c>
       <c r="B98" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>708258</v>
+        <v>708476</v>
       </c>
       <c r="R98" t="n">
-        <v>7294447</v>
+        <v>7294478</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10112,7 +10112,7 @@
         <v>128118909</v>
       </c>
       <c r="B99" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10199,17 +10199,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128118861</v>
+        <v>128118860</v>
       </c>
       <c r="B100" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>708259</v>
+        <v>708188</v>
       </c>
       <c r="R100" t="n">
-        <v>7294452</v>
+        <v>7294093</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10303,10 +10303,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128118860</v>
+        <v>128118861</v>
       </c>
       <c r="B101" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10338,10 +10338,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>708188</v>
+        <v>708259</v>
       </c>
       <c r="R101" t="n">
-        <v>7294093</v>
+        <v>7294452</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10403,7 +10403,7 @@
         <v>128118847</v>
       </c>
       <c r="B102" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10497,10 +10497,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128118895</v>
+        <v>128118886</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10508,21 +10508,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>708412</v>
+        <v>708480</v>
       </c>
       <c r="R103" t="n">
-        <v>7294150</v>
+        <v>7294478</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10587,17 +10587,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128118886</v>
+        <v>128118895</v>
       </c>
       <c r="B104" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10605,21 +10605,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>708480</v>
+        <v>708412</v>
       </c>
       <c r="R104" t="n">
-        <v>7294478</v>
+        <v>7294150</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10684,17 +10684,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128118841</v>
+        <v>128118912</v>
       </c>
       <c r="B105" t="n">
-        <v>80221</v>
+        <v>80229</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>708337</v>
+        <v>708262</v>
       </c>
       <c r="R105" t="n">
-        <v>7294039</v>
+        <v>7294457</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10781,17 +10781,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128118835</v>
+        <v>128118841</v>
       </c>
       <c r="B106" t="n">
-        <v>58548</v>
+        <v>80223</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10799,21 +10799,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>208249</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>708445</v>
+        <v>708337</v>
       </c>
       <c r="R106" t="n">
-        <v>7294644</v>
+        <v>7294039</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10885,32 +10885,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128118872</v>
+        <v>128118906</v>
       </c>
       <c r="B107" t="n">
-        <v>98585</v>
+        <v>80229</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>708200</v>
+        <v>708432</v>
       </c>
       <c r="R107" t="n">
-        <v>7294326</v>
+        <v>7294676</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -10975,39 +10975,39 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128118874</v>
+        <v>128118853</v>
       </c>
       <c r="B108" t="n">
-        <v>98585</v>
+        <v>97462</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>708235</v>
+        <v>708228</v>
       </c>
       <c r="R108" t="n">
-        <v>7294371</v>
+        <v>7294377</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11079,32 +11079,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128118853</v>
+        <v>128118872</v>
       </c>
       <c r="B109" t="n">
-        <v>97460</v>
+        <v>98588</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>708228</v>
+        <v>708200</v>
       </c>
       <c r="R109" t="n">
-        <v>7294377</v>
+        <v>7294326</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11176,32 +11176,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128118912</v>
+        <v>128118874</v>
       </c>
       <c r="B110" t="n">
-        <v>80227</v>
+        <v>98588</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>708262</v>
+        <v>708235</v>
       </c>
       <c r="R110" t="n">
-        <v>7294457</v>
+        <v>7294371</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128118906</v>
+        <v>128118835</v>
       </c>
       <c r="B111" t="n">
-        <v>80227</v>
+        <v>58548</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>208249</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>708432</v>
+        <v>708445</v>
       </c>
       <c r="R111" t="n">
-        <v>7294676</v>
+        <v>7294644</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11373,7 +11373,7 @@
         <v>128118832</v>
       </c>
       <c r="B112" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>128118888</v>
       </c>
       <c r="B113" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11564,32 +11564,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128118879</v>
+        <v>128118843</v>
       </c>
       <c r="B114" t="n">
-        <v>98585</v>
+        <v>98609</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>708260</v>
+        <v>708496</v>
       </c>
       <c r="R114" t="n">
-        <v>7294439</v>
+        <v>7294626</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Stort bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11666,32 +11666,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128118843</v>
+        <v>128118879</v>
       </c>
       <c r="B115" t="n">
-        <v>98606</v>
+        <v>98588</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>708496</v>
+        <v>708260</v>
       </c>
       <c r="R115" t="n">
-        <v>7294626</v>
+        <v>7294439</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11768,32 +11768,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128118836</v>
+        <v>128118875</v>
       </c>
       <c r="B116" t="n">
-        <v>58548</v>
+        <v>98588</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>708203</v>
+        <v>708230</v>
       </c>
       <c r="R116" t="n">
-        <v>7294324</v>
+        <v>7294377</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128118875</v>
+        <v>128118836</v>
       </c>
       <c r="B117" t="n">
-        <v>98585</v>
+        <v>58548</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>708230</v>
+        <v>708203</v>
       </c>
       <c r="R117" t="n">
-        <v>7294377</v>
+        <v>7294324</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -11962,10 +11962,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128118898</v>
+        <v>128118894</v>
       </c>
       <c r="B118" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>708249</v>
+        <v>708443</v>
       </c>
       <c r="R118" t="n">
-        <v>7294216</v>
+        <v>7294180</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12052,17 +12052,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128118894</v>
+        <v>128118898</v>
       </c>
       <c r="B119" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>708443</v>
+        <v>708249</v>
       </c>
       <c r="R119" t="n">
-        <v>7294180</v>
+        <v>7294216</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12159,7 +12159,7 @@
         <v>128118890</v>
       </c>
       <c r="B120" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12350,32 +12350,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128118883</v>
+        <v>128118889</v>
       </c>
       <c r="B122" t="n">
-        <v>98585</v>
+        <v>91484</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12385,10 +12385,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>708436</v>
+        <v>708192</v>
       </c>
       <c r="R122" t="n">
-        <v>7294589</v>
+        <v>7294318</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12440,39 +12440,39 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128118889</v>
+        <v>128118883</v>
       </c>
       <c r="B123" t="n">
-        <v>91482</v>
+        <v>98588</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>708192</v>
+        <v>708436</v>
       </c>
       <c r="R123" t="n">
-        <v>7294318</v>
+        <v>7294589</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -12547,7 +12547,7 @@
         <v>128118845</v>
       </c>
       <c r="B124" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>128118849</v>
       </c>
       <c r="B125" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>128118899</v>
       </c>
       <c r="B126" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12828,39 +12828,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128118839</v>
+        <v>128118882</v>
       </c>
       <c r="B127" t="n">
-        <v>80221</v>
+        <v>98588</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>708424</v>
+        <v>708290</v>
       </c>
       <c r="R127" t="n">
-        <v>7294672</v>
+        <v>7294501</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -12932,10 +12932,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128118882</v>
+        <v>128118902</v>
       </c>
       <c r="B128" t="n">
-        <v>98585</v>
+        <v>91727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12943,21 +12943,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>708290</v>
+        <v>708202</v>
       </c>
       <c r="R128" t="n">
-        <v>7294501</v>
+        <v>7294326</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13022,39 +13022,39 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128118902</v>
+        <v>128118839</v>
       </c>
       <c r="B129" t="n">
-        <v>91725</v>
+        <v>80223</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>708202</v>
+        <v>708424</v>
       </c>
       <c r="R129" t="n">
-        <v>7294326</v>
+        <v>7294672</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13119,39 +13119,39 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128118887</v>
+        <v>128118846</v>
       </c>
       <c r="B130" t="n">
-        <v>91482</v>
+        <v>98609</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13161,10 +13161,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>708488</v>
+        <v>708469</v>
       </c>
       <c r="R130" t="n">
-        <v>7294468</v>
+        <v>7294524</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13216,39 +13216,39 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128118846</v>
+        <v>128118887</v>
       </c>
       <c r="B131" t="n">
-        <v>98606</v>
+        <v>91484</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>708469</v>
+        <v>708488</v>
       </c>
       <c r="R131" t="n">
-        <v>7294524</v>
+        <v>7294468</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13323,7 +13323,7 @@
         <v>128118857</v>
       </c>
       <c r="B132" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>128118903</v>
       </c>
       <c r="B133" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
         <v>128118880</v>
       </c>
       <c r="B134" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>128118869</v>
       </c>
       <c r="B135" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>128118908</v>
       </c>
       <c r="B136" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -13813,7 +13813,7 @@
         <v>128118831</v>
       </c>
       <c r="B137" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>128118850</v>
       </c>
       <c r="B138" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128116294</v>
+        <v>128116295</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708521</v>
+        <v>708340</v>
       </c>
       <c r="R2" t="n">
-        <v>7294393</v>
+        <v>7294066</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128116295</v>
+        <v>128116294</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708340</v>
+        <v>708521</v>
       </c>
       <c r="R3" t="n">
-        <v>7294066</v>
+        <v>7294393</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -872,7 +872,7 @@
         <v>128116297</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128116278</v>
+        <v>128116247</v>
       </c>
       <c r="B5" t="n">
-        <v>79166</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708407</v>
+        <v>708354</v>
       </c>
       <c r="R5" t="n">
-        <v>7294657</v>
+        <v>7294074</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128116283</v>
+        <v>128116278</v>
       </c>
       <c r="B6" t="n">
-        <v>91460</v>
+        <v>79168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708522</v>
+        <v>708407</v>
       </c>
       <c r="R6" t="n">
-        <v>7294412</v>
+        <v>7294657</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128116247</v>
+        <v>128116283</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>91462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708354</v>
+        <v>708522</v>
       </c>
       <c r="R7" t="n">
-        <v>7294074</v>
+        <v>7294412</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128116246</v>
+        <v>128116306</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708396</v>
+        <v>708199</v>
       </c>
       <c r="R8" t="n">
-        <v>7294100</v>
+        <v>7294151</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128116268</v>
+        <v>128116307</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708226</v>
+        <v>708223</v>
       </c>
       <c r="R9" t="n">
-        <v>7294304</v>
+        <v>7294146</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1454,7 +1454,7 @@
         <v>128116290</v>
       </c>
       <c r="B10" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128116306</v>
+        <v>128116246</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708199</v>
+        <v>708396</v>
       </c>
       <c r="R11" t="n">
-        <v>7294151</v>
+        <v>7294100</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128116307</v>
+        <v>128116268</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708223</v>
+        <v>708226</v>
       </c>
       <c r="R12" t="n">
-        <v>7294146</v>
+        <v>7294304</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116286</v>
+        <v>128116249</v>
       </c>
       <c r="B13" t="n">
-        <v>91478</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708482</v>
+        <v>708207</v>
       </c>
       <c r="R13" t="n">
-        <v>7294632</v>
+        <v>7294133</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116249</v>
+        <v>128116286</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>91480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708207</v>
+        <v>708482</v>
       </c>
       <c r="R14" t="n">
-        <v>7294133</v>
+        <v>7294632</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1939,7 +1939,7 @@
         <v>128116304</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128116258</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128116281</v>
+        <v>128116259</v>
       </c>
       <c r="B17" t="n">
-        <v>56871</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708480</v>
+        <v>708415</v>
       </c>
       <c r="R17" t="n">
-        <v>7294127</v>
+        <v>7294078</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2230,7 +2230,7 @@
         <v>128116312</v>
       </c>
       <c r="B18" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128116253</v>
       </c>
       <c r="B19" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128116259</v>
+        <v>128116281</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>56871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708415</v>
+        <v>708480</v>
       </c>
       <c r="R20" t="n">
-        <v>7294078</v>
+        <v>7294127</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2521,7 +2521,7 @@
         <v>128116302</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128116298</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128116279</v>
+        <v>128116245</v>
       </c>
       <c r="B23" t="n">
-        <v>79166</v>
+        <v>57686</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708215</v>
+        <v>708491</v>
       </c>
       <c r="R23" t="n">
-        <v>7294156</v>
+        <v>7294463</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128116315</v>
+        <v>128116251</v>
       </c>
       <c r="B24" t="n">
-        <v>92038</v>
+        <v>97462</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708330</v>
+        <v>708490</v>
       </c>
       <c r="R24" t="n">
-        <v>7294664</v>
+        <v>7294651</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128116285</v>
+        <v>128116315</v>
       </c>
       <c r="B25" t="n">
-        <v>91460</v>
+        <v>92040</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708246</v>
+        <v>708330</v>
       </c>
       <c r="R25" t="n">
-        <v>7294412</v>
+        <v>7294664</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128116245</v>
+        <v>128116285</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>91462</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708491</v>
+        <v>708246</v>
       </c>
       <c r="R26" t="n">
-        <v>7294463</v>
+        <v>7294412</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128116251</v>
+        <v>128116279</v>
       </c>
       <c r="B27" t="n">
-        <v>97460</v>
+        <v>79168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708490</v>
+        <v>708215</v>
       </c>
       <c r="R27" t="n">
-        <v>7294651</v>
+        <v>7294156</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128116289</v>
+        <v>128116248</v>
       </c>
       <c r="B28" t="n">
-        <v>91478</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708501</v>
+        <v>708292</v>
       </c>
       <c r="R28" t="n">
-        <v>7294429</v>
+        <v>7294045</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128116255</v>
+        <v>128116289</v>
       </c>
       <c r="B29" t="n">
-        <v>80192</v>
+        <v>91480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708407</v>
+        <v>708501</v>
       </c>
       <c r="R29" t="n">
-        <v>7294680</v>
+        <v>7294429</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128116274</v>
+        <v>128116255</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708243</v>
+        <v>708407</v>
       </c>
       <c r="R30" t="n">
-        <v>7294417</v>
+        <v>7294680</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128116248</v>
+        <v>128116274</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708292</v>
+        <v>708243</v>
       </c>
       <c r="R31" t="n">
-        <v>7294045</v>
+        <v>7294417</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3588,7 +3588,7 @@
         <v>128116300</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128116313</v>
       </c>
       <c r="B33" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>128116301</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>128116264</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128116299</v>
+        <v>128116270</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708462</v>
+        <v>708197</v>
       </c>
       <c r="R37" t="n">
-        <v>7294126</v>
+        <v>7294331</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128116309</v>
+        <v>128116293</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708284</v>
+        <v>708521</v>
       </c>
       <c r="R38" t="n">
-        <v>7294509</v>
+        <v>7294413</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4272,7 +4272,7 @@
         <v>128116308</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128116293</v>
+        <v>128116309</v>
       </c>
       <c r="B40" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708521</v>
+        <v>708284</v>
       </c>
       <c r="R40" t="n">
-        <v>7294413</v>
+        <v>7294509</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128116270</v>
+        <v>128116299</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708197</v>
+        <v>708462</v>
       </c>
       <c r="R41" t="n">
-        <v>7294331</v>
+        <v>7294126</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128116239</v>
+        <v>128116265</v>
       </c>
       <c r="B42" t="n">
-        <v>91429</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708194</v>
+        <v>708523</v>
       </c>
       <c r="R42" t="n">
-        <v>7294336</v>
+        <v>7294599</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128116303</v>
+        <v>128116239</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>91431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708288</v>
+        <v>708194</v>
       </c>
       <c r="R43" t="n">
-        <v>7294045</v>
+        <v>7294336</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4754,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128116265</v>
+        <v>128116303</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708523</v>
+        <v>708288</v>
       </c>
       <c r="R44" t="n">
-        <v>7294599</v>
+        <v>7294045</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4854,7 +4854,7 @@
         <v>128116252</v>
       </c>
       <c r="B45" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128116296</v>
+        <v>128116288</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>91480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708450</v>
+        <v>708485</v>
       </c>
       <c r="R46" t="n">
-        <v>7294389</v>
+        <v>7294476</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128116288</v>
+        <v>128116296</v>
       </c>
       <c r="B47" t="n">
-        <v>91478</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708485</v>
+        <v>708450</v>
       </c>
       <c r="R47" t="n">
-        <v>7294476</v>
+        <v>7294389</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5145,7 +5145,7 @@
         <v>128116272</v>
       </c>
       <c r="B48" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116311</v>
+        <v>128116314</v>
       </c>
       <c r="B49" t="n">
-        <v>82946</v>
+        <v>92040</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R49" t="n">
-        <v>7294070</v>
+        <v>7294415</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,32 +5336,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B50" t="n">
-        <v>92038</v>
+        <v>82948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R50" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5436,7 +5436,7 @@
         <v>128116275</v>
       </c>
       <c r="B51" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128116273</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128116243</v>
+        <v>128116240</v>
       </c>
       <c r="B53" t="n">
-        <v>57849</v>
+        <v>79708</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708329</v>
+        <v>708376</v>
       </c>
       <c r="R53" t="n">
-        <v>7294658</v>
+        <v>7294699</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128116305</v>
+        <v>128116310</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708209</v>
+        <v>708426</v>
       </c>
       <c r="R54" t="n">
-        <v>7294140</v>
+        <v>7294468</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128116292</v>
+        <v>128116254</v>
       </c>
       <c r="B55" t="n">
-        <v>91482</v>
+        <v>80194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708500</v>
+        <v>708400</v>
       </c>
       <c r="R55" t="n">
-        <v>7294658</v>
+        <v>7294674</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128116310</v>
+        <v>128116260</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708426</v>
+        <v>708208</v>
       </c>
       <c r="R56" t="n">
-        <v>7294468</v>
+        <v>7294348</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128116240</v>
+        <v>128116305</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708376</v>
+        <v>708209</v>
       </c>
       <c r="R57" t="n">
-        <v>7294699</v>
+        <v>7294140</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6112,10 +6112,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128116254</v>
+        <v>128116256</v>
       </c>
       <c r="B58" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708400</v>
+        <v>708495</v>
       </c>
       <c r="R58" t="n">
-        <v>7294674</v>
+        <v>7294673</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6209,10 +6209,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128116260</v>
+        <v>128116243</v>
       </c>
       <c r="B59" t="n">
-        <v>80192</v>
+        <v>57849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708208</v>
+        <v>708329</v>
       </c>
       <c r="R59" t="n">
-        <v>7294348</v>
+        <v>7294658</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6306,32 +6306,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128116256</v>
+        <v>128116277</v>
       </c>
       <c r="B60" t="n">
-        <v>80192</v>
+        <v>98591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708495</v>
+        <v>708269</v>
       </c>
       <c r="R60" t="n">
-        <v>7294673</v>
+        <v>7294506</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6377,6 +6377,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6403,32 +6408,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128116277</v>
+        <v>128116261</v>
       </c>
       <c r="B61" t="n">
-        <v>98585</v>
+        <v>97462</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708269</v>
+        <v>708394</v>
       </c>
       <c r="R61" t="n">
-        <v>7294506</v>
+        <v>7294544</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6474,11 +6479,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6505,32 +6505,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128116261</v>
+        <v>128116292</v>
       </c>
       <c r="B62" t="n">
-        <v>97460</v>
+        <v>91484</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708394</v>
+        <v>708500</v>
       </c>
       <c r="R62" t="n">
-        <v>7294544</v>
+        <v>7294658</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6605,7 +6605,7 @@
         <v>128116271</v>
       </c>
       <c r="B63" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>128116276</v>
       </c>
       <c r="B64" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>128116287</v>
       </c>
       <c r="B65" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6990,32 +6990,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128116269</v>
+        <v>128116242</v>
       </c>
       <c r="B67" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708195</v>
+        <v>708298</v>
       </c>
       <c r="R67" t="n">
-        <v>7294329</v>
+        <v>7294185</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128116266</v>
+        <v>128116269</v>
       </c>
       <c r="B68" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708534</v>
+        <v>708195</v>
       </c>
       <c r="R68" t="n">
-        <v>7294561</v>
+        <v>7294329</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7184,32 +7184,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128116242</v>
+        <v>128116266</v>
       </c>
       <c r="B69" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708298</v>
+        <v>708534</v>
       </c>
       <c r="R69" t="n">
-        <v>7294185</v>
+        <v>7294561</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7378,10 +7378,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118837</v>
+        <v>128118863</v>
       </c>
       <c r="B71" t="n">
-        <v>56880</v>
+        <v>58059</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7389,21 +7389,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708415</v>
+        <v>708340</v>
       </c>
       <c r="R71" t="n">
-        <v>7294151</v>
+        <v>7294657</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7449,11 +7449,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>3st honor</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7480,32 +7475,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128118893</v>
+        <v>128118867</v>
       </c>
       <c r="B72" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7515,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708463</v>
+        <v>708482</v>
       </c>
       <c r="R72" t="n">
-        <v>7294191</v>
+        <v>7294514</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7570,39 +7565,39 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128118834</v>
+        <v>128118866</v>
       </c>
       <c r="B73" t="n">
-        <v>91431</v>
+        <v>98591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7612,10 +7607,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708433</v>
+        <v>708412</v>
       </c>
       <c r="R73" t="n">
-        <v>7294555</v>
+        <v>7294653</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7648,6 +7643,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118856</v>
+        <v>128118881</v>
       </c>
       <c r="B74" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708459</v>
+        <v>708273</v>
       </c>
       <c r="R74" t="n">
-        <v>7294618</v>
+        <v>7294469</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7745,6 +7745,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7771,32 +7776,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128118840</v>
+        <v>128118893</v>
       </c>
       <c r="B75" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7806,10 +7811,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708415</v>
+        <v>708463</v>
       </c>
       <c r="R75" t="n">
-        <v>7294056</v>
+        <v>7294191</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7861,17 +7866,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128118833</v>
+        <v>128118856</v>
       </c>
       <c r="B76" t="n">
-        <v>79121</v>
+        <v>80194</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7879,21 +7884,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7903,10 +7908,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>708245</v>
+        <v>708459</v>
       </c>
       <c r="R76" t="n">
-        <v>7294232</v>
+        <v>7294618</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7965,10 +7970,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118863</v>
+        <v>128118840</v>
       </c>
       <c r="B77" t="n">
-        <v>58059</v>
+        <v>80223</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7976,21 +7981,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8000,10 +8005,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708340</v>
+        <v>708415</v>
       </c>
       <c r="R77" t="n">
-        <v>7294657</v>
+        <v>7294056</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8062,32 +8067,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128118867</v>
+        <v>128118837</v>
       </c>
       <c r="B78" t="n">
-        <v>98588</v>
+        <v>56880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8097,10 +8102,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708482</v>
+        <v>708415</v>
       </c>
       <c r="R78" t="n">
-        <v>7294514</v>
+        <v>7294151</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8133,6 +8138,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>3st honor</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8159,32 +8169,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128118866</v>
+        <v>128118834</v>
       </c>
       <c r="B79" t="n">
-        <v>98588</v>
+        <v>91431</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8194,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708412</v>
+        <v>708433</v>
       </c>
       <c r="R79" t="n">
-        <v>7294653</v>
+        <v>7294555</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8230,11 +8240,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8261,32 +8266,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128118881</v>
+        <v>128118833</v>
       </c>
       <c r="B80" t="n">
-        <v>98588</v>
+        <v>79121</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8296,10 +8301,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708273</v>
+        <v>708245</v>
       </c>
       <c r="R80" t="n">
-        <v>7294469</v>
+        <v>7294232</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8332,11 +8337,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
         <v>128118848</v>
       </c>
       <c r="B82" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128118901</v>
+        <v>128118851</v>
       </c>
       <c r="B83" t="n">
-        <v>82948</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8568,21 +8568,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708358</v>
+        <v>708470</v>
       </c>
       <c r="R83" t="n">
-        <v>7294071</v>
+        <v>7294185</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8647,17 +8647,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128118851</v>
+        <v>128118901</v>
       </c>
       <c r="B84" t="n">
-        <v>57686</v>
+        <v>82948</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708470</v>
+        <v>708358</v>
       </c>
       <c r="R84" t="n">
-        <v>7294185</v>
+        <v>7294071</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8744,39 +8744,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128118873</v>
+        <v>128118844</v>
       </c>
       <c r="B85" t="n">
-        <v>98588</v>
+        <v>98612</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708238</v>
+        <v>708472</v>
       </c>
       <c r="R85" t="n">
-        <v>7294359</v>
+        <v>7294621</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8848,10 +8848,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128118877</v>
+        <v>128118873</v>
       </c>
       <c r="B86" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708246</v>
+        <v>708238</v>
       </c>
       <c r="R86" t="n">
-        <v>7294419</v>
+        <v>7294359</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8945,32 +8945,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128118844</v>
+        <v>128118877</v>
       </c>
       <c r="B87" t="n">
-        <v>98609</v>
+        <v>98591</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708472</v>
+        <v>708246</v>
       </c>
       <c r="R87" t="n">
-        <v>7294621</v>
+        <v>7294419</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9142,7 +9142,7 @@
         <v>128118876</v>
       </c>
       <c r="B89" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>128118870</v>
       </c>
       <c r="B90" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9430,32 +9430,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118829</v>
+        <v>128118868</v>
       </c>
       <c r="B92" t="n">
-        <v>105627</v>
+        <v>98591</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708299</v>
+        <v>708494</v>
       </c>
       <c r="R92" t="n">
-        <v>7294038</v>
+        <v>7294519</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9811,39 +9811,39 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128118868</v>
+        <v>128118829</v>
       </c>
       <c r="B96" t="n">
-        <v>98588</v>
+        <v>105636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708494</v>
+        <v>708299</v>
       </c>
       <c r="R96" t="n">
-        <v>7294519</v>
+        <v>7294038</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9918,7 +9918,7 @@
         <v>128118878</v>
       </c>
       <c r="B97" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10109,10 +10109,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128118909</v>
+        <v>128118847</v>
       </c>
       <c r="B99" t="n">
-        <v>80229</v>
+        <v>98612</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10120,21 +10120,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>708416</v>
+        <v>708461</v>
       </c>
       <c r="R99" t="n">
-        <v>7294052</v>
+        <v>7294368</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10199,39 +10199,39 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128118860</v>
+        <v>128118909</v>
       </c>
       <c r="B100" t="n">
-        <v>80194</v>
+        <v>80229</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>708188</v>
+        <v>708416</v>
       </c>
       <c r="R100" t="n">
-        <v>7294093</v>
+        <v>7294052</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10400,32 +10400,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128118847</v>
+        <v>128118860</v>
       </c>
       <c r="B102" t="n">
-        <v>98609</v>
+        <v>80194</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10435,10 +10435,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>708461</v>
+        <v>708188</v>
       </c>
       <c r="R102" t="n">
-        <v>7294368</v>
+        <v>7294093</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10594,32 +10594,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128118895</v>
+        <v>128118835</v>
       </c>
       <c r="B104" t="n">
-        <v>79089</v>
+        <v>58548</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>708412</v>
+        <v>708445</v>
       </c>
       <c r="R104" t="n">
-        <v>7294150</v>
+        <v>7294644</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10684,39 +10684,39 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128118912</v>
+        <v>128118872</v>
       </c>
       <c r="B105" t="n">
-        <v>80229</v>
+        <v>98591</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>708262</v>
+        <v>708200</v>
       </c>
       <c r="R105" t="n">
-        <v>7294457</v>
+        <v>7294326</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10781,39 +10781,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128118841</v>
+        <v>128118874</v>
       </c>
       <c r="B106" t="n">
-        <v>80223</v>
+        <v>98591</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>708337</v>
+        <v>708235</v>
       </c>
       <c r="R106" t="n">
-        <v>7294039</v>
+        <v>7294371</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10885,7 +10885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128118906</v>
+        <v>128118912</v>
       </c>
       <c r="B107" t="n">
         <v>80229</v>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>708432</v>
+        <v>708262</v>
       </c>
       <c r="R107" t="n">
-        <v>7294676</v>
+        <v>7294457</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -10975,17 +10975,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128118853</v>
+        <v>128118841</v>
       </c>
       <c r="B108" t="n">
-        <v>97462</v>
+        <v>80223</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10993,21 +10993,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>708228</v>
+        <v>708337</v>
       </c>
       <c r="R108" t="n">
-        <v>7294377</v>
+        <v>7294039</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11079,32 +11079,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128118872</v>
+        <v>128118906</v>
       </c>
       <c r="B109" t="n">
-        <v>98588</v>
+        <v>80229</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>708200</v>
+        <v>708432</v>
       </c>
       <c r="R109" t="n">
-        <v>7294326</v>
+        <v>7294676</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11169,39 +11169,39 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128118874</v>
+        <v>128118895</v>
       </c>
       <c r="B110" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>708235</v>
+        <v>708412</v>
       </c>
       <c r="R110" t="n">
-        <v>7294371</v>
+        <v>7294150</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128118835</v>
+        <v>128118832</v>
       </c>
       <c r="B111" t="n">
-        <v>58548</v>
+        <v>105636</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>208249</v>
+        <v>221725</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>708445</v>
+        <v>708229</v>
       </c>
       <c r="R111" t="n">
-        <v>7294644</v>
+        <v>7294386</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11370,10 +11370,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128118832</v>
+        <v>128118853</v>
       </c>
       <c r="B112" t="n">
-        <v>105627</v>
+        <v>97462</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11381,21 +11381,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>708229</v>
+        <v>708228</v>
       </c>
       <c r="R112" t="n">
-        <v>7294386</v>
+        <v>7294377</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11467,32 +11467,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128118888</v>
+        <v>128118879</v>
       </c>
       <c r="B113" t="n">
-        <v>91484</v>
+        <v>98591</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>708218</v>
+        <v>708260</v>
       </c>
       <c r="R113" t="n">
-        <v>7294252</v>
+        <v>7294439</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11540,6 +11540,11 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -11557,7 +11562,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -11567,7 +11572,7 @@
         <v>128118843</v>
       </c>
       <c r="B114" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11666,32 +11671,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128118879</v>
+        <v>128118888</v>
       </c>
       <c r="B115" t="n">
-        <v>98588</v>
+        <v>91484</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11701,10 +11706,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>708260</v>
+        <v>708218</v>
       </c>
       <c r="R115" t="n">
-        <v>7294439</v>
+        <v>7294252</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11739,11 +11744,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -11761,39 +11761,39 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128118875</v>
+        <v>128118836</v>
       </c>
       <c r="B116" t="n">
-        <v>98588</v>
+        <v>58548</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>708230</v>
+        <v>708203</v>
       </c>
       <c r="R116" t="n">
-        <v>7294377</v>
+        <v>7294324</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128118836</v>
+        <v>128118875</v>
       </c>
       <c r="B117" t="n">
-        <v>58548</v>
+        <v>98591</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>708203</v>
+        <v>708230</v>
       </c>
       <c r="R117" t="n">
-        <v>7294324</v>
+        <v>7294377</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -11962,10 +11962,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128118894</v>
+        <v>128118890</v>
       </c>
       <c r="B118" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11973,21 +11973,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>708443</v>
+        <v>708232</v>
       </c>
       <c r="R118" t="n">
-        <v>7294180</v>
+        <v>7294415</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12052,14 +12052,14 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128118898</v>
+        <v>128118894</v>
       </c>
       <c r="B119" t="n">
         <v>79089</v>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>708249</v>
+        <v>708443</v>
       </c>
       <c r="R119" t="n">
-        <v>7294216</v>
+        <v>7294180</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12149,17 +12149,17 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128118890</v>
+        <v>128118898</v>
       </c>
       <c r="B120" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12167,21 +12167,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12191,10 +12191,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>708232</v>
+        <v>708249</v>
       </c>
       <c r="R120" t="n">
-        <v>7294415</v>
+        <v>7294216</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12350,32 +12350,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128118889</v>
+        <v>128118845</v>
       </c>
       <c r="B122" t="n">
-        <v>91484</v>
+        <v>98612</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12385,10 +12385,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>708192</v>
+        <v>708477</v>
       </c>
       <c r="R122" t="n">
-        <v>7294318</v>
+        <v>7294616</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12440,39 +12440,39 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128118883</v>
+        <v>128118849</v>
       </c>
       <c r="B123" t="n">
-        <v>98588</v>
+        <v>98612</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>708436</v>
+        <v>708250</v>
       </c>
       <c r="R123" t="n">
-        <v>7294589</v>
+        <v>7294430</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12544,32 +12544,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128118845</v>
+        <v>128118889</v>
       </c>
       <c r="B124" t="n">
-        <v>98609</v>
+        <v>91484</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>708477</v>
+        <v>708192</v>
       </c>
       <c r="R124" t="n">
-        <v>7294616</v>
+        <v>7294318</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -12634,39 +12634,39 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128118849</v>
+        <v>128118883</v>
       </c>
       <c r="B125" t="n">
-        <v>98609</v>
+        <v>98591</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>708250</v>
+        <v>708436</v>
       </c>
       <c r="R125" t="n">
-        <v>7294430</v>
+        <v>7294589</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128118899</v>
+        <v>128118882</v>
       </c>
       <c r="B126" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>708214</v>
+        <v>708290</v>
       </c>
       <c r="R126" t="n">
-        <v>7294309</v>
+        <v>7294501</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -12828,17 +12828,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128118882</v>
+        <v>128118902</v>
       </c>
       <c r="B127" t="n">
-        <v>98588</v>
+        <v>91727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12846,21 +12846,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>708290</v>
+        <v>708202</v>
       </c>
       <c r="R127" t="n">
-        <v>7294501</v>
+        <v>7294326</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -12925,39 +12925,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128118902</v>
+        <v>128118839</v>
       </c>
       <c r="B128" t="n">
-        <v>91727</v>
+        <v>80223</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>708202</v>
+        <v>708424</v>
       </c>
       <c r="R128" t="n">
-        <v>7294326</v>
+        <v>7294672</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13022,39 +13022,39 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128118839</v>
+        <v>128118899</v>
       </c>
       <c r="B129" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>708424</v>
+        <v>708214</v>
       </c>
       <c r="R129" t="n">
-        <v>7294672</v>
+        <v>7294309</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13129,7 +13129,7 @@
         <v>128118846</v>
       </c>
       <c r="B130" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,32 +13320,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128118857</v>
+        <v>128118880</v>
       </c>
       <c r="B132" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>708335</v>
+        <v>708290</v>
       </c>
       <c r="R132" t="n">
-        <v>7294032</v>
+        <v>7294490</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
         <v>128118903</v>
       </c>
       <c r="B133" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13507,17 +13507,17 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128118880</v>
+        <v>128118869</v>
       </c>
       <c r="B134" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>708290</v>
+        <v>708487</v>
       </c>
       <c r="R134" t="n">
-        <v>7294490</v>
+        <v>7294472</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -13585,6 +13585,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13611,32 +13616,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128118869</v>
+        <v>128118857</v>
       </c>
       <c r="B135" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13646,10 +13651,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>708487</v>
+        <v>708335</v>
       </c>
       <c r="R135" t="n">
-        <v>7294472</v>
+        <v>7294032</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -13682,11 +13687,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Steve Daurer, Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -13813,7 +13813,7 @@
         <v>128118831</v>
       </c>
       <c r="B137" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>128118850</v>
       </c>
       <c r="B138" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128116249</v>
+        <v>128116286</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>91480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708207</v>
+        <v>708482</v>
       </c>
       <c r="R13" t="n">
-        <v>7294133</v>
+        <v>7294632</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128116286</v>
+        <v>128116304</v>
       </c>
       <c r="B14" t="n">
-        <v>91480</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708482</v>
+        <v>708225</v>
       </c>
       <c r="R14" t="n">
-        <v>7294632</v>
+        <v>7294108</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128116304</v>
+        <v>128116258</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708225</v>
+        <v>708471</v>
       </c>
       <c r="R15" t="n">
-        <v>7294108</v>
+        <v>7294139</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128116258</v>
+        <v>128116249</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708471</v>
+        <v>708207</v>
       </c>
       <c r="R16" t="n">
-        <v>7294139</v>
+        <v>7294133</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128116272</v>
+        <v>128116314</v>
       </c>
       <c r="B48" t="n">
-        <v>98591</v>
+        <v>92040</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
         <v>708243</v>
       </c>
       <c r="R48" t="n">
-        <v>7294403</v>
+        <v>7294415</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128116314</v>
+        <v>128116311</v>
       </c>
       <c r="B49" t="n">
-        <v>92040</v>
+        <v>82948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708243</v>
+        <v>708219</v>
       </c>
       <c r="R49" t="n">
-        <v>7294415</v>
+        <v>7294070</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5336,32 +5336,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128116311</v>
+        <v>128116272</v>
       </c>
       <c r="B50" t="n">
-        <v>82948</v>
+        <v>98591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708219</v>
+        <v>708243</v>
       </c>
       <c r="R50" t="n">
-        <v>7294070</v>
+        <v>7294403</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -7378,32 +7378,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118863</v>
+        <v>128118893</v>
       </c>
       <c r="B71" t="n">
-        <v>58059</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708340</v>
+        <v>708463</v>
       </c>
       <c r="R71" t="n">
-        <v>7294657</v>
+        <v>7294191</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7468,39 +7468,39 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128118867</v>
+        <v>128118856</v>
       </c>
       <c r="B72" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708482</v>
+        <v>708459</v>
       </c>
       <c r="R72" t="n">
-        <v>7294514</v>
+        <v>7294618</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7572,32 +7572,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128118866</v>
+        <v>128118840</v>
       </c>
       <c r="B73" t="n">
-        <v>98591</v>
+        <v>80223</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708412</v>
+        <v>708415</v>
       </c>
       <c r="R73" t="n">
-        <v>7294653</v>
+        <v>7294056</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7643,11 +7643,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7674,32 +7669,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118881</v>
+        <v>128118833</v>
       </c>
       <c r="B74" t="n">
-        <v>98591</v>
+        <v>79121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7709,10 +7704,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708273</v>
+        <v>708245</v>
       </c>
       <c r="R74" t="n">
-        <v>7294469</v>
+        <v>7294232</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7745,11 +7740,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7776,32 +7766,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128118893</v>
+        <v>128118834</v>
       </c>
       <c r="B75" t="n">
-        <v>79089</v>
+        <v>91431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7811,10 +7801,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708463</v>
+        <v>708433</v>
       </c>
       <c r="R75" t="n">
-        <v>7294191</v>
+        <v>7294555</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7866,39 +7856,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128118856</v>
+        <v>128118837</v>
       </c>
       <c r="B76" t="n">
-        <v>80194</v>
+        <v>56880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7908,10 +7898,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>708459</v>
+        <v>708415</v>
       </c>
       <c r="R76" t="n">
-        <v>7294618</v>
+        <v>7294151</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7944,6 +7934,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>3st honor</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7970,10 +7965,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118840</v>
+        <v>128118863</v>
       </c>
       <c r="B77" t="n">
-        <v>80223</v>
+        <v>58059</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7981,21 +7976,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8005,10 +8000,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708415</v>
+        <v>708340</v>
       </c>
       <c r="R77" t="n">
-        <v>7294056</v>
+        <v>7294657</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8067,32 +8062,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128118837</v>
+        <v>128118867</v>
       </c>
       <c r="B78" t="n">
-        <v>56880</v>
+        <v>98591</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8102,10 +8097,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708415</v>
+        <v>708482</v>
       </c>
       <c r="R78" t="n">
-        <v>7294151</v>
+        <v>7294514</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8138,11 +8133,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>3st honor</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8169,32 +8159,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128118834</v>
+        <v>128118866</v>
       </c>
       <c r="B79" t="n">
-        <v>91431</v>
+        <v>98591</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8194,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708433</v>
+        <v>708412</v>
       </c>
       <c r="R79" t="n">
-        <v>7294555</v>
+        <v>7294653</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8240,6 +8230,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8266,32 +8261,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128118833</v>
+        <v>128118881</v>
       </c>
       <c r="B80" t="n">
-        <v>79121</v>
+        <v>98591</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8296,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708245</v>
+        <v>708273</v>
       </c>
       <c r="R80" t="n">
-        <v>7294232</v>
+        <v>7294469</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8337,6 +8332,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8557,32 +8557,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128118851</v>
+        <v>128118844</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>98612</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708470</v>
+        <v>708472</v>
       </c>
       <c r="R83" t="n">
-        <v>7294185</v>
+        <v>7294621</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8654,32 +8654,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128118901</v>
+        <v>128118873</v>
       </c>
       <c r="B84" t="n">
-        <v>82948</v>
+        <v>98591</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708358</v>
+        <v>708238</v>
       </c>
       <c r="R84" t="n">
-        <v>7294071</v>
+        <v>7294359</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8744,39 +8744,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128118844</v>
+        <v>128118877</v>
       </c>
       <c r="B85" t="n">
-        <v>98612</v>
+        <v>98591</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708472</v>
+        <v>708246</v>
       </c>
       <c r="R85" t="n">
-        <v>7294621</v>
+        <v>7294419</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8848,32 +8848,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128118873</v>
+        <v>128118901</v>
       </c>
       <c r="B86" t="n">
-        <v>98591</v>
+        <v>82948</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708238</v>
+        <v>708358</v>
       </c>
       <c r="R86" t="n">
-        <v>7294359</v>
+        <v>7294071</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8938,39 +8938,39 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128118877</v>
+        <v>128118851</v>
       </c>
       <c r="B87" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708246</v>
+        <v>708470</v>
       </c>
       <c r="R87" t="n">
-        <v>7294419</v>
+        <v>7294185</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9430,32 +9430,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118868</v>
+        <v>128118884</v>
       </c>
       <c r="B92" t="n">
-        <v>98591</v>
+        <v>79168</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708494</v>
+        <v>708477</v>
       </c>
       <c r="R92" t="n">
-        <v>7294519</v>
+        <v>7294616</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9527,32 +9527,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128118854</v>
+        <v>128118896</v>
       </c>
       <c r="B93" t="n">
-        <v>97462</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708246</v>
+        <v>708411</v>
       </c>
       <c r="R93" t="n">
-        <v>7294430</v>
+        <v>7294054</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9617,39 +9617,39 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128118884</v>
+        <v>128118868</v>
       </c>
       <c r="B94" t="n">
-        <v>79168</v>
+        <v>98591</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708477</v>
+        <v>708494</v>
       </c>
       <c r="R94" t="n">
-        <v>7294616</v>
+        <v>7294519</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9721,32 +9721,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128118896</v>
+        <v>128118854</v>
       </c>
       <c r="B95" t="n">
-        <v>79089</v>
+        <v>97462</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708411</v>
+        <v>708246</v>
       </c>
       <c r="R95" t="n">
-        <v>7294054</v>
+        <v>7294430</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -9915,32 +9915,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128118878</v>
+        <v>128118892</v>
       </c>
       <c r="B97" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9950,10 +9950,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>708258</v>
+        <v>708476</v>
       </c>
       <c r="R97" t="n">
-        <v>7294447</v>
+        <v>7294478</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10005,39 +10005,39 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128118892</v>
+        <v>128118878</v>
       </c>
       <c r="B98" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>708476</v>
+        <v>708258</v>
       </c>
       <c r="R98" t="n">
-        <v>7294478</v>
+        <v>7294447</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11768,32 +11768,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128118836</v>
+        <v>128118875</v>
       </c>
       <c r="B116" t="n">
-        <v>58548</v>
+        <v>98591</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>708203</v>
+        <v>708230</v>
       </c>
       <c r="R116" t="n">
-        <v>7294324</v>
+        <v>7294377</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128118875</v>
+        <v>128118836</v>
       </c>
       <c r="B117" t="n">
-        <v>98591</v>
+        <v>58548</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>708230</v>
+        <v>708203</v>
       </c>
       <c r="R117" t="n">
-        <v>7294377</v>
+        <v>7294324</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12738,10 +12738,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128118882</v>
+        <v>128118902</v>
       </c>
       <c r="B126" t="n">
-        <v>98591</v>
+        <v>91727</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12749,21 +12749,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>708290</v>
+        <v>708202</v>
       </c>
       <c r="R126" t="n">
-        <v>7294501</v>
+        <v>7294326</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -12828,39 +12828,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128118902</v>
+        <v>128118839</v>
       </c>
       <c r="B127" t="n">
-        <v>91727</v>
+        <v>80223</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>708202</v>
+        <v>708424</v>
       </c>
       <c r="R127" t="n">
-        <v>7294326</v>
+        <v>7294672</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -12925,39 +12925,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128118839</v>
+        <v>128118899</v>
       </c>
       <c r="B128" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>708424</v>
+        <v>708214</v>
       </c>
       <c r="R128" t="n">
-        <v>7294672</v>
+        <v>7294309</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13022,39 +13022,39 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128118899</v>
+        <v>128118882</v>
       </c>
       <c r="B129" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>708214</v>
+        <v>708290</v>
       </c>
       <c r="R129" t="n">
-        <v>7294309</v>
+        <v>7294501</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -7378,10 +7378,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128118893</v>
+        <v>128118833</v>
       </c>
       <c r="B71" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7389,21 +7389,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708463</v>
+        <v>708245</v>
       </c>
       <c r="R71" t="n">
-        <v>7294191</v>
+        <v>7294232</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7669,32 +7669,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128118833</v>
+        <v>128118837</v>
       </c>
       <c r="B74" t="n">
-        <v>79121</v>
+        <v>56880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708245</v>
+        <v>708415</v>
       </c>
       <c r="R74" t="n">
-        <v>7294232</v>
+        <v>7294151</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7740,6 +7740,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>3st honor</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7766,10 +7771,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128118834</v>
+        <v>128118863</v>
       </c>
       <c r="B75" t="n">
-        <v>91431</v>
+        <v>58059</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7777,21 +7782,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7801,10 +7806,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708433</v>
+        <v>708340</v>
       </c>
       <c r="R75" t="n">
-        <v>7294555</v>
+        <v>7294657</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7863,32 +7868,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128118837</v>
+        <v>128118893</v>
       </c>
       <c r="B76" t="n">
-        <v>56880</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7898,10 +7903,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>708415</v>
+        <v>708463</v>
       </c>
       <c r="R76" t="n">
-        <v>7294151</v>
+        <v>7294191</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7936,11 +7941,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>3st honor</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -7958,17 +7958,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128118863</v>
+        <v>128118834</v>
       </c>
       <c r="B77" t="n">
-        <v>58059</v>
+        <v>91432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7976,21 +7976,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708340</v>
+        <v>708433</v>
       </c>
       <c r="R77" t="n">
-        <v>7294657</v>
+        <v>7294555</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8065,7 +8065,7 @@
         <v>128118867</v>
       </c>
       <c r="B78" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>128118866</v>
       </c>
       <c r="B79" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>128118881</v>
       </c>
       <c r="B80" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>128118848</v>
       </c>
       <c r="B82" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>128118844</v>
       </c>
       <c r="B83" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128118873</v>
       </c>
       <c r="B84" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>128118877</v>
       </c>
       <c r="B85" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9139,10 +9139,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128118876</v>
+        <v>128118870</v>
       </c>
       <c r="B89" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9174,10 +9174,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>708233</v>
+        <v>708407</v>
       </c>
       <c r="R89" t="n">
-        <v>7294407</v>
+        <v>7294148</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9236,10 +9236,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128118870</v>
+        <v>128118876</v>
       </c>
       <c r="B90" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>708407</v>
+        <v>708233</v>
       </c>
       <c r="R90" t="n">
-        <v>7294148</v>
+        <v>7294407</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9336,7 +9336,7 @@
         <v>128118885</v>
       </c>
       <c r="B91" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9430,32 +9430,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128118884</v>
+        <v>128118829</v>
       </c>
       <c r="B92" t="n">
-        <v>79168</v>
+        <v>105639</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>864</v>
+        <v>221725</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708477</v>
+        <v>708299</v>
       </c>
       <c r="R92" t="n">
-        <v>7294616</v>
+        <v>7294038</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9527,32 +9527,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128118896</v>
+        <v>128118854</v>
       </c>
       <c r="B93" t="n">
-        <v>79089</v>
+        <v>97463</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708411</v>
+        <v>708246</v>
       </c>
       <c r="R93" t="n">
-        <v>7294054</v>
+        <v>7294430</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -9627,7 +9627,7 @@
         <v>128118868</v>
       </c>
       <c r="B94" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9721,32 +9721,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128118854</v>
+        <v>128118896</v>
       </c>
       <c r="B95" t="n">
-        <v>97462</v>
+        <v>79089</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708246</v>
+        <v>708411</v>
       </c>
       <c r="R95" t="n">
-        <v>7294430</v>
+        <v>7294054</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9811,39 +9811,39 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128118829</v>
+        <v>128118884</v>
       </c>
       <c r="B96" t="n">
-        <v>105636</v>
+        <v>79168</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221725</v>
+        <v>864</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708299</v>
+        <v>708477</v>
       </c>
       <c r="R96" t="n">
-        <v>7294038</v>
+        <v>7294616</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10015,7 +10015,7 @@
         <v>128118878</v>
       </c>
       <c r="B98" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>128118847</v>
       </c>
       <c r="B99" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10497,32 +10497,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128118886</v>
+        <v>128118872</v>
       </c>
       <c r="B103" t="n">
-        <v>91484</v>
+        <v>98592</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>708480</v>
+        <v>708200</v>
       </c>
       <c r="R103" t="n">
-        <v>7294478</v>
+        <v>7294326</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10594,32 +10594,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128118835</v>
+        <v>128118886</v>
       </c>
       <c r="B104" t="n">
-        <v>58548</v>
+        <v>91485</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>208249</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>708445</v>
+        <v>708480</v>
       </c>
       <c r="R104" t="n">
-        <v>7294644</v>
+        <v>7294478</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10691,32 +10691,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128118872</v>
+        <v>128118895</v>
       </c>
       <c r="B105" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>708200</v>
+        <v>708412</v>
       </c>
       <c r="R105" t="n">
-        <v>7294326</v>
+        <v>7294150</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10781,39 +10781,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128118874</v>
+        <v>128118912</v>
       </c>
       <c r="B106" t="n">
-        <v>98591</v>
+        <v>80229</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>708235</v>
+        <v>708262</v>
       </c>
       <c r="R106" t="n">
-        <v>7294371</v>
+        <v>7294457</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10878,17 +10878,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128118912</v>
+        <v>128118841</v>
       </c>
       <c r="B107" t="n">
-        <v>80229</v>
+        <v>80223</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10896,21 +10896,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>708262</v>
+        <v>708337</v>
       </c>
       <c r="R107" t="n">
-        <v>7294457</v>
+        <v>7294039</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -10975,17 +10975,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128118841</v>
+        <v>128118906</v>
       </c>
       <c r="B108" t="n">
-        <v>80223</v>
+        <v>80229</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10993,21 +10993,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>708337</v>
+        <v>708432</v>
       </c>
       <c r="R108" t="n">
-        <v>7294039</v>
+        <v>7294676</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11072,17 +11072,17 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128118906</v>
+        <v>128118835</v>
       </c>
       <c r="B109" t="n">
-        <v>80229</v>
+        <v>58548</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11090,21 +11090,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>208249</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>708432</v>
+        <v>708445</v>
       </c>
       <c r="R109" t="n">
-        <v>7294676</v>
+        <v>7294644</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11169,39 +11169,39 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128118895</v>
+        <v>128118832</v>
       </c>
       <c r="B110" t="n">
-        <v>79089</v>
+        <v>105639</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>708412</v>
+        <v>708229</v>
       </c>
       <c r="R110" t="n">
-        <v>7294150</v>
+        <v>7294386</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128118832</v>
+        <v>128118853</v>
       </c>
       <c r="B111" t="n">
-        <v>105636</v>
+        <v>97463</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>708229</v>
+        <v>708228</v>
       </c>
       <c r="R111" t="n">
-        <v>7294386</v>
+        <v>7294377</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11370,32 +11370,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128118853</v>
+        <v>128118874</v>
       </c>
       <c r="B112" t="n">
-        <v>97462</v>
+        <v>98592</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>708228</v>
+        <v>708235</v>
       </c>
       <c r="R112" t="n">
-        <v>7294377</v>
+        <v>7294371</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11470,7 +11470,7 @@
         <v>128118879</v>
       </c>
       <c r="B113" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11569,32 +11569,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128118843</v>
+        <v>128118888</v>
       </c>
       <c r="B114" t="n">
-        <v>98612</v>
+        <v>91485</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11604,10 +11604,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>708496</v>
+        <v>708218</v>
       </c>
       <c r="R114" t="n">
-        <v>7294626</v>
+        <v>7294252</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11642,11 +11642,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -11664,39 +11659,39 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128118888</v>
+        <v>128118843</v>
       </c>
       <c r="B115" t="n">
-        <v>91484</v>
+        <v>98613</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11706,10 +11701,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>708218</v>
+        <v>708496</v>
       </c>
       <c r="R115" t="n">
-        <v>7294252</v>
+        <v>7294626</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11744,6 +11739,11 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -11761,39 +11761,39 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128118875</v>
+        <v>128118836</v>
       </c>
       <c r="B116" t="n">
-        <v>98591</v>
+        <v>58548</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>708230</v>
+        <v>708203</v>
       </c>
       <c r="R116" t="n">
-        <v>7294377</v>
+        <v>7294324</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128118836</v>
+        <v>128118875</v>
       </c>
       <c r="B117" t="n">
-        <v>58548</v>
+        <v>98592</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>708203</v>
+        <v>708230</v>
       </c>
       <c r="R117" t="n">
-        <v>7294324</v>
+        <v>7294377</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -11962,32 +11962,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128118890</v>
+        <v>128118862</v>
       </c>
       <c r="B118" t="n">
-        <v>91484</v>
+        <v>58059</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>708232</v>
+        <v>708424</v>
       </c>
       <c r="R118" t="n">
-        <v>7294415</v>
+        <v>7294076</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12253,32 +12253,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128118862</v>
+        <v>128118890</v>
       </c>
       <c r="B121" t="n">
-        <v>58059</v>
+        <v>91485</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>708424</v>
+        <v>708232</v>
       </c>
       <c r="R121" t="n">
-        <v>7294076</v>
+        <v>7294415</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12343,39 +12343,39 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128118845</v>
+        <v>128118889</v>
       </c>
       <c r="B122" t="n">
-        <v>98612</v>
+        <v>91485</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12385,10 +12385,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>708477</v>
+        <v>708192</v>
       </c>
       <c r="R122" t="n">
-        <v>7294616</v>
+        <v>7294318</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12440,17 +12440,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128118849</v>
+        <v>128118845</v>
       </c>
       <c r="B123" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>708250</v>
+        <v>708477</v>
       </c>
       <c r="R123" t="n">
-        <v>7294430</v>
+        <v>7294616</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12544,32 +12544,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128118889</v>
+        <v>128118849</v>
       </c>
       <c r="B124" t="n">
-        <v>91484</v>
+        <v>98613</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>708192</v>
+        <v>708250</v>
       </c>
       <c r="R124" t="n">
-        <v>7294318</v>
+        <v>7294430</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -12644,7 +12644,7 @@
         <v>128118883</v>
       </c>
       <c r="B125" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>128118902</v>
       </c>
       <c r="B126" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12835,32 +12835,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128118839</v>
+        <v>128118899</v>
       </c>
       <c r="B127" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>708424</v>
+        <v>708214</v>
       </c>
       <c r="R127" t="n">
-        <v>7294672</v>
+        <v>7294309</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -12925,39 +12925,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128118899</v>
+        <v>128118839</v>
       </c>
       <c r="B128" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>708214</v>
+        <v>708424</v>
       </c>
       <c r="R128" t="n">
-        <v>7294309</v>
+        <v>7294672</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13032,7 +13032,7 @@
         <v>128118882</v>
       </c>
       <c r="B129" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13126,32 +13126,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128118846</v>
+        <v>128118887</v>
       </c>
       <c r="B130" t="n">
-        <v>98612</v>
+        <v>91485</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13161,10 +13161,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>708469</v>
+        <v>708488</v>
       </c>
       <c r="R130" t="n">
-        <v>7294524</v>
+        <v>7294468</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13216,39 +13216,39 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128118887</v>
+        <v>128118846</v>
       </c>
       <c r="B131" t="n">
-        <v>91484</v>
+        <v>98613</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>708488</v>
+        <v>708469</v>
       </c>
       <c r="R131" t="n">
-        <v>7294468</v>
+        <v>7294524</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -13313,39 +13313,39 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128118880</v>
+        <v>128118903</v>
       </c>
       <c r="B132" t="n">
-        <v>98591</v>
+        <v>98509</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>708290</v>
+        <v>708233</v>
       </c>
       <c r="R132" t="n">
-        <v>7294490</v>
+        <v>7294206</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13410,39 +13410,39 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128118903</v>
+        <v>128118880</v>
       </c>
       <c r="B133" t="n">
-        <v>98508</v>
+        <v>98592</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>708233</v>
+        <v>708290</v>
       </c>
       <c r="R133" t="n">
-        <v>7294206</v>
+        <v>7294490</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Cecilia Lundin, Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
         <v>128118869</v>
       </c>
       <c r="B134" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>128118831</v>
       </c>
       <c r="B137" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>128118850</v>
       </c>
       <c r="B138" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14002,6 +14002,642 @@
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129001264</v>
+      </c>
+      <c r="B139" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Utterträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>708504</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7294541</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129001268</v>
+      </c>
+      <c r="B140" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Utterträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>708371</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7294151</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129001267</v>
+      </c>
+      <c r="B141" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Utterträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>708311</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7294080</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129001265</v>
+      </c>
+      <c r="B142" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Utterträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>708192</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7294349</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129001270</v>
+      </c>
+      <c r="B143" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Utterträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>708324</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7294192</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129001269</v>
+      </c>
+      <c r="B144" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Utterträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>708348</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7294166</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14428,37 +14428,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129001270</v>
+        <v>129001269</v>
       </c>
       <c r="B143" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>708324</v>
+        <v>708348</v>
       </c>
       <c r="R143" t="n">
-        <v>7294192</v>
+        <v>7294166</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14534,37 +14534,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129001269</v>
+        <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>708348</v>
+        <v>708324</v>
       </c>
       <c r="R144" t="n">
-        <v>7294166</v>
+        <v>7294192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14428,37 +14428,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129001270</v>
+        <v>129001269</v>
       </c>
       <c r="B143" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>708324</v>
+        <v>708348</v>
       </c>
       <c r="R143" t="n">
-        <v>7294192</v>
+        <v>7294166</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14534,37 +14534,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129001269</v>
+        <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>708348</v>
+        <v>708324</v>
       </c>
       <c r="R144" t="n">
-        <v>7294166</v>
+        <v>7294192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129001269</v>
       </c>
       <c r="B143" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129001269</v>
       </c>
       <c r="B143" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129001269</v>
       </c>
       <c r="B143" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14428,37 +14428,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129001269</v>
+        <v>129001270</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>708348</v>
+        <v>708324</v>
       </c>
       <c r="R143" t="n">
-        <v>7294166</v>
+        <v>7294192</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14534,37 +14534,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129001270</v>
+        <v>129001269</v>
       </c>
       <c r="B144" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>708324</v>
+        <v>708348</v>
       </c>
       <c r="R144" t="n">
-        <v>7294192</v>
+        <v>7294166</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 29368-2024 artfynd.xlsx
+++ b/artfynd/A 29368-2024 artfynd.xlsx
@@ -14007,7 +14007,7 @@
         <v>129001264</v>
       </c>
       <c r="B139" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>129001268</v>
       </c>
       <c r="B140" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>129001267</v>
       </c>
       <c r="B141" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>129001265</v>
       </c>
       <c r="B142" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14428,37 +14428,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129001270</v>
+        <v>129001269</v>
       </c>
       <c r="B143" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>708324</v>
+        <v>708348</v>
       </c>
       <c r="R143" t="n">
-        <v>7294192</v>
+        <v>7294166</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14534,37 +14534,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129001269</v>
+        <v>129001270</v>
       </c>
       <c r="B144" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>708348</v>
+        <v>708324</v>
       </c>
       <c r="R144" t="n">
-        <v>7294166</v>
+        <v>7294192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
